--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>- 기  준 : 전년 동기간 YOY  |  합계(FIT) = 우리팀(OTA+G-OTA) + 홈페이지(비관리)</t>
+          <t>- 기  준 : 전년 동기간 YOY  |  합계(FIT) = GS(OTA+G-OTA) + 홈페이지(비관리)</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>우리팀 (OTA+G-OTA)</t>
+          <t>GS (OTA+G-OTA)</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
@@ -1214,7 +1214,7 @@
     <row r="17">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>※ 투숙일 기준 30일 OTB · 홈페이지=자체채널(D멤버스·자사·FIT·제휴 등, 우리팀 비관리) · FIT=우리팀+홈페이지 · BSR(07/02)=소노 Booking Status Report FIT(전채널·시점차로 우리 FIT가 다소 낮음)</t>
+          <t>※ 투숙일 기준 30일 OTB · 홈페이지=자체채널(D멤버스·자사·FIT·제휴 등, GS 비관리) · FIT=GS+홈페이지 · BSR(07/02)=소노 Booking Status Report FIT(전채널·시점차로 우리 FIT가 다소 낮음)</t>
         </is>
       </c>
     </row>

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -782,7 +782,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>- 기  준 : 전년 동기간 YOY  |  합계(FIT) = GS(OTA+G-OTA) + 홈페이지(비관리)</t>
+          <t>- 기  준 : 전년 동기간 YOY  |  합계(FIT) = GS(OTA+G-OTA) + 비관리(홈페이지·제휴사·일반)</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>홈페이지 (비관리)</t>
+          <t>비관리 (홈피·제휴·일반)</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -1095,19 +1095,19 @@
         <v>184</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>-194</v>
+        <v>-210</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>2906</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3108</v>
+        <v>3124</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-202</v>
+        <v>-218</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>3321</v>
@@ -1185,19 +1185,19 @@
         <v>594</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>1585</v>
+        <v>1601</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>-991</v>
+        <v>-1007</v>
       </c>
       <c r="I16" s="20" t="n">
         <v>12460</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>14907</v>
+        <v>14923</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>-2447</v>
+        <v>-2463</v>
       </c>
       <c r="L16" s="24" t="n">
         <v>13801</v>
@@ -1214,7 +1214,7 @@
     <row r="17">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>※ 투숙일 기준 30일 OTB · 홈페이지=자체채널(D멤버스·자사·FIT·제휴 등, GS 비관리) · FIT=GS+홈페이지 · BSR(07/02)=소노 Booking Status Report FIT(전채널·시점차로 우리 FIT가 다소 낮음)</t>
+          <t>※ FIT=영업자료(대) 03일반=GS(OTA+G-OTA)+비관리(홈페이지·제휴사·일반). 제휴사·일반 코드는 온라인팀 raw_db엔 거의 없어 BSR(전채널) 대비 미달 · BSR(07/02)=소노 Booking Status Report FIT(전채널·시점차로 우리 FIT가 다소 낮음)</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>57</v>
       </c>
       <c r="P21" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q21" s="34" t="n">
-        <v>13</v>
+        <v>60</v>
+      </c>
+      <c r="Q21" s="31" t="n">
+        <v>-3</v>
       </c>
       <c r="R21" s="30" t="n">
         <v>73</v>
@@ -2551,10 +2551,10 @@
         <v>284</v>
       </c>
       <c r="V21" s="32" t="n">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="W21" s="33" t="n">
-        <v>-43</v>
+        <v>-59</v>
       </c>
     </row>
     <row r="22">
@@ -3804,10 +3804,10 @@
         <v>2906</v>
       </c>
       <c r="P6" s="30" t="n">
-        <v>3108</v>
+        <v>3124</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>-202</v>
+        <v>-218</v>
       </c>
       <c r="R6" s="30" t="n">
         <v>3910</v>
@@ -3822,10 +3822,10 @@
         <v>12460</v>
       </c>
       <c r="V6" s="32" t="n">
-        <v>14907</v>
+        <v>14923</v>
       </c>
       <c r="W6" s="33" t="n">
-        <v>-2447</v>
+        <v>-2463</v>
       </c>
     </row>
     <row r="7">
@@ -3874,10 +3874,10 @@
         <v>2853</v>
       </c>
       <c r="P7" s="30" t="n">
-        <v>2976</v>
+        <v>2992</v>
       </c>
       <c r="Q7" s="31" t="n">
-        <v>-123</v>
+        <v>-139</v>
       </c>
       <c r="R7" s="30" t="n">
         <v>3857</v>
@@ -3892,10 +3892,10 @@
         <v>12107</v>
       </c>
       <c r="V7" s="32" t="n">
-        <v>14146</v>
+        <v>14162</v>
       </c>
       <c r="W7" s="33" t="n">
-        <v>-2039</v>
+        <v>-2055</v>
       </c>
     </row>
     <row r="8">
@@ -3944,10 +3944,10 @@
         <v>2790</v>
       </c>
       <c r="P8" s="30" t="n">
-        <v>2826</v>
+        <v>2842</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>-36</v>
+        <v>-52</v>
       </c>
       <c r="R8" s="30" t="n">
         <v>3820</v>
@@ -3962,10 +3962,10 @@
         <v>11667</v>
       </c>
       <c r="V8" s="32" t="n">
-        <v>13408</v>
+        <v>13424</v>
       </c>
       <c r="W8" s="33" t="n">
-        <v>-1741</v>
+        <v>-1757</v>
       </c>
     </row>
     <row r="9">
@@ -4014,10 +4014,10 @@
         <v>2693</v>
       </c>
       <c r="P9" s="30" t="n">
-        <v>2707</v>
+        <v>2723</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>-14</v>
+        <v>-30</v>
       </c>
       <c r="R9" s="30" t="n">
         <v>3701</v>
@@ -4032,10 +4032,10 @@
         <v>11217</v>
       </c>
       <c r="V9" s="32" t="n">
-        <v>12591</v>
+        <v>12607</v>
       </c>
       <c r="W9" s="33" t="n">
-        <v>-1374</v>
+        <v>-1390</v>
       </c>
     </row>
     <row r="10">
@@ -4084,10 +4084,10 @@
         <v>2618</v>
       </c>
       <c r="P10" s="30" t="n">
-        <v>2625</v>
+        <v>2641</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>-7</v>
+        <v>-23</v>
       </c>
       <c r="R10" s="30" t="n">
         <v>3608</v>
@@ -4102,10 +4102,10 @@
         <v>10757</v>
       </c>
       <c r="V10" s="32" t="n">
-        <v>12123</v>
+        <v>12139</v>
       </c>
       <c r="W10" s="33" t="n">
-        <v>-1366</v>
+        <v>-1382</v>
       </c>
     </row>
     <row r="11">
@@ -4154,10 +4154,10 @@
         <v>2576</v>
       </c>
       <c r="P11" s="30" t="n">
-        <v>2557</v>
+        <v>2573</v>
       </c>
       <c r="Q11" s="34" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="R11" s="30" t="n">
         <v>3555</v>
@@ -4172,10 +4172,10 @@
         <v>10534</v>
       </c>
       <c r="V11" s="32" t="n">
-        <v>11815</v>
+        <v>11831</v>
       </c>
       <c r="W11" s="33" t="n">
-        <v>-1281</v>
+        <v>-1297</v>
       </c>
     </row>
     <row r="12">
@@ -4224,10 +4224,10 @@
         <v>2531</v>
       </c>
       <c r="P12" s="30" t="n">
-        <v>2471</v>
+        <v>2487</v>
       </c>
       <c r="Q12" s="34" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="R12" s="30" t="n">
         <v>3489</v>
@@ -4242,10 +4242,10 @@
         <v>10292</v>
       </c>
       <c r="V12" s="32" t="n">
-        <v>11435</v>
+        <v>11451</v>
       </c>
       <c r="W12" s="33" t="n">
-        <v>-1143</v>
+        <v>-1159</v>
       </c>
     </row>
     <row r="13">
@@ -4294,10 +4294,10 @@
         <v>2481</v>
       </c>
       <c r="P13" s="30" t="n">
-        <v>2424</v>
+        <v>2440</v>
       </c>
       <c r="Q13" s="34" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="R13" s="30" t="n">
         <v>3432</v>
@@ -4312,10 +4312,10 @@
         <v>10059</v>
       </c>
       <c r="V13" s="32" t="n">
-        <v>11076</v>
+        <v>11092</v>
       </c>
       <c r="W13" s="33" t="n">
-        <v>-1017</v>
+        <v>-1033</v>
       </c>
     </row>
     <row r="14">
@@ -4364,10 +4364,10 @@
         <v>2415</v>
       </c>
       <c r="P14" s="30" t="n">
-        <v>2349</v>
+        <v>2365</v>
       </c>
       <c r="Q14" s="34" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="R14" s="30" t="n">
         <v>3382</v>
@@ -4382,10 +4382,10 @@
         <v>9780</v>
       </c>
       <c r="V14" s="32" t="n">
-        <v>10658</v>
+        <v>10674</v>
       </c>
       <c r="W14" s="33" t="n">
-        <v>-878</v>
+        <v>-894</v>
       </c>
     </row>
     <row r="15">
@@ -4434,10 +4434,10 @@
         <v>2323</v>
       </c>
       <c r="P15" s="30" t="n">
-        <v>2283</v>
+        <v>2299</v>
       </c>
       <c r="Q15" s="34" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="R15" s="30" t="n">
         <v>3266</v>
@@ -4452,10 +4452,10 @@
         <v>9384</v>
       </c>
       <c r="V15" s="32" t="n">
-        <v>10106</v>
+        <v>10122</v>
       </c>
       <c r="W15" s="33" t="n">
-        <v>-722</v>
+        <v>-738</v>
       </c>
     </row>
     <row r="16">
@@ -4504,10 +4504,10 @@
         <v>2289</v>
       </c>
       <c r="P16" s="30" t="n">
-        <v>2197</v>
+        <v>2213</v>
       </c>
       <c r="Q16" s="34" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="R16" s="30" t="n">
         <v>3096</v>
@@ -4522,10 +4522,10 @@
         <v>9005</v>
       </c>
       <c r="V16" s="32" t="n">
-        <v>9640</v>
+        <v>9656</v>
       </c>
       <c r="W16" s="33" t="n">
-        <v>-635</v>
+        <v>-651</v>
       </c>
     </row>
     <row r="17">
@@ -4574,10 +4574,10 @@
         <v>2206</v>
       </c>
       <c r="P17" s="30" t="n">
-        <v>2128</v>
+        <v>2144</v>
       </c>
       <c r="Q17" s="34" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="R17" s="30" t="n">
         <v>2956</v>
@@ -4592,10 +4592,10 @@
         <v>8540</v>
       </c>
       <c r="V17" s="32" t="n">
-        <v>9307</v>
+        <v>9323</v>
       </c>
       <c r="W17" s="33" t="n">
-        <v>-767</v>
+        <v>-783</v>
       </c>
     </row>
     <row r="18">
@@ -4644,10 +4644,10 @@
         <v>2164</v>
       </c>
       <c r="P18" s="30" t="n">
-        <v>2072</v>
+        <v>2088</v>
       </c>
       <c r="Q18" s="34" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="R18" s="30" t="n">
         <v>2913</v>
@@ -4662,10 +4662,10 @@
         <v>8318</v>
       </c>
       <c r="V18" s="32" t="n">
-        <v>9046</v>
+        <v>9062</v>
       </c>
       <c r="W18" s="33" t="n">
-        <v>-728</v>
+        <v>-744</v>
       </c>
     </row>
     <row r="19">
@@ -4714,10 +4714,10 @@
         <v>2117</v>
       </c>
       <c r="P19" s="30" t="n">
-        <v>1988</v>
+        <v>2004</v>
       </c>
       <c r="Q19" s="34" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="R19" s="30" t="n">
         <v>2832</v>
@@ -4732,10 +4732,10 @@
         <v>8081</v>
       </c>
       <c r="V19" s="32" t="n">
-        <v>8542</v>
+        <v>8558</v>
       </c>
       <c r="W19" s="33" t="n">
-        <v>-461</v>
+        <v>-477</v>
       </c>
     </row>
     <row r="20">
@@ -4784,10 +4784,10 @@
         <v>2079</v>
       </c>
       <c r="P20" s="30" t="n">
-        <v>1910</v>
+        <v>1926</v>
       </c>
       <c r="Q20" s="34" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="R20" s="30" t="n">
         <v>2774</v>
@@ -4802,10 +4802,10 @@
         <v>7884</v>
       </c>
       <c r="V20" s="32" t="n">
-        <v>8237</v>
+        <v>8253</v>
       </c>
       <c r="W20" s="33" t="n">
-        <v>-353</v>
+        <v>-369</v>
       </c>
     </row>
     <row r="21">
@@ -4854,10 +4854,10 @@
         <v>1784</v>
       </c>
       <c r="P21" s="30" t="n">
-        <v>1840</v>
+        <v>1856</v>
       </c>
       <c r="Q21" s="31" t="n">
-        <v>-56</v>
+        <v>-72</v>
       </c>
       <c r="R21" s="30" t="n">
         <v>2672</v>
@@ -4872,10 +4872,10 @@
         <v>7391</v>
       </c>
       <c r="V21" s="32" t="n">
-        <v>7942</v>
+        <v>7958</v>
       </c>
       <c r="W21" s="33" t="n">
-        <v>-551</v>
+        <v>-567</v>
       </c>
     </row>
     <row r="22">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -345,6 +345,9 @@
     <xf numFmtId="167" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -352,9 +355,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -906,34 +906,34 @@
         <v>1231</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-228</v>
+        <v>-234</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18</v>
+        <v>133</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>304</v>
+        <v>356</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>-286</v>
+        <v>-223</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1249</v>
+        <v>1364</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1763</v>
+        <v>1821</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>-514</v>
+        <v>-457</v>
       </c>
       <c r="L10" s="13" t="n">
         <v>1361</v>
       </c>
       <c r="M10" s="14" t="n">
-        <v>0.9177075679647319</v>
+        <v>1.002204261572373</v>
       </c>
       <c r="N10" s="15" t="inlineStr">
         <is>
@@ -951,34 +951,34 @@
         <v>2547</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>3415</v>
+        <v>3416</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>-868</v>
+        <v>-869</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>115</v>
+        <v>252</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>371</v>
+        <v>486</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>-256</v>
+        <v>-234</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2662</v>
+        <v>2799</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>3786</v>
+        <v>3902</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>-1124</v>
+        <v>-1103</v>
       </c>
       <c r="L11" s="13" t="n">
         <v>2907</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>0.9157206742346061</v>
+        <v>0.9628482972136223</v>
       </c>
       <c r="N11" s="15" t="inlineStr">
         <is>
@@ -1002,28 +1002,28 @@
         <v>184</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1001</v>
+        <v>1064</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>808</v>
+        <v>832</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>1074</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>0.9320297951582868</v>
+        <v>0.9906890130353817</v>
       </c>
       <c r="N12" s="18" t="inlineStr">
         <is>
@@ -1038,41 +1038,41 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>691</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>-60</v>
+        <v>-54</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>101</v>
+        <v>371</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>118</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>-17</v>
+        <v>154</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>217</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>732</v>
+        <v>1008</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>809</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>-77</v>
+        <v>845</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>163</v>
       </c>
       <c r="L13" s="13" t="n">
         <v>805</v>
       </c>
       <c r="M13" s="14" t="n">
-        <v>0.9093167701863354</v>
-      </c>
-      <c r="N13" s="15" t="inlineStr">
-        <is>
-          <t>전년미달 ▼</t>
+        <v>1.252173913043478</v>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>전년초과 ▲</t>
         </is>
       </c>
     </row>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>2722</v>
+        <v>2725</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2730</v>
+        <v>2731</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>184</v>
+        <v>340</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>-210</v>
+        <v>-157</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2906</v>
+        <v>3065</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3124</v>
+        <v>3228</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-218</v>
+        <v>-163</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>3321</v>
       </c>
       <c r="M14" s="14" t="n">
-        <v>0.8750376392652816</v>
+        <v>0.9229147847034026</v>
       </c>
       <c r="N14" s="15" t="inlineStr">
         <is>
@@ -1131,34 +1131,34 @@
         <v>3796</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>4272</v>
+        <v>4276</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-476</v>
+        <v>-480</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>114</v>
+        <v>274</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>361</v>
+        <v>475</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>-247</v>
+        <v>-201</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>3910</v>
+        <v>4070</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>4633</v>
+        <v>4751</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-723</v>
+        <v>-681</v>
       </c>
       <c r="L15" s="13" t="n">
         <v>4333</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.9023771059312254</v>
+        <v>0.9393030233094853</v>
       </c>
       <c r="N15" s="15" t="inlineStr">
         <is>
@@ -1173,37 +1173,37 @@
         </is>
       </c>
       <c r="C16" s="20" t="n">
-        <v>11866</v>
+        <v>11875</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>13322</v>
+        <v>13334</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>-1456</v>
+        <v>-1459</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>594</v>
+        <v>1495</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>1601</v>
+        <v>2045</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>-1007</v>
+        <v>-550</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>12460</v>
+        <v>13370</v>
       </c>
       <c r="J16" s="20" t="n">
-        <v>14923</v>
+        <v>15379</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>-2463</v>
+        <v>-2009</v>
       </c>
       <c r="L16" s="24" t="n">
         <v>13801</v>
       </c>
       <c r="M16" s="25" t="n">
-        <v>0.9028331280342005</v>
+        <v>0.9687703789580465</v>
       </c>
       <c r="N16" s="26" t="inlineStr">
         <is>
@@ -1444,67 +1444,67 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" s="30" t="n">
+        <v>110</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>-52</v>
+      </c>
+      <c r="F6" s="30" t="n">
         <v>104</v>
       </c>
-      <c r="E6" s="31" t="n">
-        <v>-49</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>99</v>
-      </c>
       <c r="G6" s="30" t="n">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>-155</v>
+        <v>-139</v>
       </c>
       <c r="I6" s="30" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>66</v>
-      </c>
-      <c r="K6" s="31" t="n">
-        <v>-4</v>
+        <v>69</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="L6" s="30" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M6" s="30" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N6" s="31" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="O6" s="30" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P6" s="30" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="Q6" s="31" t="n">
         <v>-79</v>
       </c>
       <c r="R6" s="30" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="S6" s="30" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="T6" s="31" t="n">
         <v>-89</v>
       </c>
-      <c r="U6" s="32" t="n">
-        <v>353</v>
-      </c>
-      <c r="V6" s="32" t="n">
-        <v>761</v>
-      </c>
-      <c r="W6" s="33" t="n">
-        <v>-408</v>
+      <c r="U6" s="33" t="n">
+        <v>374</v>
+      </c>
+      <c r="V6" s="33" t="n">
+        <v>763</v>
+      </c>
+      <c r="W6" s="34" t="n">
+        <v>-389</v>
       </c>
     </row>
     <row r="7">
@@ -1514,66 +1514,66 @@
         </is>
       </c>
       <c r="C7" s="30" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>83</v>
-      </c>
-      <c r="E7" s="34" t="n">
         <v>81</v>
       </c>
+      <c r="E7" s="35" t="n">
+        <v>86</v>
+      </c>
       <c r="F7" s="30" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>-143</v>
+        <v>-142</v>
       </c>
       <c r="I7" s="30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J7" s="30" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K7" s="31" t="n">
-        <v>-28</v>
+        <v>-24</v>
       </c>
       <c r="L7" s="30" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N7" s="31" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="O7" s="30" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P7" s="30" t="n">
         <v>150</v>
       </c>
       <c r="Q7" s="31" t="n">
-        <v>-87</v>
+        <v>-84</v>
       </c>
       <c r="R7" s="30" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S7" s="30" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="T7" s="31" t="n">
-        <v>-111</v>
-      </c>
-      <c r="U7" s="32" t="n">
-        <v>440</v>
-      </c>
-      <c r="V7" s="32" t="n">
-        <v>738</v>
-      </c>
-      <c r="W7" s="33" t="n">
+        <v>-120</v>
+      </c>
+      <c r="U7" s="33" t="n">
+        <v>435</v>
+      </c>
+      <c r="V7" s="33" t="n">
+        <v>733</v>
+      </c>
+      <c r="W7" s="34" t="n">
         <v>-298</v>
       </c>
     </row>
@@ -1584,67 +1584,67 @@
         </is>
       </c>
       <c r="C8" s="30" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <v>-5</v>
+        <v>78</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>-228</v>
+        <v>-234</v>
       </c>
       <c r="I8" s="30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J8" s="30" t="n">
+        <v>49</v>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M8" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="K8" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="L8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="30" t="n">
-        <v>38</v>
-      </c>
       <c r="N8" s="31" t="n">
-        <v>-38</v>
+        <v>-46</v>
       </c>
       <c r="O8" s="30" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="P8" s="30" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="Q8" s="31" t="n">
-        <v>-22</v>
+        <v>-27</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="S8" s="30" t="n">
         <v>206</v>
       </c>
       <c r="T8" s="31" t="n">
-        <v>-87</v>
-      </c>
-      <c r="U8" s="32" t="n">
-        <v>450</v>
-      </c>
-      <c r="V8" s="32" t="n">
-        <v>817</v>
-      </c>
-      <c r="W8" s="33" t="n">
-        <v>-367</v>
+        <v>-75</v>
+      </c>
+      <c r="U8" s="33" t="n">
+        <v>476</v>
+      </c>
+      <c r="V8" s="33" t="n">
+        <v>848</v>
+      </c>
+      <c r="W8" s="34" t="n">
+        <v>-372</v>
       </c>
     </row>
     <row r="9">
@@ -1657,64 +1657,64 @@
         <v>62</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>58</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <v>4</v>
+        <v>54</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H9" s="31" t="n">
         <v>-2</v>
       </c>
       <c r="I9" s="30" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="K9" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="K9" s="35" t="n">
         <v>39</v>
       </c>
       <c r="L9" s="30" t="n">
         <v>25</v>
       </c>
       <c r="M9" s="30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N9" s="31" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="O9" s="30" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P9" s="30" t="n">
         <v>82</v>
       </c>
       <c r="Q9" s="31" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="S9" s="30" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="T9" s="31" t="n">
-        <v>-28</v>
-      </c>
-      <c r="U9" s="32" t="n">
-        <v>460</v>
-      </c>
-      <c r="V9" s="32" t="n">
-        <v>468</v>
-      </c>
-      <c r="W9" s="33" t="n">
-        <v>-8</v>
+        <v>-29</v>
+      </c>
+      <c r="U9" s="33" t="n">
+        <v>479</v>
+      </c>
+      <c r="V9" s="33" t="n">
+        <v>481</v>
+      </c>
+      <c r="W9" s="34" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="10">
@@ -1724,66 +1724,66 @@
         </is>
       </c>
       <c r="C10" s="30" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="E10" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="35" t="n">
         <v>7</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="H10" s="35" t="n">
-        <v>0</v>
+        <v>83</v>
+      </c>
+      <c r="H10" s="31" t="n">
+        <v>-8</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" s="31" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N10" s="31" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="O10" s="30" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P10" s="30" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q10" s="31" t="n">
-        <v>-26</v>
+        <v>-21</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S10" s="30" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T10" s="31" t="n">
-        <v>-46</v>
-      </c>
-      <c r="U10" s="32" t="n">
-        <v>223</v>
-      </c>
-      <c r="V10" s="32" t="n">
-        <v>308</v>
-      </c>
-      <c r="W10" s="33" t="n">
+        <v>-45</v>
+      </c>
+      <c r="U10" s="33" t="n">
+        <v>235</v>
+      </c>
+      <c r="V10" s="33" t="n">
+        <v>320</v>
+      </c>
+      <c r="W10" s="34" t="n">
         <v>-85</v>
       </c>
     </row>
@@ -1794,67 +1794,67 @@
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>-88</v>
+        <v>-85</v>
       </c>
       <c r="I11" s="30" t="n">
         <v>32</v>
       </c>
       <c r="J11" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="K11" s="31" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L11" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="K11" s="31" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L11" s="30" t="n">
-        <v>35</v>
-      </c>
       <c r="M11" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" s="34" t="n">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="N11" s="35" t="n">
+        <v>27</v>
       </c>
       <c r="O11" s="30" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P11" s="30" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q11" s="31" t="n">
-        <v>-41</v>
+        <v>-37</v>
       </c>
       <c r="R11" s="30" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S11" s="30" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T11" s="31" t="n">
-        <v>-14</v>
-      </c>
-      <c r="U11" s="32" t="n">
-        <v>242</v>
-      </c>
-      <c r="V11" s="32" t="n">
-        <v>380</v>
-      </c>
-      <c r="W11" s="33" t="n">
-        <v>-138</v>
+        <v>-11</v>
+      </c>
+      <c r="U11" s="33" t="n">
+        <v>258</v>
+      </c>
+      <c r="V11" s="33" t="n">
+        <v>382</v>
+      </c>
+      <c r="W11" s="34" t="n">
+        <v>-124</v>
       </c>
     </row>
     <row r="12">
@@ -1864,67 +1864,67 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E12" s="31" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="F12" s="30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>-49</v>
+        <v>-57</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>30</v>
       </c>
       <c r="K12" s="31" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="L12" s="30" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M12" s="30" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="O12" s="30" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P12" s="30" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q12" s="34" t="n">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="Q12" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S12" s="30" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="T12" s="31" t="n">
-        <v>-59</v>
-      </c>
-      <c r="U12" s="32" t="n">
-        <v>233</v>
-      </c>
-      <c r="V12" s="32" t="n">
-        <v>359</v>
-      </c>
-      <c r="W12" s="33" t="n">
-        <v>-126</v>
+        <v>-65</v>
+      </c>
+      <c r="U12" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="V12" s="33" t="n">
+        <v>385</v>
+      </c>
+      <c r="W12" s="34" t="n">
+        <v>-145</v>
       </c>
     </row>
     <row r="13">
@@ -1934,67 +1934,67 @@
         </is>
       </c>
       <c r="C13" s="30" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="H13" s="31" t="n">
-        <v>-81</v>
+        <v>-86</v>
       </c>
       <c r="I13" s="30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J13" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="K13" s="34" t="n">
-        <v>13</v>
-      </c>
       <c r="L13" s="30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M13" s="30" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N13" s="31" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="O13" s="30" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P13" s="30" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q13" s="31" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S13" s="30" t="n">
         <v>80</v>
       </c>
       <c r="T13" s="31" t="n">
-        <v>-30</v>
-      </c>
-      <c r="U13" s="32" t="n">
-        <v>279</v>
-      </c>
-      <c r="V13" s="32" t="n">
-        <v>418</v>
-      </c>
-      <c r="W13" s="33" t="n">
-        <v>-139</v>
+        <v>-29</v>
+      </c>
+      <c r="U13" s="33" t="n">
+        <v>299</v>
+      </c>
+      <c r="V13" s="33" t="n">
+        <v>433</v>
+      </c>
+      <c r="W13" s="34" t="n">
+        <v>-134</v>
       </c>
     </row>
     <row r="14">
@@ -2004,67 +2004,67 @@
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>82</v>
       </c>
       <c r="E14" s="31" t="n">
-        <v>-34</v>
+        <v>-29</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H14" s="31" t="n">
-        <v>-81</v>
+        <v>-76</v>
       </c>
       <c r="I14" s="30" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>27</v>
       </c>
       <c r="K14" s="35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" s="30" t="n">
+        <v>74</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>57</v>
+      </c>
+      <c r="N14" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="O14" s="30" t="n">
+        <v>104</v>
+      </c>
+      <c r="P14" s="30" t="n">
         <v>69</v>
       </c>
-      <c r="M14" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="N14" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="O14" s="30" t="n">
-        <v>92</v>
-      </c>
-      <c r="P14" s="30" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q14" s="34" t="n">
-        <v>26</v>
+      <c r="Q14" s="35" t="n">
+        <v>35</v>
       </c>
       <c r="R14" s="30" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S14" s="30" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="T14" s="31" t="n">
-        <v>-80</v>
-      </c>
-      <c r="U14" s="32" t="n">
-        <v>396</v>
-      </c>
-      <c r="V14" s="32" t="n">
-        <v>552</v>
-      </c>
-      <c r="W14" s="33" t="n">
-        <v>-156</v>
+        <v>-87</v>
+      </c>
+      <c r="U14" s="33" t="n">
+        <v>429</v>
+      </c>
+      <c r="V14" s="33" t="n">
+        <v>563</v>
+      </c>
+      <c r="W14" s="34" t="n">
+        <v>-134</v>
       </c>
     </row>
     <row r="15">
@@ -2074,67 +2074,67 @@
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>67</v>
-      </c>
-      <c r="E15" s="34" t="n">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>24</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>-26</v>
+        <v>-37</v>
       </c>
       <c r="I15" s="30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" s="34" t="n">
+        <v>28</v>
+      </c>
+      <c r="K15" s="35" t="n">
         <v>18</v>
       </c>
       <c r="L15" s="30" t="n">
         <v>-19</v>
       </c>
       <c r="M15" s="30" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>-57</v>
+        <v>-60</v>
       </c>
       <c r="O15" s="30" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="P15" s="30" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q15" s="31" t="n">
-        <v>-52</v>
+        <v>-48</v>
       </c>
       <c r="R15" s="30" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S15" s="30" t="n">
-        <v>152</v>
-      </c>
-      <c r="T15" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="U15" s="32" t="n">
-        <v>379</v>
-      </c>
-      <c r="V15" s="32" t="n">
-        <v>466</v>
-      </c>
-      <c r="W15" s="33" t="n">
-        <v>-87</v>
+        <v>154</v>
+      </c>
+      <c r="T15" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="U15" s="33" t="n">
+        <v>394</v>
+      </c>
+      <c r="V15" s="33" t="n">
+        <v>482</v>
+      </c>
+      <c r="W15" s="34" t="n">
+        <v>-88</v>
       </c>
     </row>
     <row r="16">
@@ -2144,67 +2144,67 @@
         </is>
       </c>
       <c r="C16" s="30" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D16" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="E16" s="34" t="n">
-        <v>16</v>
+      <c r="E16" s="35" t="n">
+        <v>23</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>80</v>
-      </c>
-      <c r="H16" s="34" t="n">
-        <v>49</v>
+        <v>79</v>
+      </c>
+      <c r="H16" s="35" t="n">
+        <v>57</v>
       </c>
       <c r="I16" s="30" t="n">
         <v>38</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="K16" s="34" t="n">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>10</v>
       </c>
       <c r="L16" s="30" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M16" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="N16" s="34" t="n">
-        <v>4</v>
+      <c r="N16" s="35" t="n">
+        <v>12</v>
       </c>
       <c r="O16" s="30" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P16" s="30" t="n">
         <v>69</v>
       </c>
-      <c r="Q16" s="34" t="n">
-        <v>14</v>
+      <c r="Q16" s="35" t="n">
+        <v>13</v>
       </c>
       <c r="R16" s="30" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="S16" s="30" t="n">
-        <v>102</v>
-      </c>
-      <c r="T16" s="34" t="n">
-        <v>38</v>
-      </c>
-      <c r="U16" s="32" t="n">
-        <v>465</v>
-      </c>
-      <c r="V16" s="32" t="n">
-        <v>333</v>
+        <v>110</v>
+      </c>
+      <c r="T16" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="U16" s="33" t="n">
+        <v>488</v>
+      </c>
+      <c r="V16" s="33" t="n">
+        <v>341</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="C17" s="30" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="E17" s="31" t="n">
-        <v>-3</v>
+        <v>46</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>10</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H17" s="31" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J17" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="K17" s="34" t="n">
-        <v>34</v>
+      <c r="K17" s="35" t="n">
+        <v>37</v>
       </c>
       <c r="L17" s="30" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M17" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="N17" s="34" t="n">
-        <v>7</v>
+      <c r="N17" s="35" t="n">
+        <v>10</v>
       </c>
       <c r="O17" s="30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P17" s="30" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q17" s="31" t="n">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="R17" s="30" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S17" s="30" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T17" s="31" t="n">
         <v>-54</v>
       </c>
-      <c r="U17" s="32" t="n">
-        <v>222</v>
-      </c>
-      <c r="V17" s="32" t="n">
-        <v>261</v>
-      </c>
-      <c r="W17" s="33" t="n">
-        <v>-39</v>
+      <c r="U17" s="33" t="n">
+        <v>246</v>
+      </c>
+      <c r="V17" s="33" t="n">
+        <v>269</v>
+      </c>
+      <c r="W17" s="34" t="n">
+        <v>-23</v>
       </c>
     </row>
     <row r="18">
@@ -2287,64 +2287,64 @@
         <v>22</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E18" s="31" t="n">
-        <v>-36</v>
+        <v>-38</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H18" s="31" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="I18" s="30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" s="31" t="n">
         <v>-4</v>
       </c>
       <c r="L18" s="30" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M18" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="N18" s="34" t="n">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="N18" s="31" t="n">
+        <v>-2</v>
       </c>
       <c r="O18" s="30" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P18" s="30" t="n">
         <v>84</v>
       </c>
       <c r="Q18" s="31" t="n">
-        <v>-37</v>
+        <v>-35</v>
       </c>
       <c r="R18" s="30" t="n">
         <v>81</v>
       </c>
       <c r="S18" s="30" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="T18" s="31" t="n">
-        <v>-184</v>
-      </c>
-      <c r="U18" s="32" t="n">
-        <v>237</v>
-      </c>
-      <c r="V18" s="32" t="n">
-        <v>504</v>
-      </c>
-      <c r="W18" s="33" t="n">
-        <v>-267</v>
+        <v>-188</v>
+      </c>
+      <c r="U18" s="33" t="n">
+        <v>240</v>
+      </c>
+      <c r="V18" s="33" t="n">
+        <v>509</v>
+      </c>
+      <c r="W18" s="34" t="n">
+        <v>-269</v>
       </c>
     </row>
     <row r="19">
@@ -2354,67 +2354,67 @@
         </is>
       </c>
       <c r="C19" s="30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E19" s="31" t="n">
-        <v>-16</v>
+        <v>-8</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H19" s="31" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="K19" s="34" t="n">
-        <v>27</v>
+      <c r="K19" s="35" t="n">
+        <v>25</v>
       </c>
       <c r="L19" s="30" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="M19" s="30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>-26</v>
+        <v>-17</v>
       </c>
       <c r="O19" s="30" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P19" s="30" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q19" s="31" t="n">
-        <v>-40</v>
+        <v>-35</v>
       </c>
       <c r="R19" s="30" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S19" s="30" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T19" s="31" t="n">
-        <v>-46</v>
-      </c>
-      <c r="U19" s="32" t="n">
-        <v>197</v>
-      </c>
-      <c r="V19" s="32" t="n">
-        <v>305</v>
-      </c>
-      <c r="W19" s="33" t="n">
-        <v>-108</v>
+        <v>-41</v>
+      </c>
+      <c r="U19" s="33" t="n">
+        <v>223</v>
+      </c>
+      <c r="V19" s="33" t="n">
+        <v>304</v>
+      </c>
+      <c r="W19" s="34" t="n">
+        <v>-81</v>
       </c>
     </row>
     <row r="20">
@@ -2424,67 +2424,67 @@
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E20" s="31" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="F20" s="30" t="n">
+        <v>53</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>49</v>
+      </c>
+      <c r="J20" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="G20" s="30" t="n">
-        <v>39</v>
-      </c>
-      <c r="H20" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="J20" s="30" t="n">
-        <v>44</v>
-      </c>
       <c r="K20" s="35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L20" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N20" s="31" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="O20" s="30" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P20" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q20" s="34" t="n">
-        <v>225</v>
+        <v>76</v>
+      </c>
+      <c r="Q20" s="35" t="n">
+        <v>220</v>
       </c>
       <c r="R20" s="30" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="S20" s="30" t="n">
-        <v>100</v>
-      </c>
-      <c r="T20" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" s="32" t="n">
-        <v>493</v>
-      </c>
-      <c r="V20" s="32" t="n">
-        <v>295</v>
+        <v>106</v>
+      </c>
+      <c r="T20" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" s="33" t="n">
+        <v>524</v>
+      </c>
+      <c r="V20" s="33" t="n">
+        <v>317</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21">
@@ -2497,64 +2497,64 @@
         <v>27</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E21" s="31" t="n">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H21" s="31" t="n">
-        <v>-92</v>
+        <v>-101</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="34" t="n">
-        <v>33</v>
+        <v>4</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>32</v>
       </c>
       <c r="L21" s="30" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M21" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="N21" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" s="35" t="n">
         <v>41</v>
       </c>
       <c r="O21" s="30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P21" s="30" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q21" s="31" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="R21" s="30" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S21" s="30" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="T21" s="31" t="n">
-        <v>-14</v>
-      </c>
-      <c r="U21" s="32" t="n">
-        <v>284</v>
-      </c>
-      <c r="V21" s="32" t="n">
-        <v>343</v>
-      </c>
-      <c r="W21" s="33" t="n">
-        <v>-59</v>
+        <v>-27</v>
+      </c>
+      <c r="U21" s="33" t="n">
+        <v>282</v>
+      </c>
+      <c r="V21" s="33" t="n">
+        <v>372</v>
+      </c>
+      <c r="W21" s="34" t="n">
+        <v>-90</v>
       </c>
     </row>
     <row r="22">
@@ -2564,31 +2564,31 @@
         </is>
       </c>
       <c r="C22" s="30" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E22" s="31" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>47</v>
-      </c>
-      <c r="H22" s="34" t="n">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="H22" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="I22" s="30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="K22" s="34" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>22</v>
       </c>
       <c r="L22" s="30" t="n">
         <v>4</v>
@@ -2600,31 +2600,31 @@
         <v>-12</v>
       </c>
       <c r="O22" s="30" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="P22" s="30" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q22" s="31" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="R22" s="30" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S22" s="30" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="T22" s="31" t="n">
-        <v>-31</v>
-      </c>
-      <c r="U22" s="32" t="n">
-        <v>251</v>
-      </c>
-      <c r="V22" s="32" t="n">
-        <v>304</v>
-      </c>
-      <c r="W22" s="33" t="n">
-        <v>-53</v>
+        <v>-35</v>
+      </c>
+      <c r="U22" s="33" t="n">
+        <v>260</v>
+      </c>
+      <c r="V22" s="33" t="n">
+        <v>314</v>
+      </c>
+      <c r="W22" s="34" t="n">
+        <v>-54</v>
       </c>
     </row>
     <row r="23">
@@ -2637,64 +2637,64 @@
         <v>147</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="E23" s="34" t="n">
-        <v>103</v>
+        <v>46</v>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>101</v>
       </c>
       <c r="F23" s="30" t="n">
+        <v>73</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>43</v>
+      </c>
+      <c r="H23" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="30" t="n">
+        <v>29</v>
+      </c>
+      <c r="J23" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="L23" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" s="30" t="n">
+        <v>19</v>
+      </c>
+      <c r="N23" s="31" t="n">
+        <v>-11</v>
+      </c>
+      <c r="O23" s="30" t="n">
+        <v>132</v>
+      </c>
+      <c r="P23" s="30" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q23" s="35" t="n">
+        <v>79</v>
+      </c>
+      <c r="R23" s="30" t="n">
+        <v>167</v>
+      </c>
+      <c r="S23" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="G23" s="30" t="n">
-        <v>41</v>
-      </c>
-      <c r="H23" s="34" t="n">
-        <v>25</v>
-      </c>
-      <c r="I23" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="J23" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="K23" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="L23" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="M23" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="N23" s="31" t="n">
-        <v>-8</v>
-      </c>
-      <c r="O23" s="30" t="n">
-        <v>129</v>
-      </c>
-      <c r="P23" s="30" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q23" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="R23" s="30" t="n">
-        <v>165</v>
-      </c>
-      <c r="S23" s="30" t="n">
-        <v>63</v>
-      </c>
-      <c r="T23" s="34" t="n">
-        <v>102</v>
-      </c>
-      <c r="U23" s="32" t="n">
-        <v>540</v>
-      </c>
-      <c r="V23" s="32" t="n">
-        <v>220</v>
+      <c r="T23" s="35" t="n">
+        <v>101</v>
+      </c>
+      <c r="U23" s="33" t="n">
+        <v>556</v>
+      </c>
+      <c r="V23" s="33" t="n">
+        <v>234</v>
       </c>
       <c r="W23" s="36" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24">
@@ -2707,10 +2707,10 @@
         <v>9</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E24" s="31" t="n">
-        <v>-29</v>
+        <v>-34</v>
       </c>
       <c r="F24" s="30" t="n">
         <v>42</v>
@@ -2718,50 +2718,50 @@
       <c r="G24" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="H24" s="34" t="n">
+      <c r="H24" s="35" t="n">
         <v>17</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="K24" s="34" t="n">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="K24" s="35" t="n">
+        <v>6</v>
       </c>
       <c r="L24" s="30" t="n">
         <v>12</v>
       </c>
       <c r="M24" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" s="35" t="n">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="N24" s="31" t="n">
+        <v>-4</v>
       </c>
       <c r="O24" s="30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P24" s="30" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q24" s="31" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="R24" s="30" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S24" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="T24" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="U24" s="32" t="n">
-        <v>203</v>
-      </c>
-      <c r="V24" s="32" t="n">
-        <v>197</v>
+        <v>70</v>
+      </c>
+      <c r="T24" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="U24" s="33" t="n">
+        <v>212</v>
+      </c>
+      <c r="V24" s="33" t="n">
+        <v>206</v>
       </c>
       <c r="W24" s="36" t="n">
         <v>6</v>
@@ -2774,67 +2774,67 @@
         </is>
       </c>
       <c r="C25" s="30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E25" s="31" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>42</v>
-      </c>
-      <c r="H25" s="34" t="n">
-        <v>6</v>
+        <v>43</v>
+      </c>
+      <c r="H25" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="I25" s="30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="K25" s="34" t="n">
-        <v>15</v>
+      <c r="K25" s="35" t="n">
+        <v>19</v>
       </c>
       <c r="L25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="34" t="n">
-        <v>1</v>
+      <c r="N25" s="31" t="n">
+        <v>-1</v>
       </c>
       <c r="O25" s="30" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P25" s="30" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="Q25" s="31" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="R25" s="30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S25" s="30" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="T25" s="31" t="n">
-        <v>-18</v>
-      </c>
-      <c r="U25" s="32" t="n">
-        <v>142</v>
-      </c>
-      <c r="V25" s="32" t="n">
-        <v>171</v>
-      </c>
-      <c r="W25" s="33" t="n">
-        <v>-29</v>
+        <v>-26</v>
+      </c>
+      <c r="U25" s="33" t="n">
+        <v>152</v>
+      </c>
+      <c r="V25" s="33" t="n">
+        <v>194</v>
+      </c>
+      <c r="W25" s="34" t="n">
+        <v>-42</v>
       </c>
     </row>
     <row r="26">
@@ -2844,67 +2844,67 @@
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" s="31" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G26" s="30" t="n">
         <v>83</v>
       </c>
       <c r="H26" s="31" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>18</v>
-      </c>
-      <c r="K26" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="K26" s="35" t="n">
         <v>6</v>
       </c>
       <c r="L26" s="30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M26" s="30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N26" s="31" t="n">
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="O26" s="30" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="P26" s="30" t="n">
         <v>56</v>
       </c>
       <c r="Q26" s="31" t="n">
-        <v>-33</v>
+        <v>-28</v>
       </c>
       <c r="R26" s="30" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="S26" s="30" t="n">
-        <v>62</v>
-      </c>
-      <c r="T26" s="34" t="n">
-        <v>33</v>
-      </c>
-      <c r="U26" s="32" t="n">
-        <v>215</v>
-      </c>
-      <c r="V26" s="32" t="n">
-        <v>283</v>
-      </c>
-      <c r="W26" s="33" t="n">
-        <v>-68</v>
+        <v>61</v>
+      </c>
+      <c r="T26" s="35" t="n">
+        <v>41</v>
+      </c>
+      <c r="U26" s="33" t="n">
+        <v>235</v>
+      </c>
+      <c r="V26" s="33" t="n">
+        <v>282</v>
+      </c>
+      <c r="W26" s="34" t="n">
+        <v>-47</v>
       </c>
     </row>
     <row r="27">
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C27" s="30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D27" s="30" t="n">
         <v>42</v>
       </c>
       <c r="E27" s="31" t="n">
-        <v>-21</v>
+        <v>-18</v>
       </c>
       <c r="F27" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="30" t="n">
+        <v>69</v>
+      </c>
+      <c r="H27" s="31" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I27" s="30" t="n">
+        <v>51</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="K27" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="G27" s="30" t="n">
-        <v>68</v>
-      </c>
-      <c r="H27" s="31" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I27" s="30" t="n">
-        <v>52</v>
-      </c>
-      <c r="J27" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="K27" s="34" t="n">
-        <v>44</v>
-      </c>
       <c r="L27" s="30" t="n">
-        <v>15</v>
+        <v>-42</v>
       </c>
       <c r="M27" s="30" t="n">
         <v>24</v>
       </c>
       <c r="N27" s="31" t="n">
-        <v>-9</v>
+        <v>-66</v>
       </c>
       <c r="O27" s="30" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P27" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="Q27" s="34" t="n">
-        <v>22</v>
+      <c r="Q27" s="35" t="n">
+        <v>28</v>
       </c>
       <c r="R27" s="30" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="S27" s="30" t="n">
-        <v>89</v>
-      </c>
-      <c r="T27" s="34" t="n">
-        <v>121</v>
-      </c>
-      <c r="U27" s="32" t="n">
-        <v>400</v>
-      </c>
-      <c r="V27" s="32" t="n">
-        <v>271</v>
+        <v>88</v>
+      </c>
+      <c r="T27" s="35" t="n">
+        <v>130</v>
+      </c>
+      <c r="U27" s="33" t="n">
+        <v>354</v>
+      </c>
+      <c r="V27" s="33" t="n">
+        <v>274</v>
       </c>
       <c r="W27" s="36" t="n">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -2984,22 +2984,22 @@
         </is>
       </c>
       <c r="C28" s="30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E28" s="31" t="n">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H28" s="31" t="n">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="I28" s="30" t="n">
         <v>12</v>
@@ -3011,40 +3011,40 @@
         <v>-5</v>
       </c>
       <c r="L28" s="30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M28" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="N28" s="34" t="n">
-        <v>9</v>
+      <c r="N28" s="35" t="n">
+        <v>6</v>
       </c>
       <c r="O28" s="30" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="P28" s="30" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q28" s="34" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q28" s="35" t="n">
         <v>1</v>
       </c>
       <c r="R28" s="30" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="S28" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="T28" s="34" t="n">
-        <v>87</v>
-      </c>
-      <c r="U28" s="32" t="n">
-        <v>280</v>
-      </c>
-      <c r="V28" s="32" t="n">
-        <v>269</v>
+        <v>76</v>
+      </c>
+      <c r="T28" s="35" t="n">
+        <v>89</v>
+      </c>
+      <c r="U28" s="33" t="n">
+        <v>293</v>
+      </c>
+      <c r="V28" s="33" t="n">
+        <v>283</v>
       </c>
       <c r="W28" s="36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -3054,19 +3054,19 @@
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" s="30" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E29" s="31" t="n">
-        <v>-66</v>
+        <v>-63</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H29" s="31" t="n">
         <v>-54</v>
@@ -3081,40 +3081,40 @@
         <v>-6</v>
       </c>
       <c r="L29" s="30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M29" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="N29" s="34" t="n">
-        <v>5</v>
+      <c r="N29" s="35" t="n">
+        <v>8</v>
       </c>
       <c r="O29" s="30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P29" s="30" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q29" s="31" t="n">
         <v>-23</v>
       </c>
       <c r="R29" s="30" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S29" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="T29" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="U29" s="32" t="n">
-        <v>204</v>
-      </c>
-      <c r="V29" s="32" t="n">
-        <v>329</v>
-      </c>
-      <c r="W29" s="33" t="n">
-        <v>-125</v>
+        <v>90</v>
+      </c>
+      <c r="T29" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="U29" s="33" t="n">
+        <v>217</v>
+      </c>
+      <c r="V29" s="33" t="n">
+        <v>340</v>
+      </c>
+      <c r="W29" s="34" t="n">
+        <v>-123</v>
       </c>
     </row>
     <row r="30">
@@ -3124,67 +3124,67 @@
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30" s="31" t="n">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H30" s="31" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K30" s="31" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M30" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="N30" s="34" t="n">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="N30" s="35" t="n">
+        <v>14</v>
       </c>
       <c r="O30" s="30" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="P30" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="Q30" s="34" t="n">
-        <v>19</v>
+      <c r="Q30" s="35" t="n">
+        <v>32</v>
       </c>
       <c r="R30" s="30" t="n">
+        <v>61</v>
+      </c>
+      <c r="S30" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="S30" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="T30" s="31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U30" s="32" t="n">
-        <v>200</v>
-      </c>
-      <c r="V30" s="32" t="n">
-        <v>201</v>
-      </c>
-      <c r="W30" s="33" t="n">
-        <v>-1</v>
+      <c r="T30" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U30" s="33" t="n">
+        <v>228</v>
+      </c>
+      <c r="V30" s="33" t="n">
+        <v>202</v>
+      </c>
+      <c r="W30" s="36" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -3206,19 +3206,19 @@
         <v>26</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="H31" s="34" t="n">
-        <v>7</v>
+        <v>20</v>
+      </c>
+      <c r="H31" s="35" t="n">
+        <v>6</v>
       </c>
       <c r="I31" s="30" t="n">
         <v>5</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K31" s="31" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L31" s="30" t="n">
         <v>15</v>
@@ -3230,31 +3230,31 @@
         <v>-3</v>
       </c>
       <c r="O31" s="30" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P31" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q31" s="34" t="n">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="Q31" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="R31" s="30" t="n">
         <v>43</v>
       </c>
       <c r="S31" s="30" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T31" s="31" t="n">
-        <v>-8</v>
-      </c>
-      <c r="U31" s="32" t="n">
-        <v>128</v>
-      </c>
-      <c r="V31" s="32" t="n">
-        <v>146</v>
-      </c>
-      <c r="W31" s="33" t="n">
-        <v>-18</v>
+        <v>-10</v>
+      </c>
+      <c r="U31" s="33" t="n">
+        <v>131</v>
+      </c>
+      <c r="V31" s="33" t="n">
+        <v>152</v>
+      </c>
+      <c r="W31" s="34" t="n">
+        <v>-21</v>
       </c>
     </row>
     <row r="32">
@@ -3273,22 +3273,22 @@
         <v>-5</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G32" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="H32" s="34" t="n">
+      <c r="H32" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="I32" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" s="34" t="n">
-        <v>5</v>
+      <c r="K32" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="L32" s="30" t="n">
         <v>13</v>
@@ -3296,35 +3296,35 @@
       <c r="M32" s="30" t="n">
         <v>-1</v>
       </c>
-      <c r="N32" s="34" t="n">
+      <c r="N32" s="35" t="n">
         <v>14</v>
       </c>
       <c r="O32" s="30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P32" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q32" s="34" t="n">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="Q32" s="31" t="n">
+        <v>-5</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="S32" s="30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="T32" s="31" t="n">
-        <v>-30</v>
-      </c>
-      <c r="U32" s="32" t="n">
-        <v>88</v>
-      </c>
-      <c r="V32" s="32" t="n">
-        <v>95</v>
-      </c>
-      <c r="W32" s="33" t="n">
-        <v>-7</v>
+        <v>-26</v>
+      </c>
+      <c r="U32" s="33" t="n">
+        <v>94</v>
+      </c>
+      <c r="V32" s="33" t="n">
+        <v>108</v>
+      </c>
+      <c r="W32" s="34" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="33">
@@ -3334,67 +3334,67 @@
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" s="30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="31" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G33" s="30" t="n">
         <v>33</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J33" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="K33" s="34" t="n">
-        <v>6</v>
-      </c>
       <c r="L33" s="30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M33" s="30" t="n">
         <v>-4</v>
       </c>
-      <c r="N33" s="34" t="n">
-        <v>13</v>
+      <c r="N33" s="35" t="n">
+        <v>14</v>
       </c>
       <c r="O33" s="30" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="P33" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" s="34" t="n">
-        <v>45</v>
+      <c r="Q33" s="35" t="n">
+        <v>56</v>
       </c>
       <c r="R33" s="30" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="S33" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="T33" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U33" s="32" t="n">
-        <v>215</v>
-      </c>
-      <c r="V33" s="32" t="n">
-        <v>161</v>
+      <c r="T33" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="U33" s="33" t="n">
+        <v>247</v>
+      </c>
+      <c r="V33" s="33" t="n">
+        <v>164</v>
       </c>
       <c r="W33" s="36" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
@@ -3418,53 +3418,53 @@
       <c r="G34" s="30" t="n">
         <v>37</v>
       </c>
-      <c r="H34" s="34" t="n">
+      <c r="H34" s="35" t="n">
         <v>2</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K34" s="34" t="n">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="K34" s="35" t="n">
+        <v>13</v>
       </c>
       <c r="L34" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M34" s="30" t="n">
         <v>14</v>
       </c>
       <c r="N34" s="31" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O34" s="30" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P34" s="30" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q34" s="31" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="R34" s="30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="S34" s="30" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T34" s="31" t="n">
-        <v>-35</v>
-      </c>
-      <c r="U34" s="32" t="n">
-        <v>169</v>
-      </c>
-      <c r="V34" s="32" t="n">
-        <v>235</v>
-      </c>
-      <c r="W34" s="33" t="n">
-        <v>-66</v>
+        <v>-22</v>
+      </c>
+      <c r="U34" s="33" t="n">
+        <v>187</v>
+      </c>
+      <c r="V34" s="33" t="n">
+        <v>236</v>
+      </c>
+      <c r="W34" s="34" t="n">
+        <v>-49</v>
       </c>
     </row>
     <row r="35">
@@ -3477,28 +3477,28 @@
         <v>2</v>
       </c>
       <c r="D35" s="30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E35" s="31" t="n">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G35" s="30" t="n">
         <v>33</v>
       </c>
       <c r="H35" s="31" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>6</v>
       </c>
       <c r="K35" s="31" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L35" s="30" t="n">
         <v>1</v>
@@ -3510,31 +3510,31 @@
         <v>-2</v>
       </c>
       <c r="O35" s="30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P35" s="30" t="n">
         <v>26</v>
       </c>
       <c r="Q35" s="31" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="R35" s="30" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S35" s="30" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="T35" s="31" t="n">
-        <v>-6</v>
-      </c>
-      <c r="U35" s="32" t="n">
-        <v>81</v>
-      </c>
-      <c r="V35" s="32" t="n">
-        <v>125</v>
-      </c>
-      <c r="W35" s="33" t="n">
-        <v>-44</v>
+        <v>-5</v>
+      </c>
+      <c r="U35" s="33" t="n">
+        <v>82</v>
+      </c>
+      <c r="V35" s="33" t="n">
+        <v>132</v>
+      </c>
+      <c r="W35" s="34" t="n">
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
@@ -3765,67 +3765,67 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>1249</v>
+        <v>1364</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>1763</v>
+        <v>1821</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>-514</v>
+        <v>-457</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>2662</v>
+        <v>2799</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>3786</v>
+        <v>3902</v>
       </c>
       <c r="H6" s="31" t="n">
-        <v>-1124</v>
+        <v>-1103</v>
       </c>
       <c r="I6" s="30" t="n">
-        <v>1001</v>
+        <v>1064</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>808</v>
-      </c>
-      <c r="K6" s="34" t="n">
-        <v>193</v>
+        <v>832</v>
+      </c>
+      <c r="K6" s="35" t="n">
+        <v>232</v>
       </c>
       <c r="L6" s="30" t="n">
-        <v>732</v>
+        <v>1008</v>
       </c>
       <c r="M6" s="30" t="n">
-        <v>809</v>
-      </c>
-      <c r="N6" s="31" t="n">
-        <v>-77</v>
+        <v>845</v>
+      </c>
+      <c r="N6" s="35" t="n">
+        <v>163</v>
       </c>
       <c r="O6" s="30" t="n">
-        <v>2906</v>
+        <v>3065</v>
       </c>
       <c r="P6" s="30" t="n">
-        <v>3124</v>
+        <v>3228</v>
       </c>
       <c r="Q6" s="31" t="n">
-        <v>-218</v>
+        <v>-163</v>
       </c>
       <c r="R6" s="30" t="n">
-        <v>3910</v>
+        <v>4070</v>
       </c>
       <c r="S6" s="30" t="n">
-        <v>4633</v>
+        <v>4751</v>
       </c>
       <c r="T6" s="31" t="n">
-        <v>-723</v>
-      </c>
-      <c r="U6" s="32" t="n">
-        <v>12460</v>
-      </c>
-      <c r="V6" s="32" t="n">
-        <v>14923</v>
-      </c>
-      <c r="W6" s="33" t="n">
-        <v>-2463</v>
+        <v>-681</v>
+      </c>
+      <c r="U6" s="33" t="n">
+        <v>13370</v>
+      </c>
+      <c r="V6" s="33" t="n">
+        <v>15379</v>
+      </c>
+      <c r="W6" s="34" t="n">
+        <v>-2009</v>
       </c>
     </row>
     <row r="7">
@@ -3835,67 +3835,67 @@
         </is>
       </c>
       <c r="C7" s="30" t="n">
-        <v>1194</v>
+        <v>1306</v>
       </c>
       <c r="D7" s="30" t="n">
-        <v>1659</v>
+        <v>1711</v>
       </c>
       <c r="E7" s="31" t="n">
-        <v>-465</v>
+        <v>-405</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>2563</v>
+        <v>2695</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>3532</v>
+        <v>3659</v>
       </c>
       <c r="H7" s="31" t="n">
-        <v>-969</v>
+        <v>-964</v>
       </c>
       <c r="I7" s="30" t="n">
-        <v>939</v>
+        <v>995</v>
       </c>
       <c r="J7" s="30" t="n">
-        <v>742</v>
-      </c>
-      <c r="K7" s="34" t="n">
-        <v>197</v>
+        <v>763</v>
+      </c>
+      <c r="K7" s="35" t="n">
+        <v>232</v>
       </c>
       <c r="L7" s="30" t="n">
-        <v>701</v>
+        <v>971</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>746</v>
-      </c>
-      <c r="N7" s="31" t="n">
-        <v>-45</v>
+        <v>778</v>
+      </c>
+      <c r="N7" s="35" t="n">
+        <v>193</v>
       </c>
       <c r="O7" s="30" t="n">
-        <v>2853</v>
+        <v>3017</v>
       </c>
       <c r="P7" s="30" t="n">
-        <v>2992</v>
+        <v>3101</v>
       </c>
       <c r="Q7" s="31" t="n">
-        <v>-139</v>
+        <v>-84</v>
       </c>
       <c r="R7" s="30" t="n">
-        <v>3857</v>
+        <v>4012</v>
       </c>
       <c r="S7" s="30" t="n">
-        <v>4491</v>
+        <v>4604</v>
       </c>
       <c r="T7" s="31" t="n">
-        <v>-634</v>
-      </c>
-      <c r="U7" s="32" t="n">
-        <v>12107</v>
-      </c>
-      <c r="V7" s="32" t="n">
-        <v>14162</v>
-      </c>
-      <c r="W7" s="33" t="n">
-        <v>-2055</v>
+        <v>-592</v>
+      </c>
+      <c r="U7" s="33" t="n">
+        <v>12996</v>
+      </c>
+      <c r="V7" s="33" t="n">
+        <v>14616</v>
+      </c>
+      <c r="W7" s="34" t="n">
+        <v>-1620</v>
       </c>
     </row>
     <row r="8">
@@ -3905,67 +3905,67 @@
         </is>
       </c>
       <c r="C8" s="30" t="n">
-        <v>1030</v>
+        <v>1139</v>
       </c>
       <c r="D8" s="30" t="n">
-        <v>1576</v>
+        <v>1630</v>
       </c>
       <c r="E8" s="31" t="n">
-        <v>-546</v>
+        <v>-491</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>2460</v>
+        <v>2590</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>3286</v>
+        <v>3412</v>
       </c>
       <c r="H8" s="31" t="n">
-        <v>-826</v>
+        <v>-822</v>
       </c>
       <c r="I8" s="30" t="n">
-        <v>900</v>
+        <v>955</v>
       </c>
       <c r="J8" s="30" t="n">
-        <v>675</v>
-      </c>
-      <c r="K8" s="34" t="n">
-        <v>225</v>
+        <v>699</v>
+      </c>
+      <c r="K8" s="35" t="n">
+        <v>256</v>
       </c>
       <c r="L8" s="30" t="n">
-        <v>667</v>
+        <v>943</v>
       </c>
       <c r="M8" s="30" t="n">
-        <v>702</v>
-      </c>
-      <c r="N8" s="31" t="n">
-        <v>-35</v>
+        <v>736</v>
+      </c>
+      <c r="N8" s="35" t="n">
+        <v>207</v>
       </c>
       <c r="O8" s="30" t="n">
-        <v>2790</v>
+        <v>2951</v>
       </c>
       <c r="P8" s="30" t="n">
-        <v>2842</v>
-      </c>
-      <c r="Q8" s="31" t="n">
-        <v>-52</v>
+        <v>2951</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="R8" s="30" t="n">
-        <v>3820</v>
+        <v>3983</v>
       </c>
       <c r="S8" s="30" t="n">
-        <v>4343</v>
+        <v>4455</v>
       </c>
       <c r="T8" s="31" t="n">
-        <v>-523</v>
-      </c>
-      <c r="U8" s="32" t="n">
-        <v>11667</v>
-      </c>
-      <c r="V8" s="32" t="n">
-        <v>13424</v>
-      </c>
-      <c r="W8" s="33" t="n">
-        <v>-1757</v>
+        <v>-472</v>
+      </c>
+      <c r="U8" s="33" t="n">
+        <v>12561</v>
+      </c>
+      <c r="V8" s="33" t="n">
+        <v>13883</v>
+      </c>
+      <c r="W8" s="34" t="n">
+        <v>-1322</v>
       </c>
     </row>
     <row r="9">
@@ -3975,67 +3975,67 @@
         </is>
       </c>
       <c r="C9" s="30" t="n">
-        <v>955</v>
+        <v>1061</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>1496</v>
+        <v>1552</v>
       </c>
       <c r="E9" s="31" t="n">
-        <v>-541</v>
+        <v>-491</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>2358</v>
+        <v>2481</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>2956</v>
+        <v>3069</v>
       </c>
       <c r="H9" s="31" t="n">
-        <v>-598</v>
+        <v>-588</v>
       </c>
       <c r="I9" s="30" t="n">
-        <v>843</v>
+        <v>896</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>631</v>
-      </c>
-      <c r="K9" s="34" t="n">
-        <v>212</v>
+        <v>650</v>
+      </c>
+      <c r="K9" s="35" t="n">
+        <v>246</v>
       </c>
       <c r="L9" s="30" t="n">
-        <v>667</v>
+        <v>945</v>
       </c>
       <c r="M9" s="30" t="n">
-        <v>664</v>
-      </c>
-      <c r="N9" s="34" t="n">
-        <v>3</v>
+        <v>692</v>
+      </c>
+      <c r="N9" s="35" t="n">
+        <v>253</v>
       </c>
       <c r="O9" s="30" t="n">
-        <v>2693</v>
+        <v>2850</v>
       </c>
       <c r="P9" s="30" t="n">
-        <v>2723</v>
-      </c>
-      <c r="Q9" s="31" t="n">
-        <v>-30</v>
+        <v>2823</v>
+      </c>
+      <c r="Q9" s="35" t="n">
+        <v>27</v>
       </c>
       <c r="R9" s="30" t="n">
-        <v>3701</v>
+        <v>3852</v>
       </c>
       <c r="S9" s="30" t="n">
-        <v>4137</v>
+        <v>4249</v>
       </c>
       <c r="T9" s="31" t="n">
-        <v>-436</v>
-      </c>
-      <c r="U9" s="32" t="n">
-        <v>11217</v>
-      </c>
-      <c r="V9" s="32" t="n">
-        <v>12607</v>
-      </c>
-      <c r="W9" s="33" t="n">
-        <v>-1390</v>
+        <v>-397</v>
+      </c>
+      <c r="U9" s="33" t="n">
+        <v>12085</v>
+      </c>
+      <c r="V9" s="33" t="n">
+        <v>13035</v>
+      </c>
+      <c r="W9" s="34" t="n">
+        <v>-950</v>
       </c>
     </row>
     <row r="10">
@@ -4045,67 +4045,67 @@
         </is>
       </c>
       <c r="C10" s="30" t="n">
-        <v>893</v>
+        <v>999</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>1438</v>
+        <v>1498</v>
       </c>
       <c r="E10" s="31" t="n">
-        <v>-545</v>
+        <v>-499</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>2222</v>
+        <v>2335</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>2818</v>
+        <v>2921</v>
       </c>
       <c r="H10" s="31" t="n">
-        <v>-596</v>
+        <v>-586</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>774</v>
+        <v>826</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>601</v>
-      </c>
-      <c r="K10" s="34" t="n">
-        <v>173</v>
+        <v>619</v>
+      </c>
+      <c r="K10" s="35" t="n">
+        <v>207</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>642</v>
+        <v>920</v>
       </c>
       <c r="M10" s="30" t="n">
-        <v>625</v>
-      </c>
-      <c r="N10" s="34" t="n">
-        <v>17</v>
+        <v>655</v>
+      </c>
+      <c r="N10" s="35" t="n">
+        <v>265</v>
       </c>
       <c r="O10" s="30" t="n">
-        <v>2618</v>
+        <v>2774</v>
       </c>
       <c r="P10" s="30" t="n">
-        <v>2641</v>
-      </c>
-      <c r="Q10" s="31" t="n">
-        <v>-23</v>
+        <v>2741</v>
+      </c>
+      <c r="Q10" s="35" t="n">
+        <v>33</v>
       </c>
       <c r="R10" s="30" t="n">
-        <v>3608</v>
+        <v>3752</v>
       </c>
       <c r="S10" s="30" t="n">
-        <v>4016</v>
+        <v>4120</v>
       </c>
       <c r="T10" s="31" t="n">
-        <v>-408</v>
-      </c>
-      <c r="U10" s="32" t="n">
-        <v>10757</v>
-      </c>
-      <c r="V10" s="32" t="n">
-        <v>12139</v>
-      </c>
-      <c r="W10" s="33" t="n">
-        <v>-1382</v>
+        <v>-368</v>
+      </c>
+      <c r="U10" s="33" t="n">
+        <v>11606</v>
+      </c>
+      <c r="V10" s="33" t="n">
+        <v>12554</v>
+      </c>
+      <c r="W10" s="34" t="n">
+        <v>-948</v>
       </c>
     </row>
     <row r="11">
@@ -4115,67 +4115,67 @@
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>862</v>
+        <v>964</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>1414</v>
+        <v>1470</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>-552</v>
+        <v>-506</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>2149</v>
+        <v>2260</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>2745</v>
+        <v>2838</v>
       </c>
       <c r="H11" s="31" t="n">
-        <v>-596</v>
+        <v>-578</v>
       </c>
       <c r="I11" s="30" t="n">
-        <v>756</v>
+        <v>806</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>579</v>
-      </c>
-      <c r="K11" s="34" t="n">
-        <v>177</v>
+        <v>596</v>
+      </c>
+      <c r="K11" s="35" t="n">
+        <v>210</v>
       </c>
       <c r="L11" s="30" t="n">
-        <v>636</v>
+        <v>915</v>
       </c>
       <c r="M11" s="30" t="n">
-        <v>603</v>
-      </c>
-      <c r="N11" s="34" t="n">
-        <v>33</v>
+        <v>635</v>
+      </c>
+      <c r="N11" s="35" t="n">
+        <v>280</v>
       </c>
       <c r="O11" s="30" t="n">
-        <v>2576</v>
+        <v>2726</v>
       </c>
       <c r="P11" s="30" t="n">
-        <v>2573</v>
-      </c>
-      <c r="Q11" s="34" t="n">
-        <v>3</v>
+        <v>2672</v>
+      </c>
+      <c r="Q11" s="35" t="n">
+        <v>54</v>
       </c>
       <c r="R11" s="30" t="n">
-        <v>3555</v>
+        <v>3700</v>
       </c>
       <c r="S11" s="30" t="n">
-        <v>3917</v>
+        <v>4023</v>
       </c>
       <c r="T11" s="31" t="n">
-        <v>-362</v>
-      </c>
-      <c r="U11" s="32" t="n">
-        <v>10534</v>
-      </c>
-      <c r="V11" s="32" t="n">
-        <v>11831</v>
-      </c>
-      <c r="W11" s="33" t="n">
-        <v>-1297</v>
+        <v>-323</v>
+      </c>
+      <c r="U11" s="33" t="n">
+        <v>11371</v>
+      </c>
+      <c r="V11" s="33" t="n">
+        <v>12234</v>
+      </c>
+      <c r="W11" s="34" t="n">
+        <v>-863</v>
       </c>
     </row>
     <row r="12">
@@ -4185,67 +4185,67 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>841</v>
+        <v>938</v>
       </c>
       <c r="D12" s="30" t="n">
-        <v>1372</v>
+        <v>1429</v>
       </c>
       <c r="E12" s="31" t="n">
-        <v>-531</v>
+        <v>-491</v>
       </c>
       <c r="F12" s="30" t="n">
-        <v>2106</v>
+        <v>2212</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>2614</v>
+        <v>2705</v>
       </c>
       <c r="H12" s="31" t="n">
-        <v>-508</v>
+        <v>-493</v>
       </c>
       <c r="I12" s="30" t="n">
-        <v>724</v>
+        <v>774</v>
       </c>
       <c r="J12" s="30" t="n">
-        <v>543</v>
-      </c>
-      <c r="K12" s="34" t="n">
-        <v>181</v>
+        <v>561</v>
+      </c>
+      <c r="K12" s="35" t="n">
+        <v>213</v>
       </c>
       <c r="L12" s="30" t="n">
-        <v>601</v>
+        <v>879</v>
       </c>
       <c r="M12" s="30" t="n">
-        <v>598</v>
-      </c>
-      <c r="N12" s="34" t="n">
-        <v>3</v>
+        <v>626</v>
+      </c>
+      <c r="N12" s="35" t="n">
+        <v>253</v>
       </c>
       <c r="O12" s="30" t="n">
-        <v>2531</v>
+        <v>2678</v>
       </c>
       <c r="P12" s="30" t="n">
-        <v>2487</v>
-      </c>
-      <c r="Q12" s="34" t="n">
-        <v>44</v>
+        <v>2587</v>
+      </c>
+      <c r="Q12" s="35" t="n">
+        <v>91</v>
       </c>
       <c r="R12" s="30" t="n">
-        <v>3489</v>
+        <v>3632</v>
       </c>
       <c r="S12" s="30" t="n">
-        <v>3837</v>
+        <v>3944</v>
       </c>
       <c r="T12" s="31" t="n">
-        <v>-348</v>
-      </c>
-      <c r="U12" s="32" t="n">
-        <v>10292</v>
-      </c>
-      <c r="V12" s="32" t="n">
-        <v>11451</v>
-      </c>
-      <c r="W12" s="33" t="n">
-        <v>-1159</v>
+        <v>-312</v>
+      </c>
+      <c r="U12" s="33" t="n">
+        <v>11113</v>
+      </c>
+      <c r="V12" s="33" t="n">
+        <v>11852</v>
+      </c>
+      <c r="W12" s="34" t="n">
+        <v>-739</v>
       </c>
     </row>
     <row r="13">
@@ -4255,67 +4255,67 @@
         </is>
       </c>
       <c r="C13" s="30" t="n">
-        <v>811</v>
+        <v>901</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1326</v>
+        <v>1378</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>-515</v>
+        <v>-477</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>2074</v>
+        <v>2178</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>2533</v>
+        <v>2614</v>
       </c>
       <c r="H13" s="31" t="n">
-        <v>-459</v>
+        <v>-436</v>
       </c>
       <c r="I13" s="30" t="n">
-        <v>697</v>
+        <v>748</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>513</v>
-      </c>
-      <c r="K13" s="34" t="n">
-        <v>184</v>
+        <v>531</v>
+      </c>
+      <c r="K13" s="35" t="n">
+        <v>217</v>
       </c>
       <c r="L13" s="30" t="n">
-        <v>564</v>
+        <v>845</v>
       </c>
       <c r="M13" s="30" t="n">
-        <v>559</v>
-      </c>
-      <c r="N13" s="34" t="n">
-        <v>5</v>
+        <v>585</v>
+      </c>
+      <c r="N13" s="35" t="n">
+        <v>260</v>
       </c>
       <c r="O13" s="30" t="n">
-        <v>2481</v>
+        <v>2625</v>
       </c>
       <c r="P13" s="30" t="n">
-        <v>2440</v>
-      </c>
-      <c r="Q13" s="34" t="n">
-        <v>41</v>
+        <v>2536</v>
+      </c>
+      <c r="Q13" s="35" t="n">
+        <v>89</v>
       </c>
       <c r="R13" s="30" t="n">
-        <v>3432</v>
+        <v>3576</v>
       </c>
       <c r="S13" s="30" t="n">
-        <v>3721</v>
+        <v>3823</v>
       </c>
       <c r="T13" s="31" t="n">
-        <v>-289</v>
-      </c>
-      <c r="U13" s="32" t="n">
-        <v>10059</v>
-      </c>
-      <c r="V13" s="32" t="n">
-        <v>11092</v>
-      </c>
-      <c r="W13" s="33" t="n">
-        <v>-1033</v>
+        <v>-247</v>
+      </c>
+      <c r="U13" s="33" t="n">
+        <v>10873</v>
+      </c>
+      <c r="V13" s="33" t="n">
+        <v>11467</v>
+      </c>
+      <c r="W13" s="34" t="n">
+        <v>-594</v>
       </c>
     </row>
     <row r="14">
@@ -4325,67 +4325,67 @@
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>1267</v>
+        <v>1318</v>
       </c>
       <c r="E14" s="31" t="n">
-        <v>-506</v>
+        <v>-471</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>2001</v>
+        <v>2100</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>2379</v>
+        <v>2450</v>
       </c>
       <c r="H14" s="31" t="n">
-        <v>-378</v>
+        <v>-350</v>
       </c>
       <c r="I14" s="30" t="n">
-        <v>670</v>
+        <v>719</v>
       </c>
       <c r="J14" s="30" t="n">
-        <v>499</v>
-      </c>
-      <c r="K14" s="34" t="n">
-        <v>171</v>
+        <v>516</v>
+      </c>
+      <c r="K14" s="35" t="n">
+        <v>203</v>
       </c>
       <c r="L14" s="30" t="n">
-        <v>551</v>
+        <v>830</v>
       </c>
       <c r="M14" s="30" t="n">
-        <v>523</v>
-      </c>
-      <c r="N14" s="34" t="n">
-        <v>28</v>
+        <v>548</v>
+      </c>
+      <c r="N14" s="35" t="n">
+        <v>282</v>
       </c>
       <c r="O14" s="30" t="n">
-        <v>2415</v>
+        <v>2553</v>
       </c>
       <c r="P14" s="30" t="n">
-        <v>2365</v>
-      </c>
-      <c r="Q14" s="34" t="n">
-        <v>50</v>
+        <v>2459</v>
+      </c>
+      <c r="Q14" s="35" t="n">
+        <v>94</v>
       </c>
       <c r="R14" s="30" t="n">
-        <v>3382</v>
+        <v>3525</v>
       </c>
       <c r="S14" s="30" t="n">
-        <v>3641</v>
+        <v>3743</v>
       </c>
       <c r="T14" s="31" t="n">
-        <v>-259</v>
-      </c>
-      <c r="U14" s="32" t="n">
-        <v>9780</v>
-      </c>
-      <c r="V14" s="32" t="n">
-        <v>10674</v>
-      </c>
-      <c r="W14" s="33" t="n">
-        <v>-894</v>
+        <v>-218</v>
+      </c>
+      <c r="U14" s="33" t="n">
+        <v>10574</v>
+      </c>
+      <c r="V14" s="33" t="n">
+        <v>11034</v>
+      </c>
+      <c r="W14" s="34" t="n">
+        <v>-460</v>
       </c>
     </row>
     <row r="15">
@@ -4395,67 +4395,67 @@
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>713</v>
+        <v>794</v>
       </c>
       <c r="D15" s="30" t="n">
-        <v>1185</v>
+        <v>1236</v>
       </c>
       <c r="E15" s="31" t="n">
-        <v>-472</v>
+        <v>-442</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>1957</v>
+        <v>2052</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>2254</v>
+        <v>2326</v>
       </c>
       <c r="H15" s="31" t="n">
-        <v>-297</v>
+        <v>-274</v>
       </c>
       <c r="I15" s="30" t="n">
-        <v>643</v>
+        <v>686</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>472</v>
-      </c>
-      <c r="K15" s="34" t="n">
-        <v>171</v>
+        <v>489</v>
+      </c>
+      <c r="K15" s="35" t="n">
+        <v>197</v>
       </c>
       <c r="L15" s="30" t="n">
-        <v>482</v>
+        <v>756</v>
       </c>
       <c r="M15" s="30" t="n">
-        <v>467</v>
-      </c>
-      <c r="N15" s="34" t="n">
-        <v>15</v>
+        <v>491</v>
+      </c>
+      <c r="N15" s="35" t="n">
+        <v>265</v>
       </c>
       <c r="O15" s="30" t="n">
-        <v>2323</v>
+        <v>2449</v>
       </c>
       <c r="P15" s="30" t="n">
-        <v>2299</v>
-      </c>
-      <c r="Q15" s="34" t="n">
-        <v>24</v>
+        <v>2390</v>
+      </c>
+      <c r="Q15" s="35" t="n">
+        <v>59</v>
       </c>
       <c r="R15" s="30" t="n">
-        <v>3266</v>
+        <v>3408</v>
       </c>
       <c r="S15" s="30" t="n">
-        <v>3445</v>
+        <v>3539</v>
       </c>
       <c r="T15" s="31" t="n">
-        <v>-179</v>
-      </c>
-      <c r="U15" s="32" t="n">
-        <v>9384</v>
-      </c>
-      <c r="V15" s="32" t="n">
-        <v>10122</v>
-      </c>
-      <c r="W15" s="33" t="n">
-        <v>-738</v>
+        <v>-131</v>
+      </c>
+      <c r="U15" s="33" t="n">
+        <v>10145</v>
+      </c>
+      <c r="V15" s="33" t="n">
+        <v>10471</v>
+      </c>
+      <c r="W15" s="34" t="n">
+        <v>-326</v>
       </c>
     </row>
     <row r="16">
@@ -4465,67 +4465,67 @@
         </is>
       </c>
       <c r="C16" s="30" t="n">
-        <v>634</v>
+        <v>706</v>
       </c>
       <c r="D16" s="30" t="n">
-        <v>1118</v>
+        <v>1172</v>
       </c>
       <c r="E16" s="31" t="n">
-        <v>-484</v>
+        <v>-466</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>1884</v>
+        <v>1981</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>2155</v>
+        <v>2218</v>
       </c>
       <c r="H16" s="31" t="n">
-        <v>-271</v>
+        <v>-237</v>
       </c>
       <c r="I16" s="30" t="n">
-        <v>601</v>
+        <v>640</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>448</v>
-      </c>
-      <c r="K16" s="34" t="n">
-        <v>153</v>
+        <v>461</v>
+      </c>
+      <c r="K16" s="35" t="n">
+        <v>179</v>
       </c>
       <c r="L16" s="30" t="n">
-        <v>501</v>
+        <v>775</v>
       </c>
       <c r="M16" s="30" t="n">
-        <v>429</v>
-      </c>
-      <c r="N16" s="34" t="n">
-        <v>72</v>
+        <v>450</v>
+      </c>
+      <c r="N16" s="35" t="n">
+        <v>325</v>
       </c>
       <c r="O16" s="30" t="n">
-        <v>2289</v>
+        <v>2410</v>
       </c>
       <c r="P16" s="30" t="n">
-        <v>2213</v>
-      </c>
-      <c r="Q16" s="34" t="n">
-        <v>76</v>
+        <v>2303</v>
+      </c>
+      <c r="Q16" s="35" t="n">
+        <v>107</v>
       </c>
       <c r="R16" s="30" t="n">
-        <v>3096</v>
+        <v>3239</v>
       </c>
       <c r="S16" s="30" t="n">
-        <v>3293</v>
+        <v>3385</v>
       </c>
       <c r="T16" s="31" t="n">
-        <v>-197</v>
-      </c>
-      <c r="U16" s="32" t="n">
-        <v>9005</v>
-      </c>
-      <c r="V16" s="32" t="n">
-        <v>9656</v>
-      </c>
-      <c r="W16" s="33" t="n">
-        <v>-651</v>
+        <v>-146</v>
+      </c>
+      <c r="U16" s="33" t="n">
+        <v>9751</v>
+      </c>
+      <c r="V16" s="33" t="n">
+        <v>9989</v>
+      </c>
+      <c r="W16" s="34" t="n">
+        <v>-238</v>
       </c>
     </row>
     <row r="17">
@@ -4535,67 +4535,67 @@
         </is>
       </c>
       <c r="C17" s="30" t="n">
-        <v>576</v>
+        <v>641</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>1076</v>
+        <v>1130</v>
       </c>
       <c r="E17" s="31" t="n">
-        <v>-500</v>
+        <v>-489</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>1755</v>
+        <v>1845</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>2075</v>
+        <v>2139</v>
       </c>
       <c r="H17" s="31" t="n">
-        <v>-320</v>
+        <v>-294</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>563</v>
+        <v>602</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>421</v>
-      </c>
-      <c r="K17" s="34" t="n">
-        <v>142</v>
+        <v>433</v>
+      </c>
+      <c r="K17" s="35" t="n">
+        <v>169</v>
       </c>
       <c r="L17" s="30" t="n">
-        <v>484</v>
+        <v>750</v>
       </c>
       <c r="M17" s="30" t="n">
-        <v>416</v>
-      </c>
-      <c r="N17" s="34" t="n">
-        <v>68</v>
+        <v>437</v>
+      </c>
+      <c r="N17" s="35" t="n">
+        <v>313</v>
       </c>
       <c r="O17" s="30" t="n">
-        <v>2206</v>
+        <v>2328</v>
       </c>
       <c r="P17" s="30" t="n">
-        <v>2144</v>
-      </c>
-      <c r="Q17" s="34" t="n">
-        <v>62</v>
+        <v>2234</v>
+      </c>
+      <c r="Q17" s="35" t="n">
+        <v>94</v>
       </c>
       <c r="R17" s="30" t="n">
-        <v>2956</v>
+        <v>3097</v>
       </c>
       <c r="S17" s="30" t="n">
-        <v>3191</v>
+        <v>3275</v>
       </c>
       <c r="T17" s="31" t="n">
-        <v>-235</v>
-      </c>
-      <c r="U17" s="32" t="n">
-        <v>8540</v>
-      </c>
-      <c r="V17" s="32" t="n">
-        <v>9323</v>
-      </c>
-      <c r="W17" s="33" t="n">
-        <v>-783</v>
+        <v>-178</v>
+      </c>
+      <c r="U17" s="33" t="n">
+        <v>9263</v>
+      </c>
+      <c r="V17" s="33" t="n">
+        <v>9648</v>
+      </c>
+      <c r="W17" s="34" t="n">
+        <v>-385</v>
       </c>
     </row>
     <row r="18">
@@ -4605,67 +4605,67 @@
         </is>
       </c>
       <c r="C18" s="30" t="n">
-        <v>535</v>
+        <v>585</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>1032</v>
+        <v>1084</v>
       </c>
       <c r="E18" s="31" t="n">
-        <v>-497</v>
+        <v>-499</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>1721</v>
+        <v>1808</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>2032</v>
+        <v>2094</v>
       </c>
       <c r="H18" s="31" t="n">
-        <v>-311</v>
+        <v>-286</v>
       </c>
       <c r="I18" s="30" t="n">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="J18" s="30" t="n">
-        <v>404</v>
-      </c>
-      <c r="K18" s="34" t="n">
-        <v>108</v>
+        <v>416</v>
+      </c>
+      <c r="K18" s="35" t="n">
+        <v>132</v>
       </c>
       <c r="L18" s="30" t="n">
-        <v>473</v>
+        <v>736</v>
       </c>
       <c r="M18" s="30" t="n">
-        <v>412</v>
-      </c>
-      <c r="N18" s="34" t="n">
-        <v>61</v>
+        <v>433</v>
+      </c>
+      <c r="N18" s="35" t="n">
+        <v>303</v>
       </c>
       <c r="O18" s="30" t="n">
-        <v>2164</v>
+        <v>2288</v>
       </c>
       <c r="P18" s="30" t="n">
-        <v>2088</v>
-      </c>
-      <c r="Q18" s="34" t="n">
-        <v>76</v>
+        <v>2176</v>
+      </c>
+      <c r="Q18" s="35" t="n">
+        <v>112</v>
       </c>
       <c r="R18" s="30" t="n">
-        <v>2913</v>
+        <v>3052</v>
       </c>
       <c r="S18" s="30" t="n">
-        <v>3094</v>
+        <v>3176</v>
       </c>
       <c r="T18" s="31" t="n">
-        <v>-181</v>
-      </c>
-      <c r="U18" s="32" t="n">
-        <v>8318</v>
-      </c>
-      <c r="V18" s="32" t="n">
-        <v>9062</v>
-      </c>
-      <c r="W18" s="33" t="n">
-        <v>-744</v>
+        <v>-124</v>
+      </c>
+      <c r="U18" s="33" t="n">
+        <v>9017</v>
+      </c>
+      <c r="V18" s="33" t="n">
+        <v>9379</v>
+      </c>
+      <c r="W18" s="34" t="n">
+        <v>-362</v>
       </c>
     </row>
     <row r="19">
@@ -4675,67 +4675,67 @@
         </is>
       </c>
       <c r="C19" s="30" t="n">
-        <v>513</v>
+        <v>563</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>974</v>
+        <v>1024</v>
       </c>
       <c r="E19" s="31" t="n">
         <v>-461</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>1682</v>
+        <v>1765</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>1986</v>
+        <v>2049</v>
       </c>
       <c r="H19" s="31" t="n">
-        <v>-304</v>
+        <v>-284</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="J19" s="30" t="n">
-        <v>380</v>
-      </c>
-      <c r="K19" s="34" t="n">
-        <v>112</v>
+        <v>391</v>
+      </c>
+      <c r="K19" s="35" t="n">
+        <v>136</v>
       </c>
       <c r="L19" s="30" t="n">
-        <v>445</v>
+        <v>712</v>
       </c>
       <c r="M19" s="30" t="n">
-        <v>385</v>
-      </c>
-      <c r="N19" s="34" t="n">
-        <v>60</v>
+        <v>407</v>
+      </c>
+      <c r="N19" s="35" t="n">
+        <v>305</v>
       </c>
       <c r="O19" s="30" t="n">
-        <v>2117</v>
+        <v>2239</v>
       </c>
       <c r="P19" s="30" t="n">
-        <v>2004</v>
-      </c>
-      <c r="Q19" s="34" t="n">
-        <v>113</v>
+        <v>2092</v>
+      </c>
+      <c r="Q19" s="35" t="n">
+        <v>147</v>
       </c>
       <c r="R19" s="30" t="n">
-        <v>2832</v>
+        <v>2971</v>
       </c>
       <c r="S19" s="30" t="n">
-        <v>2829</v>
-      </c>
-      <c r="T19" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" s="32" t="n">
-        <v>8081</v>
-      </c>
-      <c r="V19" s="32" t="n">
-        <v>8558</v>
-      </c>
-      <c r="W19" s="33" t="n">
-        <v>-477</v>
+        <v>2907</v>
+      </c>
+      <c r="T19" s="35" t="n">
+        <v>64</v>
+      </c>
+      <c r="U19" s="33" t="n">
+        <v>8777</v>
+      </c>
+      <c r="V19" s="33" t="n">
+        <v>8870</v>
+      </c>
+      <c r="W19" s="34" t="n">
+        <v>-93</v>
       </c>
     </row>
     <row r="20">
@@ -4745,67 +4745,67 @@
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>493</v>
+        <v>533</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>938</v>
+        <v>986</v>
       </c>
       <c r="E20" s="31" t="n">
-        <v>-445</v>
+        <v>-453</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>1638</v>
+        <v>1717</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>1935</v>
+        <v>1996</v>
       </c>
       <c r="H20" s="31" t="n">
-        <v>-297</v>
+        <v>-279</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>363</v>
-      </c>
-      <c r="K20" s="34" t="n">
-        <v>85</v>
+        <v>374</v>
+      </c>
+      <c r="K20" s="35" t="n">
+        <v>111</v>
       </c>
       <c r="L20" s="30" t="n">
-        <v>452</v>
+        <v>711</v>
       </c>
       <c r="M20" s="30" t="n">
-        <v>366</v>
-      </c>
-      <c r="N20" s="34" t="n">
-        <v>86</v>
+        <v>389</v>
+      </c>
+      <c r="N20" s="35" t="n">
+        <v>322</v>
       </c>
       <c r="O20" s="30" t="n">
-        <v>2079</v>
+        <v>2198</v>
       </c>
       <c r="P20" s="30" t="n">
-        <v>1926</v>
-      </c>
-      <c r="Q20" s="34" t="n">
-        <v>153</v>
+        <v>2016</v>
+      </c>
+      <c r="Q20" s="35" t="n">
+        <v>182</v>
       </c>
       <c r="R20" s="30" t="n">
-        <v>2774</v>
+        <v>2910</v>
       </c>
       <c r="S20" s="30" t="n">
-        <v>2725</v>
-      </c>
-      <c r="T20" s="34" t="n">
-        <v>49</v>
-      </c>
-      <c r="U20" s="32" t="n">
-        <v>7884</v>
-      </c>
-      <c r="V20" s="32" t="n">
-        <v>8253</v>
-      </c>
-      <c r="W20" s="33" t="n">
-        <v>-369</v>
+        <v>2805</v>
+      </c>
+      <c r="T20" s="35" t="n">
+        <v>105</v>
+      </c>
+      <c r="U20" s="33" t="n">
+        <v>8554</v>
+      </c>
+      <c r="V20" s="33" t="n">
+        <v>8566</v>
+      </c>
+      <c r="W20" s="34" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="21">
@@ -4815,67 +4815,67 @@
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>907</v>
+        <v>951</v>
       </c>
       <c r="E21" s="31" t="n">
-        <v>-424</v>
+        <v>-431</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>1596</v>
+        <v>1664</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1896</v>
+        <v>1946</v>
       </c>
       <c r="H21" s="31" t="n">
-        <v>-300</v>
+        <v>-282</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>319</v>
-      </c>
-      <c r="K21" s="34" t="n">
-        <v>85</v>
+        <v>332</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <v>104</v>
       </c>
       <c r="L21" s="30" t="n">
-        <v>452</v>
+        <v>710</v>
       </c>
       <c r="M21" s="30" t="n">
-        <v>355</v>
-      </c>
-      <c r="N21" s="34" t="n">
-        <v>97</v>
+        <v>381</v>
+      </c>
+      <c r="N21" s="35" t="n">
+        <v>329</v>
       </c>
       <c r="O21" s="30" t="n">
-        <v>1784</v>
+        <v>1902</v>
       </c>
       <c r="P21" s="30" t="n">
-        <v>1856</v>
+        <v>1940</v>
       </c>
       <c r="Q21" s="31" t="n">
-        <v>-72</v>
+        <v>-38</v>
       </c>
       <c r="R21" s="30" t="n">
-        <v>2672</v>
+        <v>2798</v>
       </c>
       <c r="S21" s="30" t="n">
-        <v>2625</v>
-      </c>
-      <c r="T21" s="34" t="n">
-        <v>47</v>
-      </c>
-      <c r="U21" s="32" t="n">
-        <v>7391</v>
-      </c>
-      <c r="V21" s="32" t="n">
-        <v>7958</v>
-      </c>
-      <c r="W21" s="33" t="n">
-        <v>-567</v>
+        <v>2699</v>
+      </c>
+      <c r="T21" s="35" t="n">
+        <v>99</v>
+      </c>
+      <c r="U21" s="33" t="n">
+        <v>8030</v>
+      </c>
+      <c r="V21" s="33" t="n">
+        <v>8249</v>
+      </c>
+      <c r="W21" s="34" t="n">
+        <v>-219</v>
       </c>
     </row>
     <row r="22">
@@ -4885,67 +4885,67 @@
         </is>
       </c>
       <c r="C22" s="30" t="n">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>856</v>
+        <v>897</v>
       </c>
       <c r="E22" s="31" t="n">
-        <v>-400</v>
+        <v>-404</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>1551</v>
+        <v>1624</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>1759</v>
+        <v>1805</v>
       </c>
       <c r="H22" s="31" t="n">
-        <v>-208</v>
+        <v>-181</v>
       </c>
       <c r="I22" s="30" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>318</v>
-      </c>
-      <c r="K22" s="34" t="n">
-        <v>52</v>
+        <v>328</v>
+      </c>
+      <c r="K22" s="35" t="n">
+        <v>72</v>
       </c>
       <c r="L22" s="30" t="n">
-        <v>404</v>
+        <v>661</v>
       </c>
       <c r="M22" s="30" t="n">
-        <v>348</v>
-      </c>
-      <c r="N22" s="34" t="n">
-        <v>56</v>
+        <v>373</v>
+      </c>
+      <c r="N22" s="35" t="n">
+        <v>288</v>
       </c>
       <c r="O22" s="30" t="n">
-        <v>1727</v>
+        <v>1843</v>
       </c>
       <c r="P22" s="30" t="n">
-        <v>1796</v>
+        <v>1873</v>
       </c>
       <c r="Q22" s="31" t="n">
-        <v>-69</v>
+        <v>-30</v>
       </c>
       <c r="R22" s="30" t="n">
-        <v>2599</v>
+        <v>2727</v>
       </c>
       <c r="S22" s="30" t="n">
-        <v>2538</v>
-      </c>
-      <c r="T22" s="34" t="n">
-        <v>61</v>
-      </c>
-      <c r="U22" s="32" t="n">
-        <v>7107</v>
-      </c>
-      <c r="V22" s="32" t="n">
-        <v>7615</v>
-      </c>
-      <c r="W22" s="33" t="n">
-        <v>-508</v>
+        <v>2601</v>
+      </c>
+      <c r="T22" s="35" t="n">
+        <v>126</v>
+      </c>
+      <c r="U22" s="33" t="n">
+        <v>7748</v>
+      </c>
+      <c r="V22" s="33" t="n">
+        <v>7877</v>
+      </c>
+      <c r="W22" s="34" t="n">
+        <v>-129</v>
       </c>
     </row>
     <row r="23">
@@ -4955,67 +4955,67 @@
         </is>
       </c>
       <c r="C23" s="30" t="n">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>811</v>
+        <v>848</v>
       </c>
       <c r="E23" s="31" t="n">
-        <v>-386</v>
+        <v>-389</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>1503</v>
+        <v>1573</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>1712</v>
+        <v>1754</v>
       </c>
       <c r="H23" s="31" t="n">
-        <v>-209</v>
+        <v>-181</v>
       </c>
       <c r="I23" s="30" t="n">
-        <v>339</v>
+        <v>370</v>
       </c>
       <c r="J23" s="30" t="n">
-        <v>307</v>
-      </c>
-      <c r="K23" s="34" t="n">
-        <v>32</v>
+        <v>320</v>
+      </c>
+      <c r="K23" s="35" t="n">
+        <v>50</v>
       </c>
       <c r="L23" s="30" t="n">
-        <v>400</v>
+        <v>657</v>
       </c>
       <c r="M23" s="30" t="n">
-        <v>332</v>
-      </c>
-      <c r="N23" s="34" t="n">
-        <v>68</v>
+        <v>357</v>
+      </c>
+      <c r="N23" s="35" t="n">
+        <v>300</v>
       </c>
       <c r="O23" s="30" t="n">
-        <v>1673</v>
+        <v>1784</v>
       </c>
       <c r="P23" s="30" t="n">
-        <v>1725</v>
+        <v>1800</v>
       </c>
       <c r="Q23" s="31" t="n">
-        <v>-52</v>
+        <v>-16</v>
       </c>
       <c r="R23" s="30" t="n">
-        <v>2516</v>
+        <v>2645</v>
       </c>
       <c r="S23" s="30" t="n">
-        <v>2424</v>
-      </c>
-      <c r="T23" s="34" t="n">
-        <v>92</v>
-      </c>
-      <c r="U23" s="32" t="n">
-        <v>6856</v>
-      </c>
-      <c r="V23" s="32" t="n">
-        <v>7311</v>
-      </c>
-      <c r="W23" s="33" t="n">
-        <v>-455</v>
+        <v>2484</v>
+      </c>
+      <c r="T23" s="35" t="n">
+        <v>161</v>
+      </c>
+      <c r="U23" s="33" t="n">
+        <v>7488</v>
+      </c>
+      <c r="V23" s="33" t="n">
+        <v>7563</v>
+      </c>
+      <c r="W23" s="34" t="n">
+        <v>-75</v>
       </c>
     </row>
     <row r="24">
@@ -5025,67 +5025,67 @@
         </is>
       </c>
       <c r="C24" s="30" t="n">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="D24" s="30" t="n">
-        <v>767</v>
+        <v>802</v>
       </c>
       <c r="E24" s="31" t="n">
-        <v>-489</v>
+        <v>-490</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>1437</v>
+        <v>1500</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>1671</v>
+        <v>1711</v>
       </c>
       <c r="H24" s="31" t="n">
-        <v>-234</v>
+        <v>-211</v>
       </c>
       <c r="I24" s="30" t="n">
+        <v>341</v>
+      </c>
+      <c r="J24" s="30" t="n">
         <v>313</v>
       </c>
-      <c r="J24" s="30" t="n">
-        <v>299</v>
-      </c>
-      <c r="K24" s="34" t="n">
-        <v>14</v>
+      <c r="K24" s="35" t="n">
+        <v>28</v>
       </c>
       <c r="L24" s="30" t="n">
-        <v>393</v>
+        <v>649</v>
       </c>
       <c r="M24" s="30" t="n">
-        <v>317</v>
-      </c>
-      <c r="N24" s="34" t="n">
-        <v>76</v>
+        <v>338</v>
+      </c>
+      <c r="N24" s="35" t="n">
+        <v>311</v>
       </c>
       <c r="O24" s="30" t="n">
-        <v>1544</v>
+        <v>1652</v>
       </c>
       <c r="P24" s="30" t="n">
-        <v>1676</v>
+        <v>1747</v>
       </c>
       <c r="Q24" s="31" t="n">
-        <v>-132</v>
+        <v>-95</v>
       </c>
       <c r="R24" s="30" t="n">
-        <v>2351</v>
+        <v>2478</v>
       </c>
       <c r="S24" s="30" t="n">
-        <v>2361</v>
-      </c>
-      <c r="T24" s="31" t="n">
-        <v>-10</v>
-      </c>
-      <c r="U24" s="32" t="n">
-        <v>6316</v>
-      </c>
-      <c r="V24" s="32" t="n">
-        <v>7091</v>
-      </c>
-      <c r="W24" s="33" t="n">
-        <v>-775</v>
+        <v>2418</v>
+      </c>
+      <c r="T24" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="U24" s="33" t="n">
+        <v>6932</v>
+      </c>
+      <c r="V24" s="33" t="n">
+        <v>7329</v>
+      </c>
+      <c r="W24" s="34" t="n">
+        <v>-397</v>
       </c>
     </row>
     <row r="25">
@@ -5095,67 +5095,67 @@
         </is>
       </c>
       <c r="C25" s="30" t="n">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="D25" s="30" t="n">
-        <v>729</v>
+        <v>759</v>
       </c>
       <c r="E25" s="31" t="n">
-        <v>-460</v>
+        <v>-456</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>1395</v>
+        <v>1458</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>1646</v>
+        <v>1686</v>
       </c>
       <c r="H25" s="31" t="n">
-        <v>-251</v>
+        <v>-228</v>
       </c>
       <c r="I25" s="30" t="n">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>285</v>
-      </c>
-      <c r="K25" s="34" t="n">
-        <v>5</v>
+        <v>294</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <v>22</v>
       </c>
       <c r="L25" s="30" t="n">
-        <v>381</v>
+        <v>637</v>
       </c>
       <c r="M25" s="30" t="n">
-        <v>305</v>
-      </c>
-      <c r="N25" s="34" t="n">
-        <v>76</v>
+        <v>322</v>
+      </c>
+      <c r="N25" s="35" t="n">
+        <v>315</v>
       </c>
       <c r="O25" s="30" t="n">
-        <v>1515</v>
+        <v>1622</v>
       </c>
       <c r="P25" s="30" t="n">
-        <v>1640</v>
+        <v>1714</v>
       </c>
       <c r="Q25" s="31" t="n">
-        <v>-125</v>
+        <v>-92</v>
       </c>
       <c r="R25" s="30" t="n">
-        <v>2263</v>
+        <v>2384</v>
       </c>
       <c r="S25" s="30" t="n">
-        <v>2289</v>
-      </c>
-      <c r="T25" s="31" t="n">
-        <v>-26</v>
-      </c>
-      <c r="U25" s="32" t="n">
-        <v>6113</v>
-      </c>
-      <c r="V25" s="32" t="n">
-        <v>6894</v>
-      </c>
-      <c r="W25" s="33" t="n">
-        <v>-781</v>
+        <v>2348</v>
+      </c>
+      <c r="T25" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="U25" s="33" t="n">
+        <v>6720</v>
+      </c>
+      <c r="V25" s="33" t="n">
+        <v>7123</v>
+      </c>
+      <c r="W25" s="34" t="n">
+        <v>-403</v>
       </c>
     </row>
     <row r="26">
@@ -5165,67 +5165,67 @@
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="D26" s="30" t="n">
-        <v>693</v>
+        <v>719</v>
       </c>
       <c r="E26" s="31" t="n">
-        <v>-430</v>
+        <v>-428</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>1347</v>
+        <v>1413</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1604</v>
+        <v>1643</v>
       </c>
       <c r="H26" s="31" t="n">
-        <v>-257</v>
+        <v>-230</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>281</v>
-      </c>
-      <c r="K26" s="31" t="n">
-        <v>-10</v>
+        <v>290</v>
+      </c>
+      <c r="K26" s="35" t="n">
+        <v>3</v>
       </c>
       <c r="L26" s="30" t="n">
-        <v>380</v>
+        <v>637</v>
       </c>
       <c r="M26" s="30" t="n">
-        <v>305</v>
-      </c>
-      <c r="N26" s="34" t="n">
-        <v>75</v>
+        <v>321</v>
+      </c>
+      <c r="N26" s="35" t="n">
+        <v>316</v>
       </c>
       <c r="O26" s="30" t="n">
-        <v>1485</v>
+        <v>1586</v>
       </c>
       <c r="P26" s="30" t="n">
-        <v>1607</v>
+        <v>1670</v>
       </c>
       <c r="Q26" s="31" t="n">
-        <v>-122</v>
+        <v>-84</v>
       </c>
       <c r="R26" s="30" t="n">
-        <v>2225</v>
+        <v>2348</v>
       </c>
       <c r="S26" s="30" t="n">
-        <v>2233</v>
-      </c>
-      <c r="T26" s="31" t="n">
-        <v>-8</v>
-      </c>
-      <c r="U26" s="32" t="n">
-        <v>5971</v>
-      </c>
-      <c r="V26" s="32" t="n">
-        <v>6723</v>
-      </c>
-      <c r="W26" s="33" t="n">
-        <v>-752</v>
+        <v>2286</v>
+      </c>
+      <c r="T26" s="35" t="n">
+        <v>62</v>
+      </c>
+      <c r="U26" s="33" t="n">
+        <v>6568</v>
+      </c>
+      <c r="V26" s="33" t="n">
+        <v>6929</v>
+      </c>
+      <c r="W26" s="34" t="n">
+        <v>-361</v>
       </c>
     </row>
     <row r="27">
@@ -5235,67 +5235,67 @@
         </is>
       </c>
       <c r="C27" s="30" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="D27" s="30" t="n">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="E27" s="31" t="n">
         <v>-398</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>1294</v>
+        <v>1359</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>1521</v>
+        <v>1560</v>
       </c>
       <c r="H27" s="31" t="n">
-        <v>-227</v>
+        <v>-201</v>
       </c>
       <c r="I27" s="30" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="K27" s="31" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="L27" s="30" t="n">
-        <v>368</v>
+        <v>622</v>
       </c>
       <c r="M27" s="30" t="n">
-        <v>281</v>
-      </c>
-      <c r="N27" s="34" t="n">
-        <v>87</v>
+        <v>299</v>
+      </c>
+      <c r="N27" s="35" t="n">
+        <v>323</v>
       </c>
       <c r="O27" s="30" t="n">
-        <v>1462</v>
+        <v>1558</v>
       </c>
       <c r="P27" s="30" t="n">
-        <v>1551</v>
+        <v>1614</v>
       </c>
       <c r="Q27" s="31" t="n">
-        <v>-89</v>
+        <v>-56</v>
       </c>
       <c r="R27" s="30" t="n">
-        <v>2130</v>
+        <v>2246</v>
       </c>
       <c r="S27" s="30" t="n">
-        <v>2171</v>
-      </c>
-      <c r="T27" s="31" t="n">
-        <v>-41</v>
-      </c>
-      <c r="U27" s="32" t="n">
-        <v>5756</v>
-      </c>
-      <c r="V27" s="32" t="n">
-        <v>6440</v>
-      </c>
-      <c r="W27" s="33" t="n">
-        <v>-684</v>
+        <v>2225</v>
+      </c>
+      <c r="T27" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="U27" s="33" t="n">
+        <v>6333</v>
+      </c>
+      <c r="V27" s="33" t="n">
+        <v>6647</v>
+      </c>
+      <c r="W27" s="34" t="n">
+        <v>-314</v>
       </c>
     </row>
     <row r="28">
@@ -5305,67 +5305,67 @@
         </is>
       </c>
       <c r="C28" s="30" t="n">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="D28" s="30" t="n">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="E28" s="31" t="n">
-        <v>-377</v>
+        <v>-380</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>1254</v>
+        <v>1324</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>1453</v>
+        <v>1491</v>
       </c>
       <c r="H28" s="31" t="n">
-        <v>-199</v>
+        <v>-167</v>
       </c>
       <c r="I28" s="30" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K28" s="31" t="n">
-        <v>-60</v>
+        <v>-43</v>
       </c>
       <c r="L28" s="30" t="n">
-        <v>353</v>
+        <v>664</v>
       </c>
       <c r="M28" s="30" t="n">
-        <v>257</v>
-      </c>
-      <c r="N28" s="34" t="n">
-        <v>96</v>
+        <v>275</v>
+      </c>
+      <c r="N28" s="35" t="n">
+        <v>389</v>
       </c>
       <c r="O28" s="30" t="n">
-        <v>1400</v>
+        <v>1490</v>
       </c>
       <c r="P28" s="30" t="n">
-        <v>1511</v>
+        <v>1574</v>
       </c>
       <c r="Q28" s="31" t="n">
-        <v>-111</v>
+        <v>-84</v>
       </c>
       <c r="R28" s="30" t="n">
-        <v>1920</v>
+        <v>2028</v>
       </c>
       <c r="S28" s="30" t="n">
-        <v>2082</v>
+        <v>2137</v>
       </c>
       <c r="T28" s="31" t="n">
-        <v>-162</v>
-      </c>
-      <c r="U28" s="32" t="n">
-        <v>5356</v>
-      </c>
-      <c r="V28" s="32" t="n">
-        <v>6169</v>
-      </c>
-      <c r="W28" s="33" t="n">
-        <v>-813</v>
+        <v>-109</v>
+      </c>
+      <c r="U28" s="33" t="n">
+        <v>5979</v>
+      </c>
+      <c r="V28" s="33" t="n">
+        <v>6373</v>
+      </c>
+      <c r="W28" s="34" t="n">
+        <v>-394</v>
       </c>
     </row>
     <row r="29">
@@ -5375,67 +5375,67 @@
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="D29" s="30" t="n">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="E29" s="31" t="n">
-        <v>-338</v>
+        <v>-340</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>1221</v>
+        <v>1288</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>1378</v>
+        <v>1414</v>
       </c>
       <c r="H29" s="31" t="n">
-        <v>-157</v>
+        <v>-126</v>
       </c>
       <c r="I29" s="30" t="n">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="J29" s="30" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K29" s="31" t="n">
-        <v>-55</v>
+        <v>-38</v>
       </c>
       <c r="L29" s="30" t="n">
-        <v>330</v>
+        <v>644</v>
       </c>
       <c r="M29" s="30" t="n">
-        <v>243</v>
-      </c>
-      <c r="N29" s="34" t="n">
-        <v>87</v>
+        <v>261</v>
+      </c>
+      <c r="N29" s="35" t="n">
+        <v>383</v>
       </c>
       <c r="O29" s="30" t="n">
-        <v>1353</v>
+        <v>1438</v>
       </c>
       <c r="P29" s="30" t="n">
-        <v>1465</v>
+        <v>1523</v>
       </c>
       <c r="Q29" s="31" t="n">
-        <v>-112</v>
+        <v>-85</v>
       </c>
       <c r="R29" s="30" t="n">
-        <v>1759</v>
+        <v>1863</v>
       </c>
       <c r="S29" s="30" t="n">
-        <v>2008</v>
+        <v>2061</v>
       </c>
       <c r="T29" s="31" t="n">
-        <v>-249</v>
-      </c>
-      <c r="U29" s="32" t="n">
-        <v>5076</v>
-      </c>
-      <c r="V29" s="32" t="n">
-        <v>5900</v>
-      </c>
-      <c r="W29" s="33" t="n">
-        <v>-824</v>
+        <v>-198</v>
+      </c>
+      <c r="U29" s="33" t="n">
+        <v>5686</v>
+      </c>
+      <c r="V29" s="33" t="n">
+        <v>6090</v>
+      </c>
+      <c r="W29" s="34" t="n">
+        <v>-404</v>
       </c>
     </row>
     <row r="30">
@@ -5445,67 +5445,67 @@
         </is>
       </c>
       <c r="C30" s="30" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D30" s="30" t="n">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="E30" s="31" t="n">
-        <v>-272</v>
+        <v>-277</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>1193</v>
+        <v>1254</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>1296</v>
+        <v>1326</v>
       </c>
       <c r="H30" s="31" t="n">
-        <v>-103</v>
+        <v>-72</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K30" s="31" t="n">
-        <v>-49</v>
+        <v>-32</v>
       </c>
       <c r="L30" s="30" t="n">
-        <v>308</v>
+        <v>619</v>
       </c>
       <c r="M30" s="30" t="n">
-        <v>226</v>
-      </c>
-      <c r="N30" s="34" t="n">
-        <v>82</v>
+        <v>244</v>
+      </c>
+      <c r="N30" s="35" t="n">
+        <v>375</v>
       </c>
       <c r="O30" s="30" t="n">
-        <v>1309</v>
+        <v>1396</v>
       </c>
       <c r="P30" s="30" t="n">
-        <v>1398</v>
+        <v>1458</v>
       </c>
       <c r="Q30" s="31" t="n">
-        <v>-89</v>
+        <v>-62</v>
       </c>
       <c r="R30" s="30" t="n">
-        <v>1655</v>
+        <v>1758</v>
       </c>
       <c r="S30" s="30" t="n">
-        <v>1923</v>
+        <v>1971</v>
       </c>
       <c r="T30" s="31" t="n">
-        <v>-268</v>
-      </c>
-      <c r="U30" s="32" t="n">
-        <v>4872</v>
-      </c>
-      <c r="V30" s="32" t="n">
-        <v>5571</v>
-      </c>
-      <c r="W30" s="33" t="n">
-        <v>-699</v>
+        <v>-213</v>
+      </c>
+      <c r="U30" s="33" t="n">
+        <v>5469</v>
+      </c>
+      <c r="V30" s="33" t="n">
+        <v>5750</v>
+      </c>
+      <c r="W30" s="34" t="n">
+        <v>-281</v>
       </c>
     </row>
     <row r="31">
@@ -5515,67 +5515,67 @@
         </is>
       </c>
       <c r="C31" s="30" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D31" s="30" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="E31" s="31" t="n">
-        <v>-250</v>
+        <v>-258</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>1165</v>
+        <v>1223</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>1259</v>
+        <v>1290</v>
       </c>
       <c r="H31" s="31" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I31" s="30" t="n">
+        <v>182</v>
+      </c>
+      <c r="J31" s="30" t="n">
+        <v>212</v>
+      </c>
+      <c r="K31" s="31" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L31" s="30" t="n">
+        <v>592</v>
+      </c>
+      <c r="M31" s="30" t="n">
+        <v>231</v>
+      </c>
+      <c r="N31" s="35" t="n">
+        <v>361</v>
+      </c>
+      <c r="O31" s="30" t="n">
+        <v>1324</v>
+      </c>
+      <c r="P31" s="30" t="n">
+        <v>1418</v>
+      </c>
+      <c r="Q31" s="31" t="n">
         <v>-94</v>
       </c>
-      <c r="I31" s="30" t="n">
-        <v>161</v>
-      </c>
-      <c r="J31" s="30" t="n">
-        <v>205</v>
-      </c>
-      <c r="K31" s="31" t="n">
-        <v>-44</v>
-      </c>
-      <c r="L31" s="30" t="n">
-        <v>282</v>
-      </c>
-      <c r="M31" s="30" t="n">
-        <v>217</v>
-      </c>
-      <c r="N31" s="34" t="n">
-        <v>65</v>
-      </c>
-      <c r="O31" s="30" t="n">
-        <v>1250</v>
-      </c>
-      <c r="P31" s="30" t="n">
-        <v>1358</v>
-      </c>
-      <c r="Q31" s="31" t="n">
-        <v>-108</v>
-      </c>
       <c r="R31" s="30" t="n">
-        <v>1600</v>
+        <v>1697</v>
       </c>
       <c r="S31" s="30" t="n">
-        <v>1867</v>
+        <v>1916</v>
       </c>
       <c r="T31" s="31" t="n">
-        <v>-267</v>
-      </c>
-      <c r="U31" s="32" t="n">
-        <v>4672</v>
-      </c>
-      <c r="V31" s="32" t="n">
-        <v>5370</v>
-      </c>
-      <c r="W31" s="33" t="n">
-        <v>-698</v>
+        <v>-219</v>
+      </c>
+      <c r="U31" s="33" t="n">
+        <v>5241</v>
+      </c>
+      <c r="V31" s="33" t="n">
+        <v>5548</v>
+      </c>
+      <c r="W31" s="34" t="n">
+        <v>-307</v>
       </c>
     </row>
     <row r="32">
@@ -5585,67 +5585,67 @@
         </is>
       </c>
       <c r="C32" s="30" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D32" s="30" t="n">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="E32" s="31" t="n">
-        <v>-241</v>
+        <v>-249</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>1139</v>
+        <v>1197</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="H32" s="31" t="n">
-        <v>-101</v>
+        <v>-73</v>
       </c>
       <c r="I32" s="30" t="n">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="K32" s="31" t="n">
-        <v>-38</v>
+        <v>-23</v>
       </c>
       <c r="L32" s="30" t="n">
-        <v>267</v>
+        <v>577</v>
       </c>
       <c r="M32" s="30" t="n">
-        <v>199</v>
-      </c>
-      <c r="N32" s="34" t="n">
-        <v>68</v>
+        <v>213</v>
+      </c>
+      <c r="N32" s="35" t="n">
+        <v>364</v>
       </c>
       <c r="O32" s="30" t="n">
-        <v>1217</v>
+        <v>1288</v>
       </c>
       <c r="P32" s="30" t="n">
-        <v>1326</v>
+        <v>1384</v>
       </c>
       <c r="Q32" s="31" t="n">
-        <v>-109</v>
+        <v>-96</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>1557</v>
+        <v>1654</v>
       </c>
       <c r="S32" s="30" t="n">
-        <v>1816</v>
+        <v>1863</v>
       </c>
       <c r="T32" s="31" t="n">
-        <v>-259</v>
-      </c>
-      <c r="U32" s="32" t="n">
-        <v>4544</v>
-      </c>
-      <c r="V32" s="32" t="n">
-        <v>5224</v>
-      </c>
-      <c r="W32" s="33" t="n">
-        <v>-680</v>
+        <v>-209</v>
+      </c>
+      <c r="U32" s="33" t="n">
+        <v>5110</v>
+      </c>
+      <c r="V32" s="33" t="n">
+        <v>5396</v>
+      </c>
+      <c r="W32" s="34" t="n">
+        <v>-286</v>
       </c>
     </row>
     <row r="33">
@@ -5655,67 +5655,67 @@
         </is>
       </c>
       <c r="C33" s="30" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D33" s="30" t="n">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="E33" s="31" t="n">
-        <v>-236</v>
+        <v>-244</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>1126</v>
+        <v>1181</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>1231</v>
+        <v>1261</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>-105</v>
+        <v>-80</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="J33" s="30" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K33" s="31" t="n">
-        <v>-43</v>
+        <v>-24</v>
       </c>
       <c r="L33" s="30" t="n">
-        <v>254</v>
+        <v>564</v>
       </c>
       <c r="M33" s="30" t="n">
-        <v>200</v>
-      </c>
-      <c r="N33" s="34" t="n">
-        <v>54</v>
+        <v>214</v>
+      </c>
+      <c r="N33" s="35" t="n">
+        <v>350</v>
       </c>
       <c r="O33" s="30" t="n">
-        <v>1188</v>
+        <v>1260</v>
       </c>
       <c r="P33" s="30" t="n">
-        <v>1302</v>
+        <v>1351</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>-114</v>
+        <v>-91</v>
       </c>
       <c r="R33" s="30" t="n">
-        <v>1530</v>
+        <v>1621</v>
       </c>
       <c r="S33" s="30" t="n">
-        <v>1759</v>
+        <v>1804</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>-229</v>
-      </c>
-      <c r="U33" s="32" t="n">
-        <v>4456</v>
-      </c>
-      <c r="V33" s="32" t="n">
-        <v>5129</v>
-      </c>
-      <c r="W33" s="33" t="n">
-        <v>-673</v>
+        <v>-183</v>
+      </c>
+      <c r="U33" s="33" t="n">
+        <v>5016</v>
+      </c>
+      <c r="V33" s="33" t="n">
+        <v>5288</v>
+      </c>
+      <c r="W33" s="34" t="n">
+        <v>-272</v>
       </c>
     </row>
     <row r="34">
@@ -5725,67 +5725,67 @@
         </is>
       </c>
       <c r="C34" s="30" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D34" s="30" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="E34" s="31" t="n">
-        <v>-230</v>
+        <v>-237</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>1103</v>
+        <v>1154</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="H34" s="31" t="n">
-        <v>-95</v>
+        <v>-74</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K34" s="31" t="n">
-        <v>-49</v>
+        <v>-31</v>
       </c>
       <c r="L34" s="30" t="n">
-        <v>245</v>
+        <v>554</v>
       </c>
       <c r="M34" s="30" t="n">
-        <v>204</v>
-      </c>
-      <c r="N34" s="34" t="n">
-        <v>41</v>
+        <v>218</v>
+      </c>
+      <c r="N34" s="35" t="n">
+        <v>336</v>
       </c>
       <c r="O34" s="30" t="n">
-        <v>1133</v>
+        <v>1194</v>
       </c>
       <c r="P34" s="30" t="n">
-        <v>1292</v>
+        <v>1341</v>
       </c>
       <c r="Q34" s="31" t="n">
-        <v>-159</v>
+        <v>-147</v>
       </c>
       <c r="R34" s="30" t="n">
-        <v>1434</v>
+        <v>1512</v>
       </c>
       <c r="S34" s="30" t="n">
-        <v>1669</v>
+        <v>1714</v>
       </c>
       <c r="T34" s="31" t="n">
-        <v>-235</v>
-      </c>
-      <c r="U34" s="32" t="n">
-        <v>4241</v>
-      </c>
-      <c r="V34" s="32" t="n">
-        <v>4968</v>
-      </c>
-      <c r="W34" s="33" t="n">
-        <v>-727</v>
+        <v>-202</v>
+      </c>
+      <c r="U34" s="33" t="n">
+        <v>4769</v>
+      </c>
+      <c r="V34" s="33" t="n">
+        <v>5124</v>
+      </c>
+      <c r="W34" s="34" t="n">
+        <v>-355</v>
       </c>
     </row>
     <row r="35">
@@ -5795,67 +5795,67 @@
         </is>
       </c>
       <c r="C35" s="30" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D35" s="30" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="E35" s="31" t="n">
-        <v>-209</v>
+        <v>-216</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>1064</v>
+        <v>1115</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>1161</v>
+        <v>1191</v>
       </c>
       <c r="H35" s="31" t="n">
-        <v>-97</v>
+        <v>-76</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="J35" s="30" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K35" s="31" t="n">
-        <v>-59</v>
+        <v>-44</v>
       </c>
       <c r="L35" s="30" t="n">
-        <v>240</v>
+        <v>550</v>
       </c>
       <c r="M35" s="30" t="n">
-        <v>190</v>
-      </c>
-      <c r="N35" s="34" t="n">
-        <v>50</v>
+        <v>204</v>
+      </c>
+      <c r="N35" s="35" t="n">
+        <v>346</v>
       </c>
       <c r="O35" s="30" t="n">
-        <v>1093</v>
+        <v>1149</v>
       </c>
       <c r="P35" s="30" t="n">
-        <v>1239</v>
+        <v>1285</v>
       </c>
       <c r="Q35" s="31" t="n">
-        <v>-146</v>
+        <v>-136</v>
       </c>
       <c r="R35" s="30" t="n">
-        <v>1359</v>
+        <v>1427</v>
       </c>
       <c r="S35" s="30" t="n">
-        <v>1559</v>
+        <v>1607</v>
       </c>
       <c r="T35" s="31" t="n">
-        <v>-200</v>
-      </c>
-      <c r="U35" s="32" t="n">
-        <v>4072</v>
-      </c>
-      <c r="V35" s="32" t="n">
-        <v>4733</v>
-      </c>
-      <c r="W35" s="33" t="n">
-        <v>-661</v>
+        <v>-180</v>
+      </c>
+      <c r="U35" s="33" t="n">
+        <v>4582</v>
+      </c>
+      <c r="V35" s="33" t="n">
+        <v>4888</v>
+      </c>
+      <c r="W35" s="34" t="n">
+        <v>-306</v>
       </c>
     </row>
   </sheetData>
@@ -5943,16 +5943,16 @@
         </is>
       </c>
       <c r="D5" s="30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="F5" s="38" t="n">
         <v>2</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6">
@@ -5967,16 +5967,16 @@
         </is>
       </c>
       <c r="D6" s="30" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-17</v>
+        <v>-43</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1064</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="7">
@@ -5991,16 +5991,16 @@
         </is>
       </c>
       <c r="D7" s="30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -6015,16 +6015,16 @@
         </is>
       </c>
       <c r="D8" s="30" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-7</v>
+        <v>-20</v>
       </c>
       <c r="F8" s="38" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>240</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9">
@@ -6039,16 +6039,16 @@
         </is>
       </c>
       <c r="D9" s="30" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-11</v>
+        <v>-21</v>
       </c>
       <c r="F9" s="38" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G9" s="30" t="n">
-        <v>1093</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="10">
@@ -6063,16 +6063,16 @@
         </is>
       </c>
       <c r="D10" s="30" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>-27</v>
+        <v>-67</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>1359</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="11">
@@ -6087,16 +6087,16 @@
         </is>
       </c>
       <c r="D11" s="30" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E11" s="30" t="n">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="F11" s="38" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="30" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6111,16 +6111,16 @@
         </is>
       </c>
       <c r="D12" s="30" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E12" s="30" t="n">
-        <v>-33</v>
+        <v>-52</v>
       </c>
       <c r="F12" s="38" t="n">
         <v>39</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>1103</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="13">
@@ -6135,16 +6135,16 @@
         </is>
       </c>
       <c r="D13" s="30" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E13" s="30" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="F13" s="38" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -6159,16 +6159,16 @@
         </is>
       </c>
       <c r="D14" s="30" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E14" s="30" t="n">
-        <v>-3</v>
+        <v>-25</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>245</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15">
@@ -6183,16 +6183,16 @@
         </is>
       </c>
       <c r="D15" s="30" t="n">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="E15" s="30" t="n">
-        <v>-36</v>
+        <v>-63</v>
       </c>
       <c r="F15" s="38" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>1133</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="16">
@@ -6207,16 +6207,16 @@
         </is>
       </c>
       <c r="D16" s="30" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="E16" s="30" t="n">
-        <v>-60</v>
+        <v>-115</v>
       </c>
       <c r="F16" s="38" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>1434</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="17">
@@ -6231,16 +6231,16 @@
         </is>
       </c>
       <c r="D17" s="30" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>-13</v>
+        <v>-29</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18">
@@ -6255,16 +6255,16 @@
         </is>
       </c>
       <c r="D18" s="30" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>-24</v>
+        <v>-37</v>
       </c>
       <c r="F18" s="38" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>1126</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="19">
@@ -6279,16 +6279,16 @@
         </is>
       </c>
       <c r="D19" s="30" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="F19" s="38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20">
@@ -6303,16 +6303,16 @@
         </is>
       </c>
       <c r="D20" s="30" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>-8</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>254</v>
+        <v>564</v>
       </c>
     </row>
     <row r="21">
@@ -6327,16 +6327,16 @@
         </is>
       </c>
       <c r="D21" s="30" t="n">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>-48</v>
+        <v>-80</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1188</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="22">
@@ -6351,16 +6351,16 @@
         </is>
       </c>
       <c r="D22" s="30" t="n">
-        <v>139</v>
+        <v>194</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>-43</v>
+        <v>-85</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>1530</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="23">
@@ -6375,16 +6375,16 @@
         </is>
       </c>
       <c r="D23" s="30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="30" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="F23" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24">
@@ -6399,16 +6399,16 @@
         </is>
       </c>
       <c r="D24" s="30" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>1139</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="25">
@@ -6423,16 +6423,16 @@
         </is>
       </c>
       <c r="D25" s="30" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E25" s="30" t="n">
-        <v>-11</v>
+        <v>-21</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
@@ -6447,16 +6447,16 @@
         </is>
       </c>
       <c r="D26" s="30" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E26" s="30" t="n">
-        <v>-7</v>
+        <v>-19</v>
       </c>
       <c r="F26" s="38" t="n">
         <v>13</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>267</v>
+        <v>577</v>
       </c>
     </row>
     <row r="27">
@@ -6471,16 +6471,16 @@
         </is>
       </c>
       <c r="D27" s="30" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>-34</v>
+        <v>-85</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>1217</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="28">
@@ -6495,16 +6495,16 @@
         </is>
       </c>
       <c r="D28" s="30" t="n">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="E28" s="30" t="n">
-        <v>-42</v>
+        <v>-85</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>1557</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="29">
@@ -6519,16 +6519,16 @@
         </is>
       </c>
       <c r="D29" s="30" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E29" s="30" t="n">
-        <v>-7</v>
+        <v>-23</v>
       </c>
       <c r="F29" s="38" t="n">
         <v>6</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30">
@@ -6543,16 +6543,16 @@
         </is>
       </c>
       <c r="D30" s="30" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E30" s="30" t="n">
-        <v>-16</v>
+        <v>-37</v>
       </c>
       <c r="F30" s="38" t="n">
         <v>26</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>1165</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="31">
@@ -6567,16 +6567,16 @@
         </is>
       </c>
       <c r="D31" s="30" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E31" s="30" t="n">
-        <v>-12</v>
+        <v>-21</v>
       </c>
       <c r="F31" s="38" t="n">
         <v>5</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32">
@@ -6591,16 +6591,16 @@
         </is>
       </c>
       <c r="D32" s="30" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E32" s="30" t="n">
-        <v>-9</v>
+        <v>-19</v>
       </c>
       <c r="F32" s="38" t="n">
         <v>15</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>282</v>
+        <v>592</v>
       </c>
     </row>
     <row r="33">
@@ -6615,16 +6615,16 @@
         </is>
       </c>
       <c r="D33" s="30" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="E33" s="30" t="n">
-        <v>-18</v>
+        <v>-43</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>1250</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="34">
@@ -6639,16 +6639,16 @@
         </is>
       </c>
       <c r="D34" s="30" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="E34" s="30" t="n">
-        <v>-22</v>
+        <v>-54</v>
       </c>
       <c r="F34" s="38" t="n">
         <v>43</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>1600</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="35">
@@ -6663,16 +6663,16 @@
         </is>
       </c>
       <c r="D35" s="30" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E35" s="30" t="n">
-        <v>-7</v>
+        <v>-38</v>
       </c>
       <c r="F35" s="38" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36">
@@ -6687,16 +6687,16 @@
         </is>
       </c>
       <c r="D36" s="30" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E36" s="30" t="n">
-        <v>-33</v>
+        <v>-55</v>
       </c>
       <c r="F36" s="38" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>1193</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="37">
@@ -6711,16 +6711,16 @@
         </is>
       </c>
       <c r="D37" s="30" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E37" s="30" t="n">
-        <v>-13</v>
+        <v>-42</v>
       </c>
       <c r="F37" s="38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G37" s="30" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="D38" s="30" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>-5</v>
+        <v>-31</v>
       </c>
       <c r="F38" s="38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>308</v>
+        <v>619</v>
       </c>
     </row>
     <row r="39">
@@ -6759,16 +6759,16 @@
         </is>
       </c>
       <c r="D39" s="30" t="n">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>-32</v>
+        <v>-99</v>
       </c>
       <c r="F39" s="38" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>1309</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="40">
@@ -6783,16 +6783,16 @@
         </is>
       </c>
       <c r="D40" s="30" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="E40" s="30" t="n">
-        <v>-100</v>
+        <v>-179</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>1655</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="41">
@@ -6807,16 +6807,16 @@
         </is>
       </c>
       <c r="D41" s="30" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E41" s="30" t="n">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="F41" s="38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42">
@@ -6831,16 +6831,16 @@
         </is>
       </c>
       <c r="D42" s="30" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="E42" s="30" t="n">
-        <v>-37</v>
+        <v>-58</v>
       </c>
       <c r="F42" s="38" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>1221</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="43">
@@ -6855,16 +6855,16 @@
         </is>
       </c>
       <c r="D43" s="30" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E43" s="30" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="F43" s="38" t="n">
         <v>5</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>183</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44">
@@ -6879,16 +6879,16 @@
         </is>
       </c>
       <c r="D44" s="30" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="E44" s="30" t="n">
-        <v>-16</v>
+        <v>-47</v>
       </c>
       <c r="F44" s="38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>330</v>
+        <v>644</v>
       </c>
     </row>
     <row r="45">
@@ -6903,16 +6903,16 @@
         </is>
       </c>
       <c r="D45" s="30" t="n">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="E45" s="30" t="n">
-        <v>-47</v>
+        <v>-106</v>
       </c>
       <c r="F45" s="38" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>1353</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="46">
@@ -6927,16 +6927,16 @@
         </is>
       </c>
       <c r="D46" s="30" t="n">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="E46" s="30" t="n">
-        <v>-74</v>
+        <v>-134</v>
       </c>
       <c r="F46" s="38" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G46" s="30" t="n">
-        <v>1759</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="47">
@@ -6951,16 +6951,16 @@
         </is>
       </c>
       <c r="D47" s="30" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E47" s="30" t="n">
-        <v>-13</v>
+        <v>-38</v>
       </c>
       <c r="F47" s="38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48">
@@ -6975,16 +6975,16 @@
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="E48" s="30" t="n">
-        <v>-24</v>
+        <v>-53</v>
       </c>
       <c r="F48" s="38" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G48" s="30" t="n">
-        <v>1254</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="49">
@@ -6999,16 +6999,16 @@
         </is>
       </c>
       <c r="D49" s="30" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E49" s="30" t="n">
-        <v>-6</v>
+        <v>-24</v>
       </c>
       <c r="F49" s="38" t="n">
         <v>12</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50">
@@ -7023,16 +7023,16 @@
         </is>
       </c>
       <c r="D50" s="30" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E50" s="30" t="n">
-        <v>-16</v>
+        <v>-40</v>
       </c>
       <c r="F50" s="38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>353</v>
+        <v>664</v>
       </c>
     </row>
     <row r="51">
@@ -7047,16 +7047,16 @@
         </is>
       </c>
       <c r="D51" s="30" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="E51" s="30" t="n">
-        <v>-37</v>
+        <v>-77</v>
       </c>
       <c r="F51" s="38" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G51" s="30" t="n">
-        <v>1400</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="52">
@@ -7071,16 +7071,16 @@
         </is>
       </c>
       <c r="D52" s="30" t="n">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="E52" s="30" t="n">
-        <v>-103</v>
+        <v>-147</v>
       </c>
       <c r="F52" s="38" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>1920</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="53">
@@ -7095,16 +7095,16 @@
         </is>
       </c>
       <c r="D53" s="30" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E53" s="30" t="n">
-        <v>-25</v>
+        <v>-38</v>
       </c>
       <c r="F53" s="38" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54">
@@ -7119,16 +7119,16 @@
         </is>
       </c>
       <c r="D54" s="30" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="E54" s="30" t="n">
-        <v>-76</v>
+        <v>-97</v>
       </c>
       <c r="F54" s="38" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G54" s="30" t="n">
-        <v>1294</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="55">
@@ -7143,16 +7143,16 @@
         </is>
       </c>
       <c r="D55" s="30" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E55" s="30" t="n">
-        <v>-27</v>
+        <v>-38</v>
       </c>
       <c r="F55" s="38" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55" s="30" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56">
@@ -7167,16 +7167,16 @@
         </is>
       </c>
       <c r="D56" s="30" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E56" s="30" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F56" s="38" t="n">
-        <v>15</v>
+        <v>-88</v>
+      </c>
+      <c r="F56" s="39" t="n">
+        <v>-42</v>
       </c>
       <c r="G56" s="30" t="n">
-        <v>368</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57">
@@ -7191,16 +7191,16 @@
         </is>
       </c>
       <c r="D57" s="30" t="n">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E57" s="30" t="n">
-        <v>-51</v>
+        <v>-84</v>
       </c>
       <c r="F57" s="38" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>1462</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="58">
@@ -7215,16 +7215,16 @@
         </is>
       </c>
       <c r="D58" s="30" t="n">
-        <v>391</v>
+        <v>474</v>
       </c>
       <c r="E58" s="30" t="n">
-        <v>-181</v>
+        <v>-256</v>
       </c>
       <c r="F58" s="38" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>2130</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="59">
@@ -7239,16 +7239,16 @@
         </is>
       </c>
       <c r="D59" s="30" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E59" s="30" t="n">
-        <v>-14</v>
+        <v>-36</v>
       </c>
       <c r="F59" s="38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G59" s="30" t="n">
-        <v>263</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60">
@@ -7263,16 +7263,16 @@
         </is>
       </c>
       <c r="D60" s="30" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E60" s="30" t="n">
-        <v>-32</v>
+        <v>-49</v>
       </c>
       <c r="F60" s="38" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G60" s="30" t="n">
-        <v>1347</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="61">
@@ -7287,16 +7287,16 @@
         </is>
       </c>
       <c r="D61" s="30" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E61" s="30" t="n">
-        <v>-21</v>
+        <v>-27</v>
       </c>
       <c r="F61" s="38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G61" s="30" t="n">
-        <v>271</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62">
@@ -7311,16 +7311,16 @@
         </is>
       </c>
       <c r="D62" s="30" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E62" s="30" t="n">
-        <v>-11</v>
+        <v>-20</v>
       </c>
       <c r="F62" s="38" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G62" s="30" t="n">
-        <v>380</v>
+        <v>637</v>
       </c>
     </row>
     <row r="63">
@@ -7335,16 +7335,16 @@
         </is>
       </c>
       <c r="D63" s="30" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="E63" s="30" t="n">
-        <v>-48</v>
+        <v>-93</v>
       </c>
       <c r="F63" s="38" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>1485</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="64">
@@ -7359,16 +7359,16 @@
         </is>
       </c>
       <c r="D64" s="30" t="n">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="E64" s="30" t="n">
-        <v>-101</v>
+        <v>-154</v>
       </c>
       <c r="F64" s="38" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G64" s="30" t="n">
-        <v>2225</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="65">
@@ -7383,16 +7383,16 @@
         </is>
       </c>
       <c r="D65" s="30" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E65" s="30" t="n">
-        <v>-4</v>
+        <v>-32</v>
       </c>
       <c r="F65" s="38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G65" s="30" t="n">
-        <v>269</v>
+        <v>303</v>
       </c>
     </row>
     <row r="66">
@@ -7407,16 +7407,16 @@
         </is>
       </c>
       <c r="D66" s="30" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E66" s="30" t="n">
-        <v>-19</v>
+        <v>-33</v>
       </c>
       <c r="F66" s="38" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>1395</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="67">
@@ -7431,16 +7431,16 @@
         </is>
       </c>
       <c r="D67" s="30" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E67" s="30" t="n">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="F67" s="38" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G67" s="30" t="n">
-        <v>290</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68">
@@ -7455,16 +7455,16 @@
         </is>
       </c>
       <c r="D68" s="30" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E68" s="30" t="n">
-        <v>-13</v>
-      </c>
-      <c r="F68" s="38" t="n">
-        <v>1</v>
+        <v>-27</v>
+      </c>
+      <c r="F68" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="G68" s="30" t="n">
-        <v>381</v>
+        <v>637</v>
       </c>
     </row>
     <row r="69">
@@ -7479,16 +7479,16 @@
         </is>
       </c>
       <c r="D69" s="30" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E69" s="30" t="n">
-        <v>-22</v>
+        <v>-54</v>
       </c>
       <c r="F69" s="38" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>1515</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="70">
@@ -7503,16 +7503,16 @@
         </is>
       </c>
       <c r="D70" s="30" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E70" s="30" t="n">
-        <v>-83</v>
+        <v>-117</v>
       </c>
       <c r="F70" s="38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G70" s="30" t="n">
-        <v>2263</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="71">
@@ -7527,16 +7527,16 @@
         </is>
       </c>
       <c r="D71" s="30" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="E71" s="30" t="n">
-        <v>-14</v>
+        <v>-52</v>
       </c>
       <c r="F71" s="38" t="n">
         <v>9</v>
       </c>
       <c r="G71" s="30" t="n">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72">
@@ -7551,16 +7551,16 @@
         </is>
       </c>
       <c r="D72" s="30" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E72" s="30" t="n">
-        <v>-48</v>
+        <v>-63</v>
       </c>
       <c r="F72" s="38" t="n">
         <v>42</v>
       </c>
       <c r="G72" s="30" t="n">
-        <v>1437</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="73">
@@ -7575,16 +7575,16 @@
         </is>
       </c>
       <c r="D73" s="30" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="E73" s="30" t="n">
-        <v>-17</v>
+        <v>-38</v>
       </c>
       <c r="F73" s="38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G73" s="30" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74">
@@ -7599,16 +7599,16 @@
         </is>
       </c>
       <c r="D74" s="30" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E74" s="30" t="n">
-        <v>-12</v>
+        <v>-34</v>
       </c>
       <c r="F74" s="38" t="n">
         <v>12</v>
       </c>
       <c r="G74" s="30" t="n">
-        <v>393</v>
+        <v>649</v>
       </c>
     </row>
     <row r="75">
@@ -7623,16 +7623,16 @@
         </is>
       </c>
       <c r="D75" s="30" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E75" s="30" t="n">
-        <v>-38</v>
+        <v>-59</v>
       </c>
       <c r="F75" s="38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G75" s="30" t="n">
-        <v>1544</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="76">
@@ -7647,16 +7647,16 @@
         </is>
       </c>
       <c r="D76" s="30" t="n">
-        <v>176</v>
+        <v>230</v>
       </c>
       <c r="E76" s="30" t="n">
-        <v>-88</v>
+        <v>-136</v>
       </c>
       <c r="F76" s="38" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G76" s="30" t="n">
-        <v>2351</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="77">
@@ -7671,16 +7671,16 @@
         </is>
       </c>
       <c r="D77" s="30" t="n">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="E77" s="30" t="n">
-        <v>-36</v>
+        <v>-81</v>
       </c>
       <c r="F77" s="38" t="n">
         <v>147</v>
       </c>
       <c r="G77" s="30" t="n">
-        <v>425</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78">
@@ -7695,16 +7695,16 @@
         </is>
       </c>
       <c r="D78" s="30" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E78" s="30" t="n">
-        <v>-47</v>
+        <v>-52</v>
       </c>
       <c r="F78" s="38" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G78" s="30" t="n">
-        <v>1503</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="79">
@@ -7719,16 +7719,16 @@
         </is>
       </c>
       <c r="D79" s="30" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E79" s="30" t="n">
-        <v>-23</v>
+        <v>-39</v>
       </c>
       <c r="F79" s="38" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G79" s="30" t="n">
-        <v>339</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80">
@@ -7743,16 +7743,16 @@
         </is>
       </c>
       <c r="D80" s="30" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E80" s="30" t="n">
-        <v>-14</v>
+        <v>-39</v>
       </c>
       <c r="F80" s="38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G80" s="30" t="n">
-        <v>400</v>
+        <v>657</v>
       </c>
     </row>
     <row r="81">
@@ -7767,16 +7767,16 @@
         </is>
       </c>
       <c r="D81" s="30" t="n">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="E81" s="30" t="n">
-        <v>-83</v>
+        <v>-163</v>
       </c>
       <c r="F81" s="38" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G81" s="30" t="n">
-        <v>1673</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="82">
@@ -7791,16 +7791,16 @@
         </is>
       </c>
       <c r="D82" s="30" t="n">
-        <v>274</v>
+        <v>363</v>
       </c>
       <c r="E82" s="30" t="n">
-        <v>-109</v>
+        <v>-196</v>
       </c>
       <c r="F82" s="38" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G82" s="30" t="n">
-        <v>2516</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="83">
@@ -7815,16 +7815,16 @@
         </is>
       </c>
       <c r="D83" s="30" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E83" s="30" t="n">
-        <v>-43</v>
+        <v>-82</v>
       </c>
       <c r="F83" s="38" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G83" s="30" t="n">
-        <v>456</v>
+        <v>493</v>
       </c>
     </row>
     <row r="84">
@@ -7839,16 +7839,16 @@
         </is>
       </c>
       <c r="D84" s="30" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E84" s="30" t="n">
-        <v>-37</v>
+        <v>-46</v>
       </c>
       <c r="F84" s="38" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G84" s="30" t="n">
-        <v>1551</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="85">
@@ -7863,16 +7863,16 @@
         </is>
       </c>
       <c r="D85" s="30" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="E85" s="30" t="n">
-        <v>-27</v>
+        <v>-55</v>
       </c>
       <c r="F85" s="38" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>370</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86">
@@ -7887,16 +7887,16 @@
         </is>
       </c>
       <c r="D86" s="30" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="E86" s="30" t="n">
-        <v>-28</v>
+        <v>-52</v>
       </c>
       <c r="F86" s="38" t="n">
         <v>4</v>
       </c>
       <c r="G86" s="30" t="n">
-        <v>404</v>
+        <v>661</v>
       </c>
     </row>
     <row r="87">
@@ -7911,16 +7911,16 @@
         </is>
       </c>
       <c r="D87" s="30" t="n">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="E87" s="30" t="n">
-        <v>-66</v>
+        <v>-152</v>
       </c>
       <c r="F87" s="38" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G87" s="30" t="n">
-        <v>1727</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="88">
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="D88" s="30" t="n">
-        <v>165</v>
+        <v>204</v>
       </c>
       <c r="E88" s="30" t="n">
-        <v>-82</v>
+        <v>-122</v>
       </c>
       <c r="F88" s="38" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G88" s="30" t="n">
-        <v>2599</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="89">
@@ -7959,16 +7959,16 @@
         </is>
       </c>
       <c r="D89" s="30" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E89" s="30" t="n">
-        <v>-46</v>
+        <v>-81</v>
       </c>
       <c r="F89" s="38" t="n">
         <v>27</v>
       </c>
       <c r="G89" s="30" t="n">
-        <v>483</v>
+        <v>520</v>
       </c>
     </row>
     <row r="90">
@@ -7983,16 +7983,16 @@
         </is>
       </c>
       <c r="D90" s="30" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E90" s="30" t="n">
-        <v>-38</v>
+        <v>-70</v>
       </c>
       <c r="F90" s="38" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G90" s="30" t="n">
-        <v>1596</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="91">
@@ -8007,16 +8007,16 @@
         </is>
       </c>
       <c r="D91" s="30" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E91" s="30" t="n">
-        <v>-38</v>
+        <v>-48</v>
       </c>
       <c r="F91" s="38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G91" s="30" t="n">
-        <v>404</v>
+        <v>436</v>
       </c>
     </row>
     <row r="92">
@@ -8031,16 +8031,16 @@
         </is>
       </c>
       <c r="D92" s="30" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E92" s="30" t="n">
-        <v>-24</v>
+        <v>-35</v>
       </c>
       <c r="F92" s="38" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G92" s="30" t="n">
-        <v>452</v>
+        <v>710</v>
       </c>
     </row>
     <row r="93">
@@ -8055,16 +8055,16 @@
         </is>
       </c>
       <c r="D93" s="30" t="n">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="E93" s="30" t="n">
-        <v>-74</v>
+        <v>-149</v>
       </c>
       <c r="F93" s="38" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G93" s="30" t="n">
-        <v>1784</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="94">
@@ -8079,16 +8079,16 @@
         </is>
       </c>
       <c r="D94" s="30" t="n">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="E94" s="30" t="n">
-        <v>-86</v>
+        <v>-147</v>
       </c>
       <c r="F94" s="38" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G94" s="30" t="n">
-        <v>2672</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="95">
@@ -8103,16 +8103,16 @@
         </is>
       </c>
       <c r="D95" s="30" t="n">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="E95" s="30" t="n">
-        <v>-36</v>
+        <v>-90</v>
       </c>
       <c r="F95" s="38" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G95" s="30" t="n">
-        <v>493</v>
+        <v>533</v>
       </c>
     </row>
     <row r="96">
@@ -8127,16 +8127,16 @@
         </is>
       </c>
       <c r="D96" s="30" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E96" s="30" t="n">
-        <v>-42</v>
+        <v>-78</v>
       </c>
       <c r="F96" s="38" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G96" s="30" t="n">
-        <v>1638</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="97">
@@ -8151,16 +8151,16 @@
         </is>
       </c>
       <c r="D97" s="30" t="n">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="E97" s="30" t="n">
-        <v>-33</v>
+        <v>-73</v>
       </c>
       <c r="F97" s="38" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G97" s="30" t="n">
-        <v>448</v>
+        <v>485</v>
       </c>
     </row>
     <row r="98">
@@ -8175,16 +8175,16 @@
         </is>
       </c>
       <c r="D98" s="30" t="n">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E98" s="30" t="n">
-        <v>-54</v>
-      </c>
-      <c r="F98" s="32" t="n">
-        <v>0</v>
+        <v>-84</v>
+      </c>
+      <c r="F98" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="G98" s="30" t="n">
-        <v>452</v>
+        <v>711</v>
       </c>
     </row>
     <row r="99">
@@ -8199,16 +8199,16 @@
         </is>
       </c>
       <c r="D99" s="30" t="n">
-        <v>427</v>
+        <v>490</v>
       </c>
       <c r="E99" s="30" t="n">
-        <v>-132</v>
+        <v>-194</v>
       </c>
       <c r="F99" s="38" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G99" s="30" t="n">
-        <v>2079</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="100">
@@ -8223,16 +8223,16 @@
         </is>
       </c>
       <c r="D100" s="30" t="n">
-        <v>236</v>
+        <v>342</v>
       </c>
       <c r="E100" s="30" t="n">
-        <v>-134</v>
+        <v>-230</v>
       </c>
       <c r="F100" s="38" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G100" s="30" t="n">
-        <v>2774</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="101">
@@ -8247,16 +8247,16 @@
         </is>
       </c>
       <c r="D101" s="30" t="n">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="E101" s="30" t="n">
-        <v>-36</v>
+        <v>-105</v>
       </c>
       <c r="F101" s="38" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G101" s="30" t="n">
-        <v>513</v>
+        <v>563</v>
       </c>
     </row>
     <row r="102">
@@ -8271,16 +8271,16 @@
         </is>
       </c>
       <c r="D102" s="30" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="E102" s="30" t="n">
-        <v>-37</v>
+        <v>-87</v>
       </c>
       <c r="F102" s="38" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G102" s="30" t="n">
-        <v>1682</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="103">
@@ -8295,16 +8295,16 @@
         </is>
       </c>
       <c r="D103" s="30" t="n">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="E103" s="30" t="n">
-        <v>-22</v>
+        <v>-61</v>
       </c>
       <c r="F103" s="38" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G103" s="30" t="n">
-        <v>492</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104">
@@ -8319,16 +8319,16 @@
         </is>
       </c>
       <c r="D104" s="30" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E104" s="30" t="n">
-        <v>-37</v>
-      </c>
-      <c r="F104" s="39" t="n">
-        <v>-7</v>
+        <v>-73</v>
+      </c>
+      <c r="F104" s="38" t="n">
+        <v>1</v>
       </c>
       <c r="G104" s="30" t="n">
-        <v>445</v>
+        <v>712</v>
       </c>
     </row>
     <row r="105">
@@ -8343,16 +8343,16 @@
         </is>
       </c>
       <c r="D105" s="30" t="n">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="E105" s="30" t="n">
-        <v>-83</v>
+        <v>-127</v>
       </c>
       <c r="F105" s="38" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G105" s="30" t="n">
-        <v>2117</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="106">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="D106" s="30" t="n">
-        <v>143</v>
+        <v>215</v>
       </c>
       <c r="E106" s="30" t="n">
-        <v>-85</v>
+        <v>-154</v>
       </c>
       <c r="F106" s="38" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G106" s="30" t="n">
-        <v>2832</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="107">
@@ -8391,16 +8391,16 @@
         </is>
       </c>
       <c r="D107" s="30" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="E107" s="30" t="n">
-        <v>-18</v>
+        <v>-71</v>
       </c>
       <c r="F107" s="38" t="n">
         <v>22</v>
       </c>
       <c r="G107" s="30" t="n">
-        <v>535</v>
+        <v>585</v>
       </c>
     </row>
     <row r="108">
@@ -8415,16 +8415,16 @@
         </is>
       </c>
       <c r="D108" s="30" t="n">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="E108" s="30" t="n">
-        <v>-26</v>
+        <v>-65</v>
       </c>
       <c r="F108" s="38" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G108" s="30" t="n">
-        <v>1721</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="109">
@@ -8439,16 +8439,16 @@
         </is>
       </c>
       <c r="D109" s="30" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="E109" s="30" t="n">
-        <v>-32</v>
+        <v>-60</v>
       </c>
       <c r="F109" s="38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G109" s="30" t="n">
-        <v>512</v>
+        <v>548</v>
       </c>
     </row>
     <row r="110">
@@ -8463,16 +8463,16 @@
         </is>
       </c>
       <c r="D110" s="30" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E110" s="30" t="n">
-        <v>-9</v>
+        <v>-37</v>
       </c>
       <c r="F110" s="38" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G110" s="30" t="n">
-        <v>473</v>
+        <v>736</v>
       </c>
     </row>
     <row r="111">
@@ -8487,16 +8487,16 @@
         </is>
       </c>
       <c r="D111" s="30" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="E111" s="30" t="n">
-        <v>-34</v>
+        <v>-81</v>
       </c>
       <c r="F111" s="38" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G111" s="30" t="n">
-        <v>2164</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="112">
@@ -8511,16 +8511,16 @@
         </is>
       </c>
       <c r="D112" s="30" t="n">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="E112" s="30" t="n">
-        <v>-64</v>
+        <v>-147</v>
       </c>
       <c r="F112" s="38" t="n">
         <v>81</v>
       </c>
       <c r="G112" s="30" t="n">
-        <v>2913</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="113">
@@ -8535,16 +8535,16 @@
         </is>
       </c>
       <c r="D113" s="30" t="n">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="E113" s="30" t="n">
-        <v>-27</v>
+        <v>-115</v>
       </c>
       <c r="F113" s="38" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G113" s="30" t="n">
-        <v>576</v>
+        <v>641</v>
       </c>
     </row>
     <row r="114">
@@ -8559,16 +8559,16 @@
         </is>
       </c>
       <c r="D114" s="30" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E114" s="30" t="n">
-        <v>-43</v>
+        <v>-68</v>
       </c>
       <c r="F114" s="38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G114" s="30" t="n">
-        <v>1755</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="115">
@@ -8583,16 +8583,16 @@
         </is>
       </c>
       <c r="D115" s="30" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="E115" s="30" t="n">
-        <v>-46</v>
+        <v>-93</v>
       </c>
       <c r="F115" s="38" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G115" s="30" t="n">
-        <v>563</v>
+        <v>602</v>
       </c>
     </row>
     <row r="116">
@@ -8607,16 +8607,16 @@
         </is>
       </c>
       <c r="D116" s="30" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="E116" s="30" t="n">
-        <v>-18</v>
+        <v>-83</v>
       </c>
       <c r="F116" s="38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G116" s="30" t="n">
-        <v>484</v>
+        <v>750</v>
       </c>
     </row>
     <row r="117">
@@ -8631,16 +8631,16 @@
         </is>
       </c>
       <c r="D117" s="30" t="n">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="E117" s="30" t="n">
-        <v>-56</v>
+        <v>-111</v>
       </c>
       <c r="F117" s="38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>2206</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="118">
@@ -8655,16 +8655,16 @@
         </is>
       </c>
       <c r="D118" s="30" t="n">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="E118" s="30" t="n">
-        <v>-83</v>
+        <v>-154</v>
       </c>
       <c r="F118" s="38" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G118" s="30" t="n">
-        <v>2956</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="119">
@@ -8679,16 +8679,16 @@
         </is>
       </c>
       <c r="D119" s="30" t="n">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="E119" s="30" t="n">
-        <v>-33</v>
+        <v>-163</v>
       </c>
       <c r="F119" s="38" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G119" s="30" t="n">
-        <v>634</v>
+        <v>706</v>
       </c>
     </row>
     <row r="120">
@@ -8703,16 +8703,16 @@
         </is>
       </c>
       <c r="D120" s="30" t="n">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="E120" s="30" t="n">
-        <v>-67</v>
+        <v>-132</v>
       </c>
       <c r="F120" s="38" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G120" s="30" t="n">
-        <v>1884</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="121">
@@ -8727,16 +8727,16 @@
         </is>
       </c>
       <c r="D121" s="30" t="n">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="E121" s="30" t="n">
-        <v>-53</v>
+        <v>-109</v>
       </c>
       <c r="F121" s="38" t="n">
         <v>38</v>
       </c>
       <c r="G121" s="30" t="n">
-        <v>601</v>
+        <v>640</v>
       </c>
     </row>
     <row r="122">
@@ -8751,16 +8751,16 @@
         </is>
       </c>
       <c r="D122" s="30" t="n">
-        <v>47</v>
+        <v>111</v>
       </c>
       <c r="E122" s="30" t="n">
-        <v>-30</v>
+        <v>-86</v>
       </c>
       <c r="F122" s="38" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G122" s="30" t="n">
-        <v>501</v>
+        <v>775</v>
       </c>
     </row>
     <row r="123">
@@ -8775,16 +8775,16 @@
         </is>
       </c>
       <c r="D123" s="30" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="E123" s="30" t="n">
-        <v>-92</v>
+        <v>-151</v>
       </c>
       <c r="F123" s="38" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G123" s="30" t="n">
-        <v>2289</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="124">
@@ -8799,16 +8799,16 @@
         </is>
       </c>
       <c r="D124" s="30" t="n">
-        <v>277</v>
+        <v>366</v>
       </c>
       <c r="E124" s="30" t="n">
-        <v>-137</v>
+        <v>-224</v>
       </c>
       <c r="F124" s="38" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G124" s="30" t="n">
-        <v>3096</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="125">
@@ -8823,16 +8823,16 @@
         </is>
       </c>
       <c r="D125" s="30" t="n">
-        <v>141</v>
+        <v>236</v>
       </c>
       <c r="E125" s="30" t="n">
-        <v>-62</v>
+        <v>-148</v>
       </c>
       <c r="F125" s="38" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G125" s="30" t="n">
-        <v>713</v>
+        <v>794</v>
       </c>
     </row>
     <row r="126">
@@ -8847,16 +8847,16 @@
         </is>
       </c>
       <c r="D126" s="30" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="E126" s="30" t="n">
-        <v>-63</v>
+        <v>-114</v>
       </c>
       <c r="F126" s="38" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G126" s="30" t="n">
-        <v>1957</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="127">
@@ -8871,16 +8871,16 @@
         </is>
       </c>
       <c r="D127" s="30" t="n">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="E127" s="30" t="n">
-        <v>-32</v>
+        <v>-79</v>
       </c>
       <c r="F127" s="38" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G127" s="30" t="n">
-        <v>643</v>
+        <v>686</v>
       </c>
     </row>
     <row r="128">
@@ -8895,16 +8895,16 @@
         </is>
       </c>
       <c r="D128" s="30" t="n">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="E128" s="30" t="n">
-        <v>-79</v>
+        <v>-116</v>
       </c>
       <c r="F128" s="39" t="n">
         <v>-19</v>
       </c>
       <c r="G128" s="30" t="n">
-        <v>482</v>
+        <v>756</v>
       </c>
     </row>
     <row r="129">
@@ -8919,16 +8919,16 @@
         </is>
       </c>
       <c r="D129" s="30" t="n">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="E129" s="30" t="n">
-        <v>-128</v>
+        <v>-201</v>
       </c>
       <c r="F129" s="38" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G129" s="30" t="n">
-        <v>2323</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="130">
@@ -8943,16 +8943,16 @@
         </is>
       </c>
       <c r="D130" s="30" t="n">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="E130" s="30" t="n">
-        <v>-172</v>
+        <v>-243</v>
       </c>
       <c r="F130" s="38" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G130" s="30" t="n">
-        <v>3266</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="131">
@@ -8967,16 +8967,16 @@
         </is>
       </c>
       <c r="D131" s="30" t="n">
-        <v>110</v>
+        <v>243</v>
       </c>
       <c r="E131" s="30" t="n">
-        <v>-62</v>
+        <v>-190</v>
       </c>
       <c r="F131" s="38" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G131" s="30" t="n">
-        <v>761</v>
+        <v>847</v>
       </c>
     </row>
     <row r="132">
@@ -8991,16 +8991,16 @@
         </is>
       </c>
       <c r="D132" s="30" t="n">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="E132" s="30" t="n">
-        <v>-77</v>
+        <v>-123</v>
       </c>
       <c r="F132" s="38" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G132" s="30" t="n">
-        <v>2001</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="133">
@@ -9015,16 +9015,16 @@
         </is>
       </c>
       <c r="D133" s="30" t="n">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="E133" s="30" t="n">
-        <v>-35</v>
+        <v>-84</v>
       </c>
       <c r="F133" s="38" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="134">
@@ -9039,16 +9039,16 @@
         </is>
       </c>
       <c r="D134" s="30" t="n">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="E134" s="30" t="n">
-        <v>-21</v>
+        <v>-60</v>
       </c>
       <c r="F134" s="38" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G134" s="30" t="n">
-        <v>551</v>
+        <v>830</v>
       </c>
     </row>
     <row r="135">
@@ -9063,16 +9063,16 @@
         </is>
       </c>
       <c r="D135" s="30" t="n">
-        <v>184</v>
+        <v>292</v>
       </c>
       <c r="E135" s="30" t="n">
-        <v>-92</v>
+        <v>-188</v>
       </c>
       <c r="F135" s="38" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="G135" s="30" t="n">
-        <v>2415</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="136">
@@ -9087,16 +9087,16 @@
         </is>
       </c>
       <c r="D136" s="30" t="n">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="E136" s="30" t="n">
-        <v>-130</v>
+        <v>-194</v>
       </c>
       <c r="F136" s="38" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G136" s="30" t="n">
-        <v>3382</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="137">
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="D137" s="30" t="n">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="E137" s="30" t="n">
-        <v>-27</v>
+        <v>-124</v>
       </c>
       <c r="F137" s="38" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G137" s="30" t="n">
-        <v>811</v>
+        <v>901</v>
       </c>
     </row>
     <row r="138">
@@ -9135,16 +9135,16 @@
         </is>
       </c>
       <c r="D138" s="30" t="n">
-        <v>184</v>
+        <v>256</v>
       </c>
       <c r="E138" s="30" t="n">
-        <v>-111</v>
+        <v>-178</v>
       </c>
       <c r="F138" s="38" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G138" s="30" t="n">
-        <v>2074</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="139">
@@ -9159,16 +9159,16 @@
         </is>
       </c>
       <c r="D139" s="30" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="E139" s="30" t="n">
-        <v>-51</v>
+        <v>-76</v>
       </c>
       <c r="F139" s="38" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G139" s="30" t="n">
-        <v>697</v>
+        <v>748</v>
       </c>
     </row>
     <row r="140">
@@ -9183,16 +9183,16 @@
         </is>
       </c>
       <c r="D140" s="30" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E140" s="30" t="n">
-        <v>-32</v>
+        <v>-85</v>
       </c>
       <c r="F140" s="38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G140" s="30" t="n">
-        <v>564</v>
+        <v>845</v>
       </c>
     </row>
     <row r="141">
@@ -9207,16 +9207,16 @@
         </is>
       </c>
       <c r="D141" s="30" t="n">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="E141" s="30" t="n">
-        <v>-141</v>
+        <v>-260</v>
       </c>
       <c r="F141" s="38" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G141" s="30" t="n">
-        <v>2481</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="142">
@@ -9231,16 +9231,16 @@
         </is>
       </c>
       <c r="D142" s="30" t="n">
-        <v>196</v>
+        <v>271</v>
       </c>
       <c r="E142" s="30" t="n">
-        <v>-146</v>
+        <v>-220</v>
       </c>
       <c r="F142" s="38" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G142" s="30" t="n">
-        <v>3432</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="143">
@@ -9255,16 +9255,16 @@
         </is>
       </c>
       <c r="D143" s="30" t="n">
-        <v>66</v>
+        <v>173</v>
       </c>
       <c r="E143" s="30" t="n">
-        <v>-36</v>
+        <v>-136</v>
       </c>
       <c r="F143" s="38" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G143" s="30" t="n">
-        <v>841</v>
+        <v>938</v>
       </c>
     </row>
     <row r="144">
@@ -9279,16 +9279,16 @@
         </is>
       </c>
       <c r="D144" s="30" t="n">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="E144" s="30" t="n">
-        <v>-74</v>
+        <v>-125</v>
       </c>
       <c r="F144" s="38" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G144" s="30" t="n">
-        <v>2106</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="145">
@@ -9303,16 +9303,16 @@
         </is>
       </c>
       <c r="D145" s="30" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="E145" s="30" t="n">
-        <v>-31</v>
+        <v>-73</v>
       </c>
       <c r="F145" s="38" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G145" s="30" t="n">
-        <v>724</v>
+        <v>774</v>
       </c>
     </row>
     <row r="146">
@@ -9327,16 +9327,16 @@
         </is>
       </c>
       <c r="D146" s="30" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E146" s="30" t="n">
-        <v>-19</v>
+        <v>-42</v>
       </c>
       <c r="F146" s="38" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G146" s="30" t="n">
-        <v>601</v>
+        <v>879</v>
       </c>
     </row>
     <row r="147">
@@ -9351,16 +9351,16 @@
         </is>
       </c>
       <c r="D147" s="30" t="n">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="E147" s="30" t="n">
-        <v>-83</v>
+        <v>-183</v>
       </c>
       <c r="F147" s="38" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G147" s="30" t="n">
-        <v>2531</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="148">
@@ -9375,16 +9375,16 @@
         </is>
       </c>
       <c r="D148" s="30" t="n">
-        <v>149</v>
+        <v>200</v>
       </c>
       <c r="E148" s="30" t="n">
-        <v>-92</v>
+        <v>-144</v>
       </c>
       <c r="F148" s="38" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G148" s="30" t="n">
-        <v>3489</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="149">
@@ -9399,16 +9399,16 @@
         </is>
       </c>
       <c r="D149" s="30" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="E149" s="30" t="n">
-        <v>-15</v>
+        <v>-70</v>
       </c>
       <c r="F149" s="38" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G149" s="30" t="n">
-        <v>862</v>
+        <v>964</v>
       </c>
     </row>
     <row r="150">
@@ -9423,16 +9423,16 @@
         </is>
       </c>
       <c r="D150" s="30" t="n">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="E150" s="30" t="n">
-        <v>-59</v>
+        <v>-86</v>
       </c>
       <c r="F150" s="38" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G150" s="30" t="n">
-        <v>2149</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="151">
@@ -9447,16 +9447,16 @@
         </is>
       </c>
       <c r="D151" s="30" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E151" s="30" t="n">
-        <v>-27</v>
+        <v>-48</v>
       </c>
       <c r="F151" s="38" t="n">
         <v>32</v>
       </c>
       <c r="G151" s="30" t="n">
-        <v>756</v>
+        <v>806</v>
       </c>
     </row>
     <row r="152">
@@ -9471,16 +9471,16 @@
         </is>
       </c>
       <c r="D152" s="30" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E152" s="30" t="n">
-        <v>-17</v>
+        <v>-46</v>
       </c>
       <c r="F152" s="38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G152" s="30" t="n">
-        <v>636</v>
+        <v>915</v>
       </c>
     </row>
     <row r="153">
@@ -9495,16 +9495,16 @@
         </is>
       </c>
       <c r="D153" s="30" t="n">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="E153" s="30" t="n">
-        <v>-82</v>
+        <v>-140</v>
       </c>
       <c r="F153" s="38" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G153" s="30" t="n">
-        <v>2576</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="154">
@@ -9519,16 +9519,16 @@
         </is>
       </c>
       <c r="D154" s="30" t="n">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="E154" s="30" t="n">
-        <v>-97</v>
+        <v>-135</v>
       </c>
       <c r="F154" s="38" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G154" s="30" t="n">
-        <v>3555</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="155">
@@ -9543,16 +9543,16 @@
         </is>
       </c>
       <c r="D155" s="30" t="n">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="E155" s="30" t="n">
-        <v>-39</v>
+        <v>-124</v>
       </c>
       <c r="F155" s="38" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G155" s="30" t="n">
-        <v>893</v>
+        <v>999</v>
       </c>
     </row>
     <row r="156">
@@ -9567,16 +9567,16 @@
         </is>
       </c>
       <c r="D156" s="30" t="n">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="E156" s="30" t="n">
-        <v>-51</v>
+        <v>-96</v>
       </c>
       <c r="F156" s="38" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G156" s="30" t="n">
-        <v>2222</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="157">
@@ -9591,16 +9591,16 @@
         </is>
       </c>
       <c r="D157" s="30" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="E157" s="30" t="n">
-        <v>-32</v>
+        <v>-56</v>
       </c>
       <c r="F157" s="38" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G157" s="30" t="n">
-        <v>774</v>
+        <v>826</v>
       </c>
     </row>
     <row r="158">
@@ -9615,16 +9615,16 @@
         </is>
       </c>
       <c r="D158" s="30" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="E158" s="30" t="n">
-        <v>-27</v>
+        <v>-60</v>
       </c>
       <c r="F158" s="38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G158" s="30" t="n">
-        <v>642</v>
+        <v>920</v>
       </c>
     </row>
     <row r="159">
@@ -9639,16 +9639,16 @@
         </is>
       </c>
       <c r="D159" s="30" t="n">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="E159" s="30" t="n">
-        <v>-76</v>
+        <v>-157</v>
       </c>
       <c r="F159" s="38" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G159" s="30" t="n">
-        <v>2618</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="160">
@@ -9663,16 +9663,16 @@
         </is>
       </c>
       <c r="D160" s="30" t="n">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="E160" s="30" t="n">
-        <v>-94</v>
+        <v>-134</v>
       </c>
       <c r="F160" s="38" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G160" s="30" t="n">
-        <v>3608</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="161">
@@ -9687,16 +9687,16 @@
         </is>
       </c>
       <c r="D161" s="30" t="n">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="E161" s="30" t="n">
-        <v>-44</v>
+        <v>-149</v>
       </c>
       <c r="F161" s="38" t="n">
         <v>62</v>
       </c>
       <c r="G161" s="30" t="n">
-        <v>955</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="162">
@@ -9711,16 +9711,16 @@
         </is>
       </c>
       <c r="D162" s="30" t="n">
-        <v>217</v>
+        <v>321</v>
       </c>
       <c r="E162" s="30" t="n">
-        <v>-81</v>
+        <v>-175</v>
       </c>
       <c r="F162" s="38" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G162" s="30" t="n">
-        <v>2358</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="163">
@@ -9735,16 +9735,16 @@
         </is>
       </c>
       <c r="D163" s="30" t="n">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="E163" s="30" t="n">
-        <v>-46</v>
+        <v>-126</v>
       </c>
       <c r="F163" s="38" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G163" s="30" t="n">
-        <v>843</v>
+        <v>896</v>
       </c>
     </row>
     <row r="164">
@@ -9759,16 +9759,16 @@
         </is>
       </c>
       <c r="D164" s="30" t="n">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E164" s="30" t="n">
-        <v>-47</v>
+        <v>-96</v>
       </c>
       <c r="F164" s="38" t="n">
         <v>25</v>
       </c>
       <c r="G164" s="30" t="n">
-        <v>667</v>
+        <v>945</v>
       </c>
     </row>
     <row r="165">
@@ -9783,16 +9783,16 @@
         </is>
       </c>
       <c r="D165" s="30" t="n">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="E165" s="30" t="n">
-        <v>-109</v>
+        <v>-202</v>
       </c>
       <c r="F165" s="38" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G165" s="30" t="n">
-        <v>2693</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="166">
@@ -9807,16 +9807,16 @@
         </is>
       </c>
       <c r="D166" s="30" t="n">
-        <v>219</v>
+        <v>320</v>
       </c>
       <c r="E166" s="30" t="n">
-        <v>-126</v>
+        <v>-220</v>
       </c>
       <c r="F166" s="38" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G166" s="30" t="n">
-        <v>3701</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="167">
@@ -9831,16 +9831,16 @@
         </is>
       </c>
       <c r="D167" s="30" t="n">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="E167" s="30" t="n">
-        <v>-34</v>
+        <v>-132</v>
       </c>
       <c r="F167" s="38" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G167" s="30" t="n">
-        <v>1030</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="168">
@@ -9855,16 +9855,16 @@
         </is>
       </c>
       <c r="D168" s="30" t="n">
-        <v>180</v>
+        <v>268</v>
       </c>
       <c r="E168" s="30" t="n">
-        <v>-78</v>
+        <v>-159</v>
       </c>
       <c r="F168" s="38" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G168" s="30" t="n">
-        <v>2460</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="169">
@@ -9879,16 +9879,16 @@
         </is>
       </c>
       <c r="D169" s="30" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="E169" s="30" t="n">
-        <v>-36</v>
+        <v>-75</v>
       </c>
       <c r="F169" s="38" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G169" s="30" t="n">
-        <v>900</v>
+        <v>955</v>
       </c>
     </row>
     <row r="170">
@@ -9903,16 +9903,16 @@
         </is>
       </c>
       <c r="D170" s="30" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="E170" s="30" t="n">
-        <v>-83</v>
-      </c>
-      <c r="F170" s="32" t="n">
-        <v>0</v>
+        <v>-132</v>
+      </c>
+      <c r="F170" s="39" t="n">
+        <v>-2</v>
       </c>
       <c r="G170" s="30" t="n">
-        <v>667</v>
+        <v>943</v>
       </c>
     </row>
     <row r="171">
@@ -9927,16 +9927,16 @@
         </is>
       </c>
       <c r="D171" s="30" t="n">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="E171" s="30" t="n">
-        <v>-99</v>
+        <v>-165</v>
       </c>
       <c r="F171" s="38" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G171" s="30" t="n">
-        <v>2790</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="172">
@@ -9951,16 +9951,16 @@
         </is>
       </c>
       <c r="D172" s="30" t="n">
-        <v>243</v>
+        <v>387</v>
       </c>
       <c r="E172" s="30" t="n">
-        <v>-124</v>
+        <v>-256</v>
       </c>
       <c r="F172" s="38" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G172" s="30" t="n">
-        <v>3820</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="173">
@@ -9975,16 +9975,16 @@
         </is>
       </c>
       <c r="D173" s="30" t="n">
-        <v>344</v>
+        <v>469</v>
       </c>
       <c r="E173" s="30" t="n">
-        <v>-180</v>
+        <v>-302</v>
       </c>
       <c r="F173" s="38" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G173" s="30" t="n">
-        <v>1194</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="174">
@@ -9999,16 +9999,16 @@
         </is>
       </c>
       <c r="D174" s="30" t="n">
-        <v>187</v>
+        <v>260</v>
       </c>
       <c r="E174" s="30" t="n">
-        <v>-84</v>
+        <v>-155</v>
       </c>
       <c r="F174" s="38" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G174" s="30" t="n">
-        <v>2563</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="175">
@@ -10023,16 +10023,16 @@
         </is>
       </c>
       <c r="D175" s="30" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="E175" s="30" t="n">
-        <v>-37</v>
+        <v>-87</v>
       </c>
       <c r="F175" s="38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G175" s="30" t="n">
-        <v>939</v>
+        <v>995</v>
       </c>
     </row>
     <row r="176">
@@ -10047,16 +10047,16 @@
         </is>
       </c>
       <c r="D176" s="30" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E176" s="30" t="n">
-        <v>-25</v>
+        <v>-67</v>
       </c>
       <c r="F176" s="38" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G176" s="30" t="n">
-        <v>701</v>
+        <v>971</v>
       </c>
     </row>
     <row r="177">
@@ -10071,16 +10071,16 @@
         </is>
       </c>
       <c r="D177" s="30" t="n">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="E177" s="30" t="n">
-        <v>-127</v>
+        <v>-190</v>
       </c>
       <c r="F177" s="38" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G177" s="30" t="n">
-        <v>2853</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="178">
@@ -10095,16 +10095,16 @@
         </is>
       </c>
       <c r="D178" s="30" t="n">
-        <v>181</v>
+        <v>327</v>
       </c>
       <c r="E178" s="30" t="n">
-        <v>-144</v>
+        <v>-298</v>
       </c>
       <c r="F178" s="38" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G178" s="30" t="n">
-        <v>3857</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="179">
@@ -10119,16 +10119,16 @@
         </is>
       </c>
       <c r="D179" s="30" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="E179" s="30" t="n">
-        <v>-78</v>
+        <v>-182</v>
       </c>
       <c r="F179" s="38" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G179" s="30" t="n">
-        <v>1249</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="180">
@@ -10143,16 +10143,16 @@
         </is>
       </c>
       <c r="D180" s="30" t="n">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="E180" s="30" t="n">
-        <v>-80</v>
+        <v>-154</v>
       </c>
       <c r="F180" s="38" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G180" s="30" t="n">
-        <v>2662</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="181">
@@ -10167,16 +10167,16 @@
         </is>
       </c>
       <c r="D181" s="30" t="n">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="E181" s="30" t="n">
-        <v>-167</v>
+        <v>-225</v>
       </c>
       <c r="F181" s="38" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G181" s="30" t="n">
-        <v>1001</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="182">
@@ -10191,16 +10191,16 @@
         </is>
       </c>
       <c r="D182" s="30" t="n">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="E182" s="30" t="n">
-        <v>-31</v>
+        <v>-109</v>
       </c>
       <c r="F182" s="38" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G182" s="30" t="n">
-        <v>732</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="183">
@@ -10215,16 +10215,16 @@
         </is>
       </c>
       <c r="D183" s="30" t="n">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="E183" s="30" t="n">
-        <v>-91</v>
+        <v>-159</v>
       </c>
       <c r="F183" s="38" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G183" s="30" t="n">
-        <v>2906</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="184">
@@ -10239,16 +10239,16 @@
         </is>
       </c>
       <c r="D184" s="30" t="n">
-        <v>199</v>
+        <v>324</v>
       </c>
       <c r="E184" s="30" t="n">
-        <v>-146</v>
+        <v>-266</v>
       </c>
       <c r="F184" s="38" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G184" s="30" t="n">
-        <v>3910</v>
+        <v>4070</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -295,6 +295,9 @@
     <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -313,12 +316,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -718,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L34"/>
+  <dimension ref="B2:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.2" customWidth="1" min="1" max="1"/>
@@ -1097,48 +1095,48 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>65422</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>56392</v>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>9030</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>6549</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>7469</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>-920</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>71971</v>
-      </c>
-      <c r="J16" s="19" t="n">
-        <v>63861</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>8110</v>
-      </c>
-      <c r="L16" s="23" t="inlineStr">
-        <is>
-          <t>전년초과 ▲</t>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>소노벨 양평</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>414</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>425</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>466</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>502</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>-36</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>전년미달 ▼</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>※ FIT=영업자료(대) 03일반=GS(OTA+G-OTA)+기타(홈페이지·제휴사·일반). 제휴사·일반 코드는 온라인팀 raw_db엔 거의 없어 BSR(전채널) 대비 미달</t>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>델피노</t>
         </is>
       </c>
       <c r="C17" s="9" t="n">
@@ -1624,7 +1622,7 @@
       <c r="G29" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="H29" s="25" t="n">
+      <c r="H29" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
@@ -1834,6 +1832,52 @@
       <c r="L34" s="13" t="inlineStr">
         <is>
           <t>전년초과 ▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>65422</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>56392</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>9030</v>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>6549</v>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>7469</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>-920</v>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v>71971</v>
+      </c>
+      <c r="J35" s="20" t="n">
+        <v>63861</v>
+      </c>
+      <c r="K35" s="21" t="n">
+        <v>8110</v>
+      </c>
+      <c r="L35" s="24" t="inlineStr">
+        <is>
+          <t>전년초과 ▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>※ FIT=영업자료(대) 03일반=GS(OTA+G-OTA)+기타(홈페이지·제휴사·일반). 제휴사·일반 코드는 온라인팀 raw_db엔 거의 없어 BSR(전채널) 대비 미달</t>
         </is>
       </c>
     </row>

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -760,7 +760,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="4">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>978</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>168</v>
@@ -1098,13 +1098,13 @@
         <v>-124</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>1270</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>8757</v>
+        <v>8758</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>7808</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>762</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>-98</v>
+        <v>-99</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>9421</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="C35" s="23" t="n">
-        <v>82560</v>
+        <v>82559</v>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="I35" s="23" t="n">
-        <v>90787</v>
+        <v>90786</v>
       </c>
       <c r="J35" s="24" t="inlineStr">
         <is>
@@ -1944,22 +1944,22 @@
         <v>-1456</v>
       </c>
       <c r="F36" s="25" t="n">
-        <v>7782</v>
+        <v>7781</v>
       </c>
       <c r="G36" s="25" t="n">
         <v>10235</v>
       </c>
       <c r="H36" s="30" t="n">
-        <v>-2453</v>
+        <v>-2454</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>85180</v>
+        <v>85179</v>
       </c>
       <c r="J36" s="23" t="n">
         <v>89089</v>
       </c>
       <c r="K36" s="29" t="n">
-        <v>-3909</v>
+        <v>-3910</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
@@ -2737,13 +2737,13 @@
         <v>-10</v>
       </c>
       <c r="X6" s="34" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y6" s="34" t="n">
         <v>258</v>
       </c>
       <c r="Z6" s="35" t="n">
-        <v>-193</v>
+        <v>-194</v>
       </c>
       <c r="AA6" s="34" t="n">
         <v>12</v>
@@ -2899,13 +2899,13 @@
         <v>-1</v>
       </c>
       <c r="BZ6" s="38" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="CA6" s="38" t="n">
         <v>1362</v>
       </c>
       <c r="CB6" s="39" t="n">
-        <v>-796</v>
+        <v>-797</v>
       </c>
     </row>
     <row r="7">
@@ -3924,13 +3924,13 @@
         <v>5</v>
       </c>
       <c r="R11" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11" s="34" t="n">
         <v>6</v>
       </c>
       <c r="T11" s="35" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U11" s="34" t="n">
         <v>3</v>
@@ -3978,13 +3978,13 @@
         <v>-30</v>
       </c>
       <c r="AJ11" s="34" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AK11" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL11" s="37" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AM11" s="34" t="n">
         <v>9</v>
@@ -4906,13 +4906,13 @@
         <v>-11</v>
       </c>
       <c r="X15" s="34" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y15" s="34" t="n">
         <v>96</v>
       </c>
       <c r="Z15" s="37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA15" s="34" t="n">
         <v>38</v>
@@ -5068,13 +5068,13 @@
         <v>2</v>
       </c>
       <c r="BZ15" s="38" t="n">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="CA15" s="38" t="n">
         <v>973</v>
       </c>
       <c r="CB15" s="40" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16">
@@ -5870,13 +5870,13 @@
         <v>-13</v>
       </c>
       <c r="X19" s="34" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y19" s="34" t="n">
         <v>195</v>
       </c>
       <c r="Z19" s="35" t="n">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="AA19" s="34" t="n">
         <v>18</v>
@@ -6032,13 +6032,13 @@
         <v>0</v>
       </c>
       <c r="BZ19" s="38" t="n">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="CA19" s="38" t="n">
         <v>2137</v>
       </c>
       <c r="CB19" s="39" t="n">
-        <v>-705</v>
+        <v>-706</v>
       </c>
     </row>
     <row r="20">
@@ -6111,13 +6111,13 @@
         <v>-1</v>
       </c>
       <c r="X20" s="34" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y20" s="34" t="n">
         <v>248</v>
       </c>
       <c r="Z20" s="35" t="n">
-        <v>-98</v>
+        <v>-97</v>
       </c>
       <c r="AA20" s="34" t="n">
         <v>35</v>
@@ -6273,13 +6273,13 @@
         <v>2</v>
       </c>
       <c r="BZ20" s="38" t="n">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="CA20" s="38" t="n">
         <v>2558</v>
       </c>
       <c r="CB20" s="39" t="n">
-        <v>-904</v>
+        <v>-903</v>
       </c>
     </row>
     <row r="21">
@@ -6352,13 +6352,13 @@
         <v>14</v>
       </c>
       <c r="X21" s="34" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Y21" s="34" t="n">
         <v>191</v>
       </c>
       <c r="Z21" s="37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA21" s="34" t="n">
         <v>66</v>
@@ -6514,13 +6514,13 @@
         <v>2</v>
       </c>
       <c r="BZ21" s="38" t="n">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="CA21" s="38" t="n">
         <v>2151</v>
       </c>
       <c r="CB21" s="39" t="n">
-        <v>-248</v>
+        <v>-247</v>
       </c>
     </row>
     <row r="22">
@@ -6593,13 +6593,13 @@
         <v>4</v>
       </c>
       <c r="X22" s="34" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Y22" s="34" t="n">
         <v>152</v>
       </c>
-      <c r="Z22" s="36" t="n">
-        <v>0</v>
+      <c r="Z22" s="37" t="n">
+        <v>2</v>
       </c>
       <c r="AA22" s="34" t="n">
         <v>55</v>
@@ -6755,13 +6755,13 @@
         <v>2</v>
       </c>
       <c r="BZ22" s="38" t="n">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="CA22" s="38" t="n">
         <v>1782</v>
       </c>
       <c r="CB22" s="39" t="n">
-        <v>-62</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="23">
@@ -7075,13 +7075,13 @@
         <v>-13</v>
       </c>
       <c r="X24" s="34" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y24" s="34" t="n">
         <v>208</v>
       </c>
       <c r="Z24" s="35" t="n">
-        <v>-100</v>
+        <v>-101</v>
       </c>
       <c r="AA24" s="34" t="n">
         <v>20</v>
@@ -7237,13 +7237,13 @@
         <v>5</v>
       </c>
       <c r="BZ24" s="38" t="n">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="CA24" s="38" t="n">
         <v>2625</v>
       </c>
       <c r="CB24" s="39" t="n">
-        <v>-1306</v>
+        <v>-1307</v>
       </c>
     </row>
     <row r="25">
@@ -7316,13 +7316,13 @@
         <v>-5</v>
       </c>
       <c r="X25" s="34" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y25" s="34" t="n">
         <v>258</v>
       </c>
       <c r="Z25" s="35" t="n">
-        <v>-51</v>
+        <v>-50</v>
       </c>
       <c r="AA25" s="34" t="n">
         <v>21</v>
@@ -7478,13 +7478,13 @@
         <v>3</v>
       </c>
       <c r="BZ25" s="38" t="n">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="CA25" s="38" t="n">
         <v>2630</v>
       </c>
       <c r="CB25" s="39" t="n">
-        <v>-1044</v>
+        <v>-1043</v>
       </c>
     </row>
     <row r="26">
@@ -7557,13 +7557,13 @@
         <v>4</v>
       </c>
       <c r="X26" s="34" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Y26" s="34" t="n">
         <v>235</v>
       </c>
       <c r="Z26" s="37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA26" s="34" t="n">
         <v>83</v>
@@ -7719,13 +7719,13 @@
         <v>-6</v>
       </c>
       <c r="BZ26" s="38" t="n">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="CA26" s="38" t="n">
         <v>2522</v>
       </c>
       <c r="CB26" s="40" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27">
@@ -8039,13 +8039,13 @@
         <v>-2</v>
       </c>
       <c r="X28" s="34" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Y28" s="34" t="n">
         <v>100</v>
       </c>
       <c r="Z28" s="37" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA28" s="34" t="n">
         <v>78</v>
@@ -8201,13 +8201,13 @@
         <v>-5</v>
       </c>
       <c r="BZ28" s="38" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="CA28" s="38" t="n">
         <v>1818</v>
       </c>
       <c r="CB28" s="40" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
@@ -8521,13 +8521,13 @@
         <v>-10</v>
       </c>
       <c r="X30" s="34" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y30" s="34" t="n">
         <v>192</v>
       </c>
       <c r="Z30" s="35" t="n">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="AA30" s="34" t="n">
         <v>28</v>
@@ -8683,13 +8683,13 @@
         <v>3</v>
       </c>
       <c r="BZ30" s="38" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="CA30" s="38" t="n">
         <v>1493</v>
       </c>
       <c r="CB30" s="39" t="n">
-        <v>-348</v>
+        <v>-349</v>
       </c>
     </row>
     <row r="31">
@@ -8762,13 +8762,13 @@
         <v>-22</v>
       </c>
       <c r="X31" s="34" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y31" s="34" t="n">
         <v>142</v>
       </c>
       <c r="Z31" s="37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA31" s="34" t="n">
         <v>63</v>
@@ -8924,13 +8924,13 @@
         <v>-1</v>
       </c>
       <c r="BZ31" s="38" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="CA31" s="38" t="n">
         <v>1314</v>
       </c>
       <c r="CB31" s="39" t="n">
-        <v>-236</v>
+        <v>-235</v>
       </c>
     </row>
     <row r="32">
@@ -9003,13 +9003,13 @@
         <v>14</v>
       </c>
       <c r="X32" s="34" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y32" s="34" t="n">
         <v>155</v>
       </c>
       <c r="Z32" s="37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA32" s="34" t="n">
         <v>35</v>
@@ -9165,13 +9165,13 @@
         <v>0</v>
       </c>
       <c r="BZ32" s="38" t="n">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="CA32" s="38" t="n">
         <v>1412</v>
       </c>
       <c r="CB32" s="39" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
     </row>
     <row r="33">
@@ -9485,13 +9485,13 @@
         <v>6</v>
       </c>
       <c r="X34" s="34" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Y34" s="34" t="n">
         <v>142</v>
       </c>
       <c r="Z34" s="37" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AA34" s="34" t="n">
         <v>57</v>
@@ -9647,13 +9647,13 @@
         <v>1</v>
       </c>
       <c r="BZ34" s="38" t="n">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="CA34" s="38" t="n">
         <v>1696</v>
       </c>
       <c r="CB34" s="40" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35">
@@ -10664,13 +10664,13 @@
         <v>-108</v>
       </c>
       <c r="R6" s="34" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="S6" s="34" t="n">
         <v>1268</v>
       </c>
       <c r="T6" s="35" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="U6" s="34" t="n">
         <v>655</v>
@@ -10844,13 +10844,13 @@
         <v>27</v>
       </c>
       <c r="BZ6" s="38" t="n">
-        <v>90787</v>
+        <v>90786</v>
       </c>
       <c r="CA6" s="38" t="n">
         <v>87854</v>
       </c>
       <c r="CB6" s="40" t="n">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="7">
@@ -10905,13 +10905,13 @@
         <v>-105</v>
       </c>
       <c r="R7" s="34" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="S7" s="34" t="n">
         <v>1266</v>
       </c>
       <c r="T7" s="35" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="U7" s="34" t="n">
         <v>653</v>
@@ -10923,13 +10923,13 @@
         <v>-99</v>
       </c>
       <c r="X7" s="34" t="n">
-        <v>9356</v>
+        <v>9357</v>
       </c>
       <c r="Y7" s="34" t="n">
         <v>8154</v>
       </c>
       <c r="Z7" s="37" t="n">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="AA7" s="34" t="n">
         <v>4656</v>
@@ -11146,13 +11146,13 @@
         <v>-109</v>
       </c>
       <c r="R8" s="34" t="n">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="S8" s="34" t="n">
         <v>1269</v>
       </c>
       <c r="T8" s="35" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="U8" s="34" t="n">
         <v>653</v>
@@ -11164,13 +11164,13 @@
         <v>-93</v>
       </c>
       <c r="X8" s="34" t="n">
-        <v>9248</v>
+        <v>9249</v>
       </c>
       <c r="Y8" s="34" t="n">
         <v>7928</v>
       </c>
       <c r="Z8" s="37" t="n">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="AA8" s="34" t="n">
         <v>4632</v>
@@ -11387,13 +11387,13 @@
         <v>-100</v>
       </c>
       <c r="R9" s="34" t="n">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="S9" s="34" t="n">
         <v>1274</v>
       </c>
       <c r="T9" s="35" t="n">
-        <v>-161</v>
+        <v>-162</v>
       </c>
       <c r="U9" s="34" t="n">
         <v>643</v>
@@ -11405,13 +11405,13 @@
         <v>-94</v>
       </c>
       <c r="X9" s="34" t="n">
-        <v>9120</v>
+        <v>9121</v>
       </c>
       <c r="Y9" s="34" t="n">
         <v>7776</v>
       </c>
       <c r="Z9" s="37" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="AA9" s="34" t="n">
         <v>4595</v>
@@ -11628,13 +11628,13 @@
         <v>-101</v>
       </c>
       <c r="R10" s="34" t="n">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="S10" s="34" t="n">
         <v>1265</v>
       </c>
       <c r="T10" s="35" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="U10" s="34" t="n">
         <v>648</v>
@@ -11646,13 +11646,13 @@
         <v>-71</v>
       </c>
       <c r="X10" s="34" t="n">
-        <v>9061</v>
+        <v>9062</v>
       </c>
       <c r="Y10" s="34" t="n">
         <v>7673</v>
       </c>
       <c r="Z10" s="37" t="n">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AA10" s="34" t="n">
         <v>4553</v>
@@ -11869,13 +11869,13 @@
         <v>-99</v>
       </c>
       <c r="R11" s="34" t="n">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="S11" s="34" t="n">
         <v>1246</v>
       </c>
       <c r="T11" s="35" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="U11" s="34" t="n">
         <v>638</v>
@@ -11887,13 +11887,13 @@
         <v>-63</v>
       </c>
       <c r="X11" s="34" t="n">
-        <v>8979</v>
+        <v>8980</v>
       </c>
       <c r="Y11" s="34" t="n">
         <v>7586</v>
       </c>
       <c r="Z11" s="37" t="n">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="AA11" s="34" t="n">
         <v>4510</v>
@@ -12128,13 +12128,13 @@
         <v>-60</v>
       </c>
       <c r="X12" s="34" t="n">
-        <v>8899</v>
+        <v>8900</v>
       </c>
       <c r="Y12" s="34" t="n">
         <v>7507</v>
       </c>
       <c r="Z12" s="37" t="n">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="AA12" s="34" t="n">
         <v>4458</v>
@@ -12164,13 +12164,13 @@
         <v>-1789</v>
       </c>
       <c r="AJ12" s="34" t="n">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="AK12" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL12" s="37" t="n">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="AM12" s="34" t="n">
         <v>1623</v>
@@ -12369,13 +12369,13 @@
         <v>-58</v>
       </c>
       <c r="X13" s="34" t="n">
-        <v>8743</v>
+        <v>8744</v>
       </c>
       <c r="Y13" s="34" t="n">
         <v>7380</v>
       </c>
       <c r="Z13" s="37" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="AA13" s="34" t="n">
         <v>4380</v>
@@ -12405,13 +12405,13 @@
         <v>-1765</v>
       </c>
       <c r="AJ13" s="34" t="n">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="AK13" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL13" s="37" t="n">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="AM13" s="34" t="n">
         <v>1608</v>
@@ -12610,13 +12610,13 @@
         <v>-36</v>
       </c>
       <c r="X14" s="34" t="n">
-        <v>8641</v>
+        <v>8642</v>
       </c>
       <c r="Y14" s="34" t="n">
         <v>7222</v>
       </c>
       <c r="Z14" s="37" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="AA14" s="34" t="n">
         <v>4324</v>
@@ -12646,13 +12646,13 @@
         <v>-1677</v>
       </c>
       <c r="AJ14" s="34" t="n">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="AK14" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL14" s="37" t="n">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="AM14" s="34" t="n">
         <v>1566</v>
@@ -12851,13 +12851,13 @@
         <v>-46</v>
       </c>
       <c r="X15" s="34" t="n">
-        <v>8482</v>
+        <v>8483</v>
       </c>
       <c r="Y15" s="34" t="n">
         <v>7138</v>
       </c>
       <c r="Z15" s="37" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="AA15" s="34" t="n">
         <v>4259</v>
@@ -12887,13 +12887,13 @@
         <v>-1715</v>
       </c>
       <c r="AJ15" s="34" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="AK15" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL15" s="37" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="AM15" s="34" t="n">
         <v>1527</v>
@@ -13092,13 +13092,13 @@
         <v>-35</v>
       </c>
       <c r="X16" s="34" t="n">
-        <v>8361</v>
+        <v>8363</v>
       </c>
       <c r="Y16" s="34" t="n">
         <v>7042</v>
       </c>
       <c r="Z16" s="37" t="n">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="AA16" s="34" t="n">
         <v>4221</v>
@@ -13128,13 +13128,13 @@
         <v>-1751</v>
       </c>
       <c r="AJ16" s="34" t="n">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="AK16" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL16" s="37" t="n">
-        <v>3452</v>
+        <v>3451</v>
       </c>
       <c r="AM16" s="34" t="n">
         <v>1503</v>
@@ -13254,13 +13254,13 @@
         <v>28</v>
       </c>
       <c r="BZ16" s="38" t="n">
-        <v>81772</v>
+        <v>81773</v>
       </c>
       <c r="CA16" s="38" t="n">
         <v>76545</v>
       </c>
       <c r="CB16" s="40" t="n">
-        <v>5227</v>
+        <v>5228</v>
       </c>
     </row>
     <row r="17">
@@ -13333,13 +13333,13 @@
         <v>-36</v>
       </c>
       <c r="X17" s="34" t="n">
-        <v>8295</v>
+        <v>8297</v>
       </c>
       <c r="Y17" s="34" t="n">
         <v>6920</v>
       </c>
       <c r="Z17" s="37" t="n">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="AA17" s="34" t="n">
         <v>4171</v>
@@ -13369,13 +13369,13 @@
         <v>-1734</v>
       </c>
       <c r="AJ17" s="34" t="n">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="AK17" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL17" s="37" t="n">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="AM17" s="34" t="n">
         <v>1480</v>
@@ -13495,13 +13495,13 @@
         <v>25</v>
       </c>
       <c r="BZ17" s="38" t="n">
-        <v>80756</v>
+        <v>80757</v>
       </c>
       <c r="CA17" s="38" t="n">
         <v>75180</v>
       </c>
       <c r="CB17" s="40" t="n">
-        <v>5576</v>
+        <v>5577</v>
       </c>
     </row>
     <row r="18">
@@ -13574,13 +13574,13 @@
         <v>-20</v>
       </c>
       <c r="X18" s="34" t="n">
-        <v>8178</v>
+        <v>8180</v>
       </c>
       <c r="Y18" s="34" t="n">
         <v>6793</v>
       </c>
       <c r="Z18" s="37" t="n">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="AA18" s="34" t="n">
         <v>4155</v>
@@ -13610,13 +13610,13 @@
         <v>-1661</v>
       </c>
       <c r="AJ18" s="34" t="n">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="AK18" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL18" s="37" t="n">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="AM18" s="34" t="n">
         <v>1454</v>
@@ -13736,13 +13736,13 @@
         <v>27</v>
       </c>
       <c r="BZ18" s="38" t="n">
-        <v>79806</v>
+        <v>79807</v>
       </c>
       <c r="CA18" s="38" t="n">
         <v>73466</v>
       </c>
       <c r="CB18" s="40" t="n">
-        <v>6340</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="19">
@@ -13815,13 +13815,13 @@
         <v>-7</v>
       </c>
       <c r="X19" s="34" t="n">
-        <v>8109</v>
+        <v>8111</v>
       </c>
       <c r="Y19" s="34" t="n">
         <v>6583</v>
       </c>
       <c r="Z19" s="37" t="n">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="AA19" s="34" t="n">
         <v>4126</v>
@@ -13851,13 +13851,13 @@
         <v>-1605</v>
       </c>
       <c r="AJ19" s="34" t="n">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="AK19" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL19" s="37" t="n">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="AM19" s="34" t="n">
         <v>1418</v>
@@ -13977,13 +13977,13 @@
         <v>30</v>
       </c>
       <c r="BZ19" s="38" t="n">
-        <v>78734</v>
+        <v>78735</v>
       </c>
       <c r="CA19" s="38" t="n">
         <v>71530</v>
       </c>
       <c r="CB19" s="40" t="n">
-        <v>7204</v>
+        <v>7205</v>
       </c>
     </row>
     <row r="20">
@@ -14056,13 +14056,13 @@
         <v>6</v>
       </c>
       <c r="X20" s="34" t="n">
-        <v>7989</v>
+        <v>7992</v>
       </c>
       <c r="Y20" s="34" t="n">
         <v>6388</v>
       </c>
       <c r="Z20" s="37" t="n">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="AA20" s="34" t="n">
         <v>4108</v>
@@ -14092,13 +14092,13 @@
         <v>-1551</v>
       </c>
       <c r="AJ20" s="34" t="n">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="AK20" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL20" s="37" t="n">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="AM20" s="34" t="n">
         <v>1368</v>
@@ -14218,13 +14218,13 @@
         <v>30</v>
       </c>
       <c r="BZ20" s="38" t="n">
-        <v>77302</v>
+        <v>77304</v>
       </c>
       <c r="CA20" s="38" t="n">
         <v>69393</v>
       </c>
       <c r="CB20" s="40" t="n">
-        <v>7909</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="21">
@@ -14297,13 +14297,13 @@
         <v>7</v>
       </c>
       <c r="X21" s="34" t="n">
-        <v>7839</v>
+        <v>7841</v>
       </c>
       <c r="Y21" s="34" t="n">
         <v>6140</v>
       </c>
       <c r="Z21" s="37" t="n">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="AA21" s="34" t="n">
         <v>4073</v>
@@ -14333,13 +14333,13 @@
         <v>-1533</v>
       </c>
       <c r="AJ21" s="34" t="n">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="AK21" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL21" s="37" t="n">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="AM21" s="34" t="n">
         <v>1288</v>
@@ -14459,13 +14459,13 @@
         <v>28</v>
       </c>
       <c r="BZ21" s="38" t="n">
-        <v>75648</v>
+        <v>75649</v>
       </c>
       <c r="CA21" s="38" t="n">
         <v>66835</v>
       </c>
       <c r="CB21" s="40" t="n">
-        <v>8813</v>
+        <v>8814</v>
       </c>
     </row>
     <row r="22">
@@ -14538,13 +14538,13 @@
         <v>-7</v>
       </c>
       <c r="X22" s="34" t="n">
-        <v>7626</v>
+        <v>7627</v>
       </c>
       <c r="Y22" s="34" t="n">
         <v>5949</v>
       </c>
       <c r="Z22" s="37" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="AA22" s="34" t="n">
         <v>4007</v>
@@ -14574,13 +14574,13 @@
         <v>-1497</v>
       </c>
       <c r="AJ22" s="34" t="n">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="AK22" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL22" s="37" t="n">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="AM22" s="34" t="n">
         <v>1235</v>
@@ -14779,13 +14779,13 @@
         <v>-11</v>
       </c>
       <c r="X23" s="34" t="n">
-        <v>7474</v>
+        <v>7473</v>
       </c>
       <c r="Y23" s="34" t="n">
         <v>5797</v>
       </c>
       <c r="Z23" s="37" t="n">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="AA23" s="34" t="n">
         <v>3952</v>
@@ -14815,13 +14815,13 @@
         <v>-1477</v>
       </c>
       <c r="AJ23" s="34" t="n">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="AK23" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL23" s="37" t="n">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="AM23" s="34" t="n">
         <v>1204</v>
@@ -14941,13 +14941,13 @@
         <v>24</v>
       </c>
       <c r="BZ23" s="38" t="n">
-        <v>72025</v>
+        <v>72023</v>
       </c>
       <c r="CA23" s="38" t="n">
         <v>62902</v>
       </c>
       <c r="CB23" s="40" t="n">
-        <v>9123</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="24">
@@ -15020,13 +15020,13 @@
         <v>-4</v>
       </c>
       <c r="X24" s="34" t="n">
-        <v>7343</v>
+        <v>7342</v>
       </c>
       <c r="Y24" s="34" t="n">
         <v>5633</v>
       </c>
       <c r="Z24" s="37" t="n">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AA24" s="34" t="n">
         <v>3937</v>
@@ -15056,13 +15056,13 @@
         <v>-1340</v>
       </c>
       <c r="AJ24" s="34" t="n">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="AK24" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL24" s="37" t="n">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="AM24" s="34" t="n">
         <v>1152</v>
@@ -15182,13 +15182,13 @@
         <v>25</v>
       </c>
       <c r="BZ24" s="38" t="n">
-        <v>71000</v>
+        <v>70998</v>
       </c>
       <c r="CA24" s="38" t="n">
         <v>60965</v>
       </c>
       <c r="CB24" s="40" t="n">
-        <v>10035</v>
+        <v>10033</v>
       </c>
     </row>
     <row r="25">
@@ -15297,13 +15297,13 @@
         <v>-1096</v>
       </c>
       <c r="AJ25" s="34" t="n">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="AK25" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL25" s="37" t="n">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="AM25" s="34" t="n">
         <v>1092</v>
@@ -15423,13 +15423,13 @@
         <v>20</v>
       </c>
       <c r="BZ25" s="38" t="n">
-        <v>69681</v>
+        <v>69680</v>
       </c>
       <c r="CA25" s="38" t="n">
         <v>58340</v>
       </c>
       <c r="CB25" s="40" t="n">
-        <v>11341</v>
+        <v>11340</v>
       </c>
     </row>
     <row r="26">
@@ -15502,13 +15502,13 @@
         <v>14</v>
       </c>
       <c r="X26" s="34" t="n">
-        <v>7028</v>
+        <v>7027</v>
       </c>
       <c r="Y26" s="34" t="n">
         <v>5167</v>
       </c>
       <c r="Z26" s="37" t="n">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="AA26" s="34" t="n">
         <v>3896</v>
@@ -15538,13 +15538,13 @@
         <v>-954</v>
       </c>
       <c r="AJ26" s="34" t="n">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="AK26" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL26" s="37" t="n">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="AM26" s="34" t="n">
         <v>1021</v>
@@ -15664,13 +15664,13 @@
         <v>17</v>
       </c>
       <c r="BZ26" s="38" t="n">
-        <v>68095</v>
+        <v>68093</v>
       </c>
       <c r="CA26" s="38" t="n">
         <v>55710</v>
       </c>
       <c r="CB26" s="40" t="n">
-        <v>12385</v>
+        <v>12383</v>
       </c>
     </row>
     <row r="27">
@@ -15743,13 +15743,13 @@
         <v>10</v>
       </c>
       <c r="X27" s="34" t="n">
-        <v>6779</v>
+        <v>6777</v>
       </c>
       <c r="Y27" s="34" t="n">
         <v>4932</v>
       </c>
       <c r="Z27" s="37" t="n">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AA27" s="34" t="n">
         <v>3813</v>
@@ -15779,13 +15779,13 @@
         <v>-809</v>
       </c>
       <c r="AJ27" s="34" t="n">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="AK27" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL27" s="37" t="n">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="AM27" s="34" t="n">
         <v>980</v>
@@ -15905,13 +15905,13 @@
         <v>23</v>
       </c>
       <c r="BZ27" s="38" t="n">
-        <v>65404</v>
+        <v>65401</v>
       </c>
       <c r="CA27" s="38" t="n">
         <v>53188</v>
       </c>
       <c r="CB27" s="40" t="n">
-        <v>12216</v>
+        <v>12213</v>
       </c>
     </row>
     <row r="28">
@@ -15984,13 +15984,13 @@
         <v>25</v>
       </c>
       <c r="X28" s="34" t="n">
-        <v>6489</v>
+        <v>6487</v>
       </c>
       <c r="Y28" s="34" t="n">
         <v>4684</v>
       </c>
       <c r="Z28" s="37" t="n">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="AA28" s="34" t="n">
         <v>3719</v>
@@ -16020,13 +16020,13 @@
         <v>-569</v>
       </c>
       <c r="AJ28" s="34" t="n">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="AK28" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL28" s="37" t="n">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="AM28" s="34" t="n">
         <v>919</v>
@@ -16146,13 +16146,13 @@
         <v>24</v>
       </c>
       <c r="BZ28" s="38" t="n">
-        <v>63535</v>
+        <v>63532</v>
       </c>
       <c r="CA28" s="38" t="n">
         <v>50712</v>
       </c>
       <c r="CB28" s="40" t="n">
-        <v>12823</v>
+        <v>12820</v>
       </c>
     </row>
     <row r="29">
@@ -16225,13 +16225,13 @@
         <v>27</v>
       </c>
       <c r="X29" s="34" t="n">
-        <v>6041</v>
+        <v>6038</v>
       </c>
       <c r="Y29" s="34" t="n">
         <v>4584</v>
       </c>
       <c r="Z29" s="37" t="n">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="AA29" s="34" t="n">
         <v>3641</v>
@@ -16261,13 +16261,13 @@
         <v>-570</v>
       </c>
       <c r="AJ29" s="34" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="AK29" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL29" s="37" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="AM29" s="34" t="n">
         <v>848</v>
@@ -16387,13 +16387,13 @@
         <v>29</v>
       </c>
       <c r="BZ29" s="38" t="n">
-        <v>61507</v>
+        <v>61503</v>
       </c>
       <c r="CA29" s="38" t="n">
         <v>48894</v>
       </c>
       <c r="CB29" s="40" t="n">
-        <v>12613</v>
+        <v>12609</v>
       </c>
     </row>
     <row r="30">
@@ -16466,13 +16466,13 @@
         <v>24</v>
       </c>
       <c r="X30" s="34" t="n">
-        <v>5825</v>
+        <v>5822</v>
       </c>
       <c r="Y30" s="34" t="n">
         <v>4525</v>
       </c>
       <c r="Z30" s="37" t="n">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="AA30" s="34" t="n">
         <v>3593</v>
@@ -16502,13 +16502,13 @@
         <v>-562</v>
       </c>
       <c r="AJ30" s="34" t="n">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="AK30" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL30" s="37" t="n">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="AM30" s="34" t="n">
         <v>827</v>
@@ -16628,13 +16628,13 @@
         <v>27</v>
       </c>
       <c r="BZ30" s="38" t="n">
-        <v>60192</v>
+        <v>60188</v>
       </c>
       <c r="CA30" s="38" t="n">
         <v>47755</v>
       </c>
       <c r="CB30" s="40" t="n">
-        <v>12437</v>
+        <v>12433</v>
       </c>
     </row>
     <row r="31">
@@ -16707,13 +16707,13 @@
         <v>34</v>
       </c>
       <c r="X31" s="34" t="n">
-        <v>5724</v>
+        <v>5722</v>
       </c>
       <c r="Y31" s="34" t="n">
         <v>4333</v>
       </c>
       <c r="Z31" s="37" t="n">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="AA31" s="34" t="n">
         <v>3565</v>
@@ -16743,13 +16743,13 @@
         <v>-476</v>
       </c>
       <c r="AJ31" s="34" t="n">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="AK31" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL31" s="37" t="n">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="AM31" s="34" t="n">
         <v>794</v>
@@ -16869,13 +16869,13 @@
         <v>24</v>
       </c>
       <c r="BZ31" s="38" t="n">
-        <v>59047</v>
+        <v>59044</v>
       </c>
       <c r="CA31" s="38" t="n">
         <v>46262</v>
       </c>
       <c r="CB31" s="40" t="n">
-        <v>12785</v>
+        <v>12782</v>
       </c>
     </row>
     <row r="32">
@@ -16948,13 +16948,13 @@
         <v>56</v>
       </c>
       <c r="X32" s="34" t="n">
-        <v>5568</v>
+        <v>5565</v>
       </c>
       <c r="Y32" s="34" t="n">
         <v>4191</v>
       </c>
       <c r="Z32" s="37" t="n">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="AA32" s="34" t="n">
         <v>3502</v>
@@ -16984,13 +16984,13 @@
         <v>-416</v>
       </c>
       <c r="AJ32" s="34" t="n">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="AK32" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL32" s="37" t="n">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="AM32" s="34" t="n">
         <v>768</v>
@@ -17110,13 +17110,13 @@
         <v>25</v>
       </c>
       <c r="BZ32" s="38" t="n">
-        <v>57969</v>
+        <v>57965</v>
       </c>
       <c r="CA32" s="38" t="n">
         <v>44948</v>
       </c>
       <c r="CB32" s="40" t="n">
-        <v>13021</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="33">
@@ -17189,13 +17189,13 @@
         <v>42</v>
       </c>
       <c r="X33" s="34" t="n">
-        <v>5401</v>
+        <v>5399</v>
       </c>
       <c r="Y33" s="34" t="n">
         <v>4036</v>
       </c>
       <c r="Z33" s="37" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="AA33" s="34" t="n">
         <v>3467</v>
@@ -17225,13 +17225,13 @@
         <v>-329</v>
       </c>
       <c r="AJ33" s="34" t="n">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="AK33" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL33" s="37" t="n">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="AM33" s="34" t="n">
         <v>738</v>
@@ -17351,13 +17351,13 @@
         <v>25</v>
       </c>
       <c r="BZ33" s="38" t="n">
-        <v>56637</v>
+        <v>56634</v>
       </c>
       <c r="CA33" s="38" t="n">
         <v>43536</v>
       </c>
       <c r="CB33" s="40" t="n">
-        <v>13101</v>
+        <v>13098</v>
       </c>
     </row>
     <row r="34">
@@ -17430,13 +17430,13 @@
         <v>53</v>
       </c>
       <c r="X34" s="34" t="n">
-        <v>5170</v>
+        <v>5168</v>
       </c>
       <c r="Y34" s="34" t="n">
         <v>3896</v>
       </c>
       <c r="Z34" s="37" t="n">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AA34" s="34" t="n">
         <v>3400</v>
@@ -17466,13 +17466,13 @@
         <v>-251</v>
       </c>
       <c r="AJ34" s="34" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="AK34" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" s="37" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="AM34" s="34" t="n">
         <v>704</v>
@@ -17592,13 +17592,13 @@
         <v>22</v>
       </c>
       <c r="BZ34" s="38" t="n">
-        <v>55047</v>
+        <v>55044</v>
       </c>
       <c r="CA34" s="38" t="n">
         <v>42121</v>
       </c>
       <c r="CB34" s="40" t="n">
-        <v>12926</v>
+        <v>12923</v>
       </c>
     </row>
     <row r="35">
@@ -17671,13 +17671,13 @@
         <v>47</v>
       </c>
       <c r="X35" s="34" t="n">
-        <v>4913</v>
+        <v>4912</v>
       </c>
       <c r="Y35" s="34" t="n">
         <v>3754</v>
       </c>
       <c r="Z35" s="37" t="n">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="AA35" s="34" t="n">
         <v>3343</v>
@@ -17707,13 +17707,13 @@
         <v>-214</v>
       </c>
       <c r="AJ35" s="34" t="n">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="AK35" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AL35" s="37" t="n">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="AM35" s="34" t="n">
         <v>657</v>
@@ -17833,13 +17833,13 @@
         <v>21</v>
       </c>
       <c r="BZ35" s="38" t="n">
-        <v>52984</v>
+        <v>52982</v>
       </c>
       <c r="CA35" s="38" t="n">
         <v>40425</v>
       </c>
       <c r="CB35" s="40" t="n">
-        <v>12559</v>
+        <v>12557</v>
       </c>
     </row>
   </sheetData>
@@ -18123,7 +18123,7 @@
         <v>154</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>4913</v>
+        <v>4912</v>
       </c>
     </row>
     <row r="13">
@@ -18219,7 +18219,7 @@
         <v>197</v>
       </c>
       <c r="G16" s="34" t="n">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="17">
@@ -18714,16 +18714,16 @@
         </is>
       </c>
       <c r="D37" s="34" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E37" s="34" t="n">
         <v>-366</v>
       </c>
       <c r="F37" s="42" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G37" s="34" t="n">
-        <v>5170</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="38">
@@ -18819,7 +18819,7 @@
         <v>184</v>
       </c>
       <c r="G41" s="34" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="42">
@@ -19314,16 +19314,16 @@
         </is>
       </c>
       <c r="D62" s="34" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E62" s="34" t="n">
-        <v>-385</v>
+        <v>-384</v>
       </c>
       <c r="F62" s="42" t="n">
         <v>231</v>
       </c>
       <c r="G62" s="34" t="n">
-        <v>5401</v>
+        <v>5399</v>
       </c>
     </row>
     <row r="63">
@@ -19419,7 +19419,7 @@
         <v>178</v>
       </c>
       <c r="G66" s="34" t="n">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="67">
@@ -19914,16 +19914,16 @@
         </is>
       </c>
       <c r="D87" s="34" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E87" s="34" t="n">
         <v>-331</v>
       </c>
       <c r="F87" s="42" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G87" s="34" t="n">
-        <v>5568</v>
+        <v>5565</v>
       </c>
     </row>
     <row r="88">
@@ -20019,7 +20019,7 @@
         <v>103</v>
       </c>
       <c r="G91" s="34" t="n">
-        <v>2238</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="92">
@@ -20514,16 +20514,16 @@
         </is>
       </c>
       <c r="D112" s="34" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E112" s="34" t="n">
-        <v>-348</v>
+        <v>-346</v>
       </c>
       <c r="F112" s="42" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G112" s="34" t="n">
-        <v>5724</v>
+        <v>5722</v>
       </c>
     </row>
     <row r="113">
@@ -20619,7 +20619,7 @@
         <v>58</v>
       </c>
       <c r="G116" s="34" t="n">
-        <v>2296</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="117">
@@ -21114,16 +21114,16 @@
         </is>
       </c>
       <c r="D137" s="34" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E137" s="34" t="n">
         <v>-289</v>
       </c>
       <c r="F137" s="42" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G137" s="34" t="n">
-        <v>5825</v>
+        <v>5822</v>
       </c>
     </row>
     <row r="138">
@@ -21219,7 +21219,7 @@
         <v>71</v>
       </c>
       <c r="G141" s="34" t="n">
-        <v>2367</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="142">
@@ -21714,16 +21714,16 @@
         </is>
       </c>
       <c r="D162" s="34" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E162" s="34" t="n">
-        <v>-387</v>
+        <v>-386</v>
       </c>
       <c r="F162" s="42" t="n">
         <v>216</v>
       </c>
       <c r="G162" s="34" t="n">
-        <v>6041</v>
+        <v>6038</v>
       </c>
     </row>
     <row r="163">
@@ -21819,7 +21819,7 @@
         <v>66</v>
       </c>
       <c r="G166" s="34" t="n">
-        <v>2433</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="167">
@@ -22314,16 +22314,16 @@
         </is>
       </c>
       <c r="D187" s="34" t="n">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="E187" s="34" t="n">
         <v>-510</v>
       </c>
       <c r="F187" s="42" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G187" s="34" t="n">
-        <v>6489</v>
+        <v>6487</v>
       </c>
     </row>
     <row r="188">
@@ -22419,7 +22419,7 @@
         <v>146</v>
       </c>
       <c r="G191" s="34" t="n">
-        <v>2579</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="192">
@@ -22914,16 +22914,16 @@
         </is>
       </c>
       <c r="D212" s="34" t="n">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E212" s="34" t="n">
-        <v>-404</v>
+        <v>-402</v>
       </c>
       <c r="F212" s="42" t="n">
         <v>290</v>
       </c>
       <c r="G212" s="34" t="n">
-        <v>6779</v>
+        <v>6777</v>
       </c>
     </row>
     <row r="213">
@@ -23019,7 +23019,7 @@
         <v>84</v>
       </c>
       <c r="G216" s="34" t="n">
-        <v>2663</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="217">
@@ -23517,13 +23517,13 @@
         <v>729</v>
       </c>
       <c r="E237" s="34" t="n">
-        <v>-480</v>
+        <v>-479</v>
       </c>
       <c r="F237" s="42" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G237" s="34" t="n">
-        <v>7028</v>
+        <v>7027</v>
       </c>
     </row>
     <row r="238">
@@ -23619,7 +23619,7 @@
         <v>58</v>
       </c>
       <c r="G241" s="34" t="n">
-        <v>2721</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="242">
@@ -24114,13 +24114,13 @@
         </is>
       </c>
       <c r="D262" s="34" t="n">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E262" s="34" t="n">
-        <v>-476</v>
+        <v>-474</v>
       </c>
       <c r="F262" s="42" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G262" s="34" t="n">
         <v>7235</v>
@@ -24219,7 +24219,7 @@
         <v>81</v>
       </c>
       <c r="G266" s="34" t="n">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="267">
@@ -24714,16 +24714,16 @@
         </is>
       </c>
       <c r="D287" s="34" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E287" s="34" t="n">
         <v>-382</v>
       </c>
       <c r="F287" s="42" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G287" s="34" t="n">
-        <v>7343</v>
+        <v>7342</v>
       </c>
     </row>
     <row r="288">
@@ -24819,7 +24819,7 @@
         <v>77</v>
       </c>
       <c r="G291" s="34" t="n">
-        <v>2879</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="292">
@@ -25314,16 +25314,16 @@
         </is>
       </c>
       <c r="D312" s="34" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E312" s="34" t="n">
-        <v>-277</v>
+        <v>-276</v>
       </c>
       <c r="F312" s="42" t="n">
         <v>131</v>
       </c>
       <c r="G312" s="34" t="n">
-        <v>7474</v>
+        <v>7473</v>
       </c>
     </row>
     <row r="313">
@@ -25419,7 +25419,7 @@
         <v>69</v>
       </c>
       <c r="G316" s="34" t="n">
-        <v>2948</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="317">
@@ -25914,16 +25914,16 @@
         </is>
       </c>
       <c r="D337" s="34" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E337" s="34" t="n">
-        <v>-290</v>
+        <v>-289</v>
       </c>
       <c r="F337" s="42" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G337" s="34" t="n">
-        <v>7626</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="338">
@@ -26019,7 +26019,7 @@
         <v>127</v>
       </c>
       <c r="G341" s="34" t="n">
-        <v>3075</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="342">
@@ -26514,16 +26514,16 @@
         </is>
       </c>
       <c r="D362" s="34" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E362" s="34" t="n">
         <v>-412</v>
       </c>
       <c r="F362" s="42" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G362" s="34" t="n">
-        <v>7839</v>
+        <v>7841</v>
       </c>
     </row>
     <row r="363">
@@ -26619,7 +26619,7 @@
         <v>112</v>
       </c>
       <c r="G366" s="34" t="n">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="367">
@@ -27114,16 +27114,16 @@
         </is>
       </c>
       <c r="D387" s="34" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E387" s="34" t="n">
-        <v>-333</v>
+        <v>-331</v>
       </c>
       <c r="F387" s="42" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G387" s="34" t="n">
-        <v>7989</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="388">
@@ -27219,7 +27219,7 @@
         <v>40</v>
       </c>
       <c r="G391" s="34" t="n">
-        <v>3227</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="392">
@@ -27717,13 +27717,13 @@
         <v>402</v>
       </c>
       <c r="E412" s="34" t="n">
-        <v>-282</v>
+        <v>-283</v>
       </c>
       <c r="F412" s="42" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G412" s="34" t="n">
-        <v>8109</v>
+        <v>8111</v>
       </c>
     </row>
     <row r="413">
@@ -27819,7 +27819,7 @@
         <v>63</v>
       </c>
       <c r="G416" s="34" t="n">
-        <v>3290</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="417">
@@ -28323,7 +28323,7 @@
         <v>69</v>
       </c>
       <c r="G437" s="34" t="n">
-        <v>8178</v>
+        <v>8180</v>
       </c>
     </row>
     <row r="438">
@@ -28419,7 +28419,7 @@
         <v>46</v>
       </c>
       <c r="G441" s="34" t="n">
-        <v>3336</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="442">
@@ -28923,7 +28923,7 @@
         <v>117</v>
       </c>
       <c r="G462" s="34" t="n">
-        <v>8295</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="463">
@@ -29019,7 +29019,7 @@
         <v>54</v>
       </c>
       <c r="G466" s="34" t="n">
-        <v>3390</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="467">
@@ -29523,7 +29523,7 @@
         <v>66</v>
       </c>
       <c r="G487" s="34" t="n">
-        <v>8361</v>
+        <v>8363</v>
       </c>
     </row>
     <row r="488">
@@ -29619,7 +29619,7 @@
         <v>62</v>
       </c>
       <c r="G491" s="34" t="n">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="492">
@@ -30114,16 +30114,16 @@
         </is>
       </c>
       <c r="D512" s="34" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E512" s="34" t="n">
         <v>-249</v>
       </c>
       <c r="F512" s="42" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G512" s="34" t="n">
-        <v>8482</v>
+        <v>8483</v>
       </c>
     </row>
     <row r="513">
@@ -30219,7 +30219,7 @@
         <v>96</v>
       </c>
       <c r="G516" s="34" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="517">
@@ -30714,16 +30714,16 @@
         </is>
       </c>
       <c r="D537" s="34" t="n">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E537" s="34" t="n">
-        <v>-486</v>
+        <v>-485</v>
       </c>
       <c r="F537" s="42" t="n">
         <v>159</v>
       </c>
       <c r="G537" s="34" t="n">
-        <v>8641</v>
+        <v>8642</v>
       </c>
     </row>
     <row r="538">
@@ -30819,7 +30819,7 @@
         <v>130</v>
       </c>
       <c r="G541" s="34" t="n">
-        <v>3678</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="542">
@@ -31323,7 +31323,7 @@
         <v>102</v>
       </c>
       <c r="G562" s="34" t="n">
-        <v>8743</v>
+        <v>8744</v>
       </c>
     </row>
     <row r="563">
@@ -31419,7 +31419,7 @@
         <v>63</v>
       </c>
       <c r="G566" s="34" t="n">
-        <v>3741</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="567">
@@ -31914,16 +31914,16 @@
         </is>
       </c>
       <c r="D587" s="34" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E587" s="34" t="n">
-        <v>-312</v>
+        <v>-311</v>
       </c>
       <c r="F587" s="42" t="n">
         <v>156</v>
       </c>
       <c r="G587" s="34" t="n">
-        <v>8899</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="588">
@@ -32019,7 +32019,7 @@
         <v>38</v>
       </c>
       <c r="G591" s="34" t="n">
-        <v>3779</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="592">
@@ -32466,16 +32466,16 @@
         </is>
       </c>
       <c r="D610" s="34" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E610" s="34" t="n">
         <v>-60</v>
       </c>
       <c r="F610" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G610" s="34" t="n">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="611">
@@ -32514,16 +32514,16 @@
         </is>
       </c>
       <c r="D612" s="34" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E612" s="34" t="n">
-        <v>-293</v>
+        <v>-292</v>
       </c>
       <c r="F612" s="42" t="n">
         <v>80</v>
       </c>
       <c r="G612" s="34" t="n">
-        <v>8979</v>
+        <v>8980</v>
       </c>
     </row>
     <row r="613">
@@ -32610,13 +32610,13 @@
         </is>
       </c>
       <c r="D616" s="34" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E616" s="34" t="n">
         <v>-90</v>
       </c>
       <c r="F616" s="42" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G616" s="34" t="n">
         <v>3816</v>
@@ -33075,7 +33075,7 @@
         <v>12</v>
       </c>
       <c r="G635" s="34" t="n">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="636">
@@ -33123,7 +33123,7 @@
         <v>82</v>
       </c>
       <c r="G637" s="34" t="n">
-        <v>9061</v>
+        <v>9062</v>
       </c>
     </row>
     <row r="638">
@@ -33675,7 +33675,7 @@
         <v>-2</v>
       </c>
       <c r="G660" s="34" t="n">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="661">
@@ -33723,7 +33723,7 @@
         <v>59</v>
       </c>
       <c r="G662" s="34" t="n">
-        <v>9120</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="663">
@@ -34275,7 +34275,7 @@
         <v>7</v>
       </c>
       <c r="G685" s="34" t="n">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="686">
@@ -34323,7 +34323,7 @@
         <v>128</v>
       </c>
       <c r="G687" s="34" t="n">
-        <v>9248</v>
+        <v>9249</v>
       </c>
     </row>
     <row r="688">
@@ -34875,7 +34875,7 @@
         <v>10</v>
       </c>
       <c r="G710" s="34" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="711">
@@ -34914,16 +34914,16 @@
         </is>
       </c>
       <c r="D712" s="34" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E712" s="34" t="n">
-        <v>-390</v>
+        <v>-389</v>
       </c>
       <c r="F712" s="42" t="n">
         <v>108</v>
       </c>
       <c r="G712" s="34" t="n">
-        <v>9356</v>
+        <v>9357</v>
       </c>
     </row>
     <row r="713">
@@ -35475,7 +35475,7 @@
         <v>2</v>
       </c>
       <c r="G735" s="34" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="736">
@@ -35514,13 +35514,13 @@
         </is>
       </c>
       <c r="D737" s="34" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E737" s="34" t="n">
         <v>-271</v>
       </c>
       <c r="F737" s="42" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G737" s="34" t="n">
         <v>9421</v>

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -763,7 +763,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="4">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/02 (일)</t>
+          <t>08/03 (월)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/03 (월)</t>
+          <t>08/04 (화)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/04 (화)</t>
+          <t>08/05 (수)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/06 (목)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/07 (금)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/05 (수)</t>
+          <t>08/08 (토)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/06 (목)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/07 (금)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/08 (토)</t>
+          <t>08/09 (일)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/09 (일)</t>
+          <t>08/10 (월)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/10 (월)</t>
+          <t>08/11 (화)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/11 (화)</t>
+          <t>08/12 (수)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/13 (목)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/14 (금)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">
